--- a/optimize_prep/output/approx_accuracy_report.xlsx
+++ b/optimize_prep/output/approx_accuracy_report.xlsx
@@ -598,28 +598,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>63281779</v>
+        <v>63071710</v>
       </c>
       <c r="E4" t="n">
-        <v>63281779</v>
+        <v>63071710</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>56717761</v>
+        <v>56481516</v>
       </c>
       <c r="H4" t="n">
-        <v>-10.37</v>
+        <v>-10.45</v>
       </c>
       <c r="I4" t="n">
-        <v>6564018</v>
+        <v>6590194</v>
       </c>
       <c r="J4" t="n">
-        <v>1044642000</v>
+        <v>1043020538</v>
       </c>
       <c r="K4" t="n">
-        <v>1044642000</v>
+        <v>1043020538</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -645,31 +645,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>161080947</v>
+        <v>161236335</v>
       </c>
       <c r="E5" t="n">
-        <v>161080947</v>
+        <v>161236335</v>
       </c>
       <c r="F5" t="n">
         <v>-0</v>
       </c>
       <c r="G5" t="n">
-        <v>107632430</v>
+        <v>107791520</v>
       </c>
       <c r="H5" t="n">
-        <v>-33.18</v>
+        <v>-33.15</v>
       </c>
       <c r="I5" t="n">
-        <v>53448516</v>
+        <v>53444815</v>
       </c>
       <c r="J5" t="n">
-        <v>3001588278</v>
+        <v>3002470635</v>
       </c>
       <c r="K5" t="n">
-        <v>3001588278</v>
+        <v>3002470635</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -692,28 +692,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>103936384</v>
+        <v>103943612</v>
       </c>
       <c r="E6" t="n">
-        <v>103936384</v>
+        <v>103943612</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>93689692</v>
+        <v>93659666</v>
       </c>
       <c r="H6" t="n">
-        <v>-9.859999999999999</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>10246692</v>
+        <v>10283946</v>
       </c>
       <c r="J6" t="n">
-        <v>1087577241</v>
+        <v>1086663745</v>
       </c>
       <c r="K6" t="n">
-        <v>1087577241</v>
+        <v>1086663745</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -739,28 +739,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>206367314</v>
+        <v>206228546</v>
       </c>
       <c r="E7" t="n">
-        <v>206367314</v>
+        <v>206228546</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>184075231</v>
+        <v>183866388</v>
       </c>
       <c r="H7" t="n">
-        <v>-10.8</v>
+        <v>-10.84</v>
       </c>
       <c r="I7" t="n">
-        <v>22292083</v>
+        <v>22362158</v>
       </c>
       <c r="J7" t="n">
-        <v>1796114499</v>
+        <v>1794288389</v>
       </c>
       <c r="K7" t="n">
-        <v>1796114499</v>
+        <v>1794288389</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -786,34 +786,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>72341794</v>
+        <v>78861997</v>
       </c>
       <c r="E8" t="n">
-        <v>72341794</v>
+        <v>78861997</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>62313424</v>
+        <v>78002396</v>
       </c>
       <c r="H8" t="n">
-        <v>-13.86</v>
+        <v>-1.09</v>
       </c>
       <c r="I8" t="n">
-        <v>10028370</v>
+        <v>859600</v>
       </c>
       <c r="J8" t="n">
-        <v>1491278447</v>
+        <v>1570951150</v>
       </c>
       <c r="K8" t="n">
-        <v>1491278447</v>
+        <v>1570951150</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -833,34 +833,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>43133457</v>
+        <v>44953916</v>
       </c>
       <c r="E9" t="n">
-        <v>43133457</v>
+        <v>44953916</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>42977193</v>
+        <v>42324254</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.36</v>
+        <v>-5.85</v>
       </c>
       <c r="I9" t="n">
-        <v>156264</v>
+        <v>2629662</v>
       </c>
       <c r="J9" t="n">
-        <v>1109330699</v>
+        <v>1110784884</v>
       </c>
       <c r="K9" t="n">
-        <v>1109330699</v>
+        <v>1110784884</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -968,28 +968,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32001877</v>
+        <v>31636106</v>
       </c>
       <c r="E12" t="n">
-        <v>32001877</v>
+        <v>31636106</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>20584163</v>
+        <v>20521508</v>
       </c>
       <c r="H12" t="n">
-        <v>-35.68</v>
+        <v>-35.13</v>
       </c>
       <c r="I12" t="n">
-        <v>11417714</v>
+        <v>11114598</v>
       </c>
       <c r="J12" t="n">
-        <v>627167127</v>
+        <v>624595350</v>
       </c>
       <c r="K12" t="n">
-        <v>627167127</v>
+        <v>624595350</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1015,28 +1015,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-48088020</v>
+        <v>-46835551</v>
       </c>
       <c r="E13" t="n">
-        <v>-48088020</v>
+        <v>-46835551</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-44594832</v>
+        <v>-43737863</v>
       </c>
       <c r="H13" t="n">
-        <v>7.26</v>
+        <v>6.61</v>
       </c>
       <c r="I13" t="n">
-        <v>-3493189</v>
+        <v>-3097688</v>
       </c>
       <c r="J13" t="n">
-        <v>-1208239316</v>
+        <v>-1207358083</v>
       </c>
       <c r="K13" t="n">
-        <v>-1208239316</v>
+        <v>-1207358083</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-37591</v>
+        <v>-1096</v>
       </c>
       <c r="E18" t="n">
-        <v>-37591</v>
+        <v>-1096</v>
       </c>
       <c r="F18" t="n">
         <v>-0</v>
       </c>
       <c r="G18" t="n">
-        <v>-37591</v>
+        <v>-1096</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-399999987</v>
+        <v>-399963496</v>
       </c>
       <c r="K18" t="n">
-        <v>-399999987</v>
+        <v>-399963496</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1275,34 +1275,34 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-69943537</v>
+        <v>-69931279</v>
       </c>
       <c r="E19" t="n">
-        <v>-69943537</v>
+        <v>-69931279</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G19" t="n">
-        <v>-63769409</v>
+        <v>-63893777</v>
       </c>
       <c r="H19" t="n">
-        <v>8.83</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-6174127</v>
+        <v>-6037502</v>
       </c>
       <c r="J19" t="n">
-        <v>-2065192056</v>
+        <v>-2064682015</v>
       </c>
       <c r="K19" t="n">
-        <v>-2065192056</v>
+        <v>-2064682015</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1322,31 +1322,31 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7531326</v>
+        <v>7504692</v>
       </c>
       <c r="E20" t="n">
-        <v>7531326</v>
+        <v>7504692</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>4094995</v>
+        <v>4095008</v>
       </c>
       <c r="H20" t="n">
-        <v>-45.63</v>
+        <v>-45.43</v>
       </c>
       <c r="I20" t="n">
-        <v>3436331</v>
+        <v>3409684</v>
       </c>
       <c r="J20" t="n">
-        <v>200001061</v>
+        <v>200000936</v>
       </c>
       <c r="K20" t="n">
-        <v>200001061</v>
+        <v>200000936</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1369,34 +1369,34 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-14772956</v>
+        <v>-15062077</v>
       </c>
       <c r="E21" t="n">
-        <v>-14772956</v>
+        <v>-15062077</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-8189953</v>
+        <v>-8189919</v>
       </c>
       <c r="H21" t="n">
-        <v>44.56</v>
+        <v>45.63</v>
       </c>
       <c r="I21" t="n">
-        <v>-6583003</v>
+        <v>-6872158</v>
       </c>
       <c r="J21" t="n">
-        <v>-400002724</v>
+        <v>-400002071</v>
       </c>
       <c r="K21" t="n">
-        <v>-400002724</v>
+        <v>-400002071</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="22">
@@ -2254,31 +2254,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>497210</v>
+        <v>499376</v>
       </c>
       <c r="F16" t="n">
-        <v>497210</v>
+        <v>499376</v>
       </c>
       <c r="G16" t="n">
         <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>7061228</v>
+        <v>7089570</v>
       </c>
       <c r="I16" t="n">
-        <v>1320.17</v>
+        <v>1319.69</v>
       </c>
       <c r="J16" t="n">
-        <v>19586353</v>
+        <v>19120304</v>
       </c>
       <c r="K16" t="n">
-        <v>19586355</v>
+        <v>19120305</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>19586355</v>
+        <v>19120305</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2306,34 +2306,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-2087968</v>
+        <v>-2142960</v>
       </c>
       <c r="F17" t="n">
-        <v>-2087968</v>
+        <v>-2142960</v>
       </c>
       <c r="G17" t="n">
         <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>4476050</v>
+        <v>4447234</v>
       </c>
       <c r="I17" t="n">
-        <v>314.37</v>
+        <v>307.53</v>
       </c>
       <c r="J17" t="n">
-        <v>24939534</v>
+        <v>24569067</v>
       </c>
       <c r="K17" t="n">
-        <v>24939533</v>
+        <v>24569068</v>
       </c>
       <c r="L17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>24939533</v>
+        <v>24569068</v>
       </c>
       <c r="N17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2358,34 +2358,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>-3897341</v>
+        <v>-3990697</v>
       </c>
       <c r="F18" t="n">
-        <v>-3897341</v>
+        <v>-3990697</v>
       </c>
       <c r="G18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2666677</v>
+        <v>2599497</v>
       </c>
       <c r="I18" t="n">
-        <v>168.42</v>
+        <v>165.14</v>
       </c>
       <c r="J18" t="n">
-        <v>64125311</v>
+        <v>63153444</v>
       </c>
       <c r="K18" t="n">
-        <v>64125309</v>
+        <v>63153447</v>
       </c>
       <c r="L18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>64125309</v>
+        <v>63153447</v>
       </c>
       <c r="N18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2410,34 +2410,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2142069</v>
+        <v>2176760</v>
       </c>
       <c r="F19" t="n">
-        <v>2142069</v>
+        <v>2176760</v>
       </c>
       <c r="G19" t="n">
         <v>-0</v>
       </c>
       <c r="H19" t="n">
-        <v>8706087</v>
+        <v>8766954</v>
       </c>
       <c r="I19" t="n">
-        <v>306.43</v>
+        <v>302.75</v>
       </c>
       <c r="J19" t="n">
-        <v>-58505766</v>
+        <v>-57675768</v>
       </c>
       <c r="K19" t="n">
-        <v>-58505766</v>
+        <v>-57675766</v>
       </c>
       <c r="L19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-58505766</v>
+        <v>-57675766</v>
       </c>
       <c r="N19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2462,34 +2462,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-3316929</v>
+        <v>-3400070</v>
       </c>
       <c r="F20" t="n">
-        <v>-3316929</v>
+        <v>-3400070</v>
       </c>
       <c r="G20" t="n">
         <v>-0</v>
       </c>
       <c r="H20" t="n">
-        <v>3247089</v>
+        <v>3190124</v>
       </c>
       <c r="I20" t="n">
-        <v>197.89</v>
+        <v>193.83</v>
       </c>
       <c r="J20" t="n">
-        <v>7554739</v>
+        <v>7597734</v>
       </c>
       <c r="K20" t="n">
-        <v>7554738</v>
+        <v>7597734</v>
       </c>
       <c r="L20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7554738</v>
+        <v>7597734</v>
       </c>
       <c r="N20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2514,34 +2514,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1560994</v>
+        <v>1585460</v>
       </c>
       <c r="F21" t="n">
-        <v>1560994</v>
+        <v>1585460</v>
       </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8175654</v>
+      </c>
+      <c r="I21" t="n">
+        <v>415.66</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-7524320</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-7524322</v>
+      </c>
+      <c r="L21" t="n">
         <v>-0</v>
       </c>
-      <c r="H21" t="n">
-        <v>8125012</v>
-      </c>
-      <c r="I21" t="n">
-        <v>420.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-7481861</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-7481859</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
-        <v>-7481859</v>
+        <v>-7524322</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="22">
@@ -2566,34 +2566,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-1775876</v>
+        <v>-1826420</v>
       </c>
       <c r="F22" t="n">
-        <v>-1775876</v>
+        <v>-1826420</v>
       </c>
       <c r="G22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>4788142</v>
+        <v>4763774</v>
       </c>
       <c r="I22" t="n">
-        <v>369.62</v>
+        <v>360.83</v>
       </c>
       <c r="J22" t="n">
-        <v>-24588602</v>
+        <v>-24079680</v>
       </c>
       <c r="K22" t="n">
-        <v>-24588603</v>
+        <v>-24079678</v>
       </c>
       <c r="L22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-24588603</v>
+        <v>-24079678</v>
       </c>
       <c r="N22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2618,31 +2618,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4012611</v>
+        <v>3795608</v>
       </c>
       <c r="F23" t="n">
-        <v>4012611</v>
+        <v>3795608</v>
       </c>
       <c r="G23" t="n">
         <v>-0</v>
       </c>
       <c r="H23" t="n">
-        <v>57461127</v>
+        <v>57240423</v>
       </c>
       <c r="I23" t="n">
-        <v>1332.01</v>
+        <v>1408.07</v>
       </c>
       <c r="J23" t="n">
-        <v>-1866014</v>
+        <v>-1975186</v>
       </c>
       <c r="K23" t="n">
-        <v>-1866011</v>
+        <v>-1975185</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1866011</v>
+        <v>-1975185</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2670,31 +2670,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-23483339</v>
+        <v>-23413591</v>
       </c>
       <c r="F24" t="n">
-        <v>-23483340</v>
+        <v>-23413591</v>
       </c>
       <c r="G24" t="n">
         <v>-0</v>
       </c>
       <c r="H24" t="n">
-        <v>29965176</v>
+        <v>30031224</v>
       </c>
       <c r="I24" t="n">
-        <v>227.6</v>
+        <v>228.26</v>
       </c>
       <c r="J24" t="n">
-        <v>10286307</v>
+        <v>10446248</v>
       </c>
       <c r="K24" t="n">
-        <v>10284726</v>
+        <v>10444496</v>
       </c>
       <c r="L24" t="n">
         <v>-0.02</v>
       </c>
       <c r="M24" t="n">
-        <v>10284726</v>
+        <v>10444496</v>
       </c>
       <c r="N24" t="n">
         <v>-0.02</v>
@@ -2722,34 +2722,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-58096339</v>
+        <v>-57925950</v>
       </c>
       <c r="F25" t="n">
-        <v>-58096339</v>
+        <v>-57925950</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-4647823</v>
+        <v>-4481135</v>
       </c>
       <c r="I25" t="n">
-        <v>92</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>26663480</v>
+        <v>27074775</v>
       </c>
       <c r="K25" t="n">
-        <v>26663480</v>
+        <v>27074775</v>
       </c>
       <c r="L25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>26663480</v>
+        <v>27074775</v>
       </c>
       <c r="N25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2774,34 +2774,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>57447918</v>
+        <v>57282372</v>
       </c>
       <c r="F26" t="n">
-        <v>57447918</v>
+        <v>57282372</v>
       </c>
       <c r="G26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>110896434</v>
+        <v>110727187</v>
       </c>
       <c r="I26" t="n">
-        <v>93.04000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="J26" t="n">
-        <v>-23521803</v>
+        <v>-23902403</v>
       </c>
       <c r="K26" t="n">
-        <v>-23521803</v>
+        <v>-23902399</v>
       </c>
       <c r="L26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-23521803</v>
+        <v>-23902399</v>
       </c>
       <c r="N26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2826,31 +2826,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-27459403</v>
+        <v>-27194036</v>
       </c>
       <c r="F27" t="n">
-        <v>-27459403</v>
+        <v>-27194036</v>
       </c>
       <c r="G27" t="n">
         <v>-0</v>
       </c>
       <c r="H27" t="n">
-        <v>25989113</v>
+        <v>26250779</v>
       </c>
       <c r="I27" t="n">
-        <v>194.65</v>
+        <v>196.53</v>
       </c>
       <c r="J27" t="n">
-        <v>12139530</v>
+        <v>12397680</v>
       </c>
       <c r="K27" t="n">
-        <v>12139531</v>
+        <v>12397684</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>12139531</v>
+        <v>12397684</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2878,31 +2878,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>26730887</v>
+        <v>26470091</v>
       </c>
       <c r="F28" t="n">
-        <v>26730887</v>
+        <v>26470091</v>
       </c>
       <c r="G28" t="n">
         <v>-0</v>
       </c>
       <c r="H28" t="n">
-        <v>80179403</v>
+        <v>79914906</v>
       </c>
       <c r="I28" t="n">
-        <v>199.95</v>
+        <v>201.91</v>
       </c>
       <c r="J28" t="n">
-        <v>-11938824</v>
+        <v>-12197310</v>
       </c>
       <c r="K28" t="n">
-        <v>-11938822</v>
+        <v>-12197304</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-11938822</v>
+        <v>-12197304</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2930,31 +2930,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2756796</v>
+        <v>2941110</v>
       </c>
       <c r="F29" t="n">
-        <v>2756796</v>
+        <v>2941111</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>56205312</v>
+        <v>56385926</v>
       </c>
       <c r="I29" t="n">
-        <v>1938.79</v>
+        <v>1817.16</v>
       </c>
       <c r="J29" t="n">
-        <v>-552091</v>
+        <v>-493911</v>
       </c>
       <c r="K29" t="n">
-        <v>-552089</v>
+        <v>-493901</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-552089</v>
+        <v>-493901</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2982,34 +2982,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1423828</v>
+        <v>1401842</v>
       </c>
       <c r="F30" t="n">
-        <v>1423828</v>
+        <v>1401842</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H30" t="n">
-        <v>11670520</v>
+        <v>11685788</v>
       </c>
       <c r="I30" t="n">
-        <v>719.66</v>
+        <v>733.6</v>
       </c>
       <c r="J30" t="n">
-        <v>27259014</v>
+        <v>27108471</v>
       </c>
       <c r="K30" t="n">
-        <v>27259016</v>
+        <v>27108467</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M30" t="n">
-        <v>27259016</v>
+        <v>27108467</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="31">
@@ -3034,34 +3034,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-1488350</v>
+        <v>-1501357</v>
       </c>
       <c r="F31" t="n">
-        <v>-1488350</v>
+        <v>-1501357</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>8758342</v>
+        <v>8782589</v>
       </c>
       <c r="I31" t="n">
-        <v>688.46</v>
+        <v>684.98</v>
       </c>
       <c r="J31" t="n">
-        <v>31092440</v>
+        <v>30973964</v>
       </c>
       <c r="K31" t="n">
-        <v>31092441</v>
+        <v>30973962</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" t="n">
-        <v>31092441</v>
+        <v>30973962</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3086,31 +3086,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-3587681</v>
+        <v>-3598711</v>
       </c>
       <c r="F32" t="n">
-        <v>-3587681</v>
+        <v>-3598711</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>6659011</v>
+        <v>6685235</v>
       </c>
       <c r="I32" t="n">
-        <v>285.61</v>
+        <v>285.77</v>
       </c>
       <c r="J32" t="n">
-        <v>80180835</v>
+        <v>79868570</v>
       </c>
       <c r="K32" t="n">
-        <v>80180832</v>
+        <v>79868567</v>
       </c>
       <c r="L32" t="n">
         <v>-0</v>
       </c>
       <c r="M32" t="n">
-        <v>80180832</v>
+        <v>79868567</v>
       </c>
       <c r="N32" t="n">
         <v>-0</v>
@@ -3138,34 +3138,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3419709</v>
+        <v>3402086</v>
       </c>
       <c r="F33" t="n">
-        <v>3419709</v>
+        <v>3402086</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>13666401</v>
+        <v>13686032</v>
       </c>
       <c r="I33" t="n">
-        <v>299.64</v>
+        <v>302.28</v>
       </c>
       <c r="J33" t="n">
-        <v>-72450582</v>
+        <v>-72188151</v>
       </c>
       <c r="K33" t="n">
-        <v>-72450582</v>
+        <v>-72188154</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M33" t="n">
-        <v>-72450582</v>
+        <v>-72188154</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="34">
@@ -3190,34 +3190,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-2836701</v>
+        <v>-2842868</v>
       </c>
       <c r="F34" t="n">
-        <v>-2836701</v>
+        <v>-2842868</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>7409991</v>
+        <v>7441078</v>
       </c>
       <c r="I34" t="n">
-        <v>361.22</v>
+        <v>361.75</v>
       </c>
       <c r="J34" t="n">
-        <v>6897147</v>
+        <v>6912030</v>
       </c>
       <c r="K34" t="n">
-        <v>6897149</v>
+        <v>6912027</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M34" t="n">
-        <v>6897149</v>
+        <v>6912027</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="35">
@@ -3242,34 +3242,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2667554</v>
+        <v>2645071</v>
       </c>
       <c r="F35" t="n">
-        <v>2667554</v>
+        <v>2645071</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>12914246</v>
+        <v>12929017</v>
       </c>
       <c r="I35" t="n">
-        <v>384.12</v>
+        <v>388.8</v>
       </c>
       <c r="J35" t="n">
-        <v>-6833058</v>
+        <v>-6847757</v>
       </c>
       <c r="K35" t="n">
-        <v>-6833058</v>
+        <v>-6847760</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M35" t="n">
-        <v>-6833058</v>
+        <v>-6847760</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="36">
@@ -3294,31 +3294,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-1045615</v>
+        <v>-1053280</v>
       </c>
       <c r="F36" t="n">
-        <v>-1045615</v>
+        <v>-1053280</v>
       </c>
       <c r="G36" t="n">
         <v>-0</v>
       </c>
       <c r="H36" t="n">
-        <v>9201077</v>
+        <v>9230666</v>
       </c>
       <c r="I36" t="n">
-        <v>979.97</v>
+        <v>976.37</v>
       </c>
       <c r="J36" t="n">
-        <v>-33045040</v>
+        <v>-32882440</v>
       </c>
       <c r="K36" t="n">
-        <v>-33045040</v>
+        <v>-32882443</v>
       </c>
       <c r="L36" t="n">
         <v>-0</v>
       </c>
       <c r="M36" t="n">
-        <v>-33045040</v>
+        <v>-32882443</v>
       </c>
       <c r="N36" t="n">
         <v>-0</v>
@@ -3346,34 +3346,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-498386</v>
+        <v>-507620</v>
       </c>
       <c r="F37" t="n">
-        <v>-594569</v>
+        <v>-602084</v>
       </c>
       <c r="G37" t="n">
-        <v>-19.3</v>
+        <v>-18.61</v>
       </c>
       <c r="H37" t="n">
-        <v>21697514</v>
+        <v>21760074</v>
       </c>
       <c r="I37" t="n">
-        <v>4453.56</v>
+        <v>4386.69</v>
       </c>
       <c r="J37" t="n">
-        <v>-5470529</v>
+        <v>-5487565</v>
       </c>
       <c r="K37" t="n">
-        <v>-5470530</v>
+        <v>-5487564</v>
       </c>
       <c r="L37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-5470530</v>
+        <v>-5487564</v>
       </c>
       <c r="N37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3398,31 +3398,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-9764729</v>
+        <v>-9741662</v>
       </c>
       <c r="F38" t="n">
-        <v>-9765408</v>
+        <v>-9742106</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="H38" t="n">
-        <v>12526675</v>
+        <v>12620052</v>
       </c>
       <c r="I38" t="n">
-        <v>228.28</v>
+        <v>229.55</v>
       </c>
       <c r="J38" t="n">
-        <v>9668714</v>
+        <v>9669408</v>
       </c>
       <c r="K38" t="n">
-        <v>9668382</v>
+        <v>9669070</v>
       </c>
       <c r="L38" t="n">
         <v>-0</v>
       </c>
       <c r="M38" t="n">
-        <v>9668382</v>
+        <v>9669070</v>
       </c>
       <c r="N38" t="n">
         <v>-0</v>
@@ -3450,34 +3450,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-23849876</v>
+        <v>-23794617</v>
       </c>
       <c r="F39" t="n">
-        <v>-23850048</v>
+        <v>-23794192</v>
       </c>
       <c r="G39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1557965</v>
+        <v>-1432034</v>
       </c>
       <c r="I39" t="n">
-        <v>93.47</v>
+        <v>93.98</v>
       </c>
       <c r="J39" t="n">
-        <v>24611995</v>
+        <v>24612672</v>
       </c>
       <c r="K39" t="n">
-        <v>24611994</v>
+        <v>24612675</v>
       </c>
       <c r="L39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>24611994</v>
+        <v>24612675</v>
       </c>
       <c r="N39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3502,34 +3502,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>23168422</v>
+        <v>23116208</v>
       </c>
       <c r="F40" t="n">
-        <v>23166604</v>
+        <v>23113779</v>
       </c>
       <c r="G40" t="n">
         <v>-0.01</v>
       </c>
       <c r="H40" t="n">
-        <v>45458687</v>
+        <v>45475937</v>
       </c>
       <c r="I40" t="n">
-        <v>96.20999999999999</v>
+        <v>96.73</v>
       </c>
       <c r="J40" t="n">
-        <v>-23111768</v>
+        <v>-23115869</v>
       </c>
       <c r="K40" t="n">
-        <v>-23111770</v>
+        <v>-23115866</v>
       </c>
       <c r="L40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-23111770</v>
+        <v>-23115866</v>
       </c>
       <c r="N40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3554,31 +3554,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-9669632</v>
+        <v>-9636853</v>
       </c>
       <c r="F41" t="n">
-        <v>-9585658</v>
+        <v>-9554185</v>
       </c>
       <c r="G41" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="H41" t="n">
-        <v>12706425</v>
+        <v>12807973</v>
       </c>
       <c r="I41" t="n">
-        <v>231.41</v>
+        <v>232.91</v>
       </c>
       <c r="J41" t="n">
-        <v>14697866</v>
+        <v>14713726</v>
       </c>
       <c r="K41" t="n">
-        <v>14697867</v>
+        <v>14713728</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>14697867</v>
+        <v>14713728</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3606,34 +3606,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>8952989</v>
+        <v>8923345</v>
       </c>
       <c r="F42" t="n">
-        <v>8866729</v>
+        <v>8838377</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.96</v>
+        <v>-0.95</v>
       </c>
       <c r="H42" t="n">
-        <v>31158812</v>
+        <v>31200535</v>
       </c>
       <c r="I42" t="n">
-        <v>248.03</v>
+        <v>249.65</v>
       </c>
       <c r="J42" t="n">
-        <v>-14502086</v>
+        <v>-14517901</v>
       </c>
       <c r="K42" t="n">
-        <v>-14502088</v>
+        <v>-14517900</v>
       </c>
       <c r="L42" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-14502088</v>
+        <v>-14517900</v>
       </c>
       <c r="N42" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3658,31 +3658,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2688826</v>
+        <v>2693701</v>
       </c>
       <c r="F43" t="n">
-        <v>2775550</v>
+        <v>2778748</v>
       </c>
       <c r="G43" t="n">
-        <v>3.23</v>
+        <v>3.16</v>
       </c>
       <c r="H43" t="n">
-        <v>25067633</v>
+        <v>25140906</v>
       </c>
       <c r="I43" t="n">
-        <v>832.29</v>
+        <v>833.3200000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>2456723</v>
+        <v>2471276</v>
       </c>
       <c r="K43" t="n">
-        <v>2456723</v>
+        <v>2471277</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2456723</v>
+        <v>2471277</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3710,34 +3710,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1434024</v>
+        <v>287047</v>
       </c>
       <c r="F44" t="n">
-        <v>1434024</v>
+        <v>287047</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H44" t="n">
-        <v>11462394</v>
+        <v>1146647</v>
       </c>
       <c r="I44" t="n">
-        <v>699.3200000000001</v>
+        <v>299.46</v>
       </c>
       <c r="J44" t="n">
-        <v>32128752</v>
+        <v>34078764</v>
       </c>
       <c r="K44" t="n">
-        <v>33277421</v>
+        <v>34078764</v>
       </c>
       <c r="L44" t="n">
-        <v>3.58</v>
+        <v>-0</v>
       </c>
       <c r="M44" t="n">
-        <v>33277421</v>
+        <v>34078764</v>
       </c>
       <c r="N44" t="n">
-        <v>3.58</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="45">
@@ -3762,34 +3762,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-1275861</v>
+        <v>-170755</v>
       </c>
       <c r="F45" t="n">
-        <v>-1275861</v>
+        <v>-170755</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>8752509</v>
+        <v>688845</v>
       </c>
       <c r="I45" t="n">
-        <v>786.01</v>
+        <v>503.41</v>
       </c>
       <c r="J45" t="n">
-        <v>38974664</v>
+        <v>41380880</v>
       </c>
       <c r="K45" t="n">
-        <v>40397633</v>
+        <v>41380880</v>
       </c>
       <c r="L45" t="n">
-        <v>3.65</v>
+        <v>-0</v>
       </c>
       <c r="M45" t="n">
-        <v>40397633</v>
+        <v>41380880</v>
       </c>
       <c r="N45" t="n">
-        <v>3.65</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="46">
@@ -3814,34 +3814,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-3176194</v>
+        <v>-425751</v>
       </c>
       <c r="F46" t="n">
-        <v>-3176194</v>
+        <v>-425751</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H46" t="n">
-        <v>6852176</v>
+        <v>433849</v>
       </c>
       <c r="I46" t="n">
-        <v>315.74</v>
+        <v>201.9</v>
       </c>
       <c r="J46" t="n">
-        <v>100161347</v>
+        <v>106036598</v>
       </c>
       <c r="K46" t="n">
-        <v>103808661</v>
+        <v>106036598</v>
       </c>
       <c r="L46" t="n">
-        <v>3.64</v>
+        <v>-0</v>
       </c>
       <c r="M46" t="n">
-        <v>103808661</v>
+        <v>106036598</v>
       </c>
       <c r="N46" t="n">
-        <v>3.64</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="47">
@@ -3866,34 +3866,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3221374</v>
+        <v>429566</v>
       </c>
       <c r="F47" t="n">
-        <v>3221374</v>
+        <v>429566</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H47" t="n">
-        <v>13249744</v>
+        <v>1289166</v>
       </c>
       <c r="I47" t="n">
-        <v>311.31</v>
+        <v>200.11</v>
       </c>
       <c r="J47" t="n">
-        <v>-91498854</v>
+        <v>-97773111</v>
       </c>
       <c r="K47" t="n">
-        <v>-94859099</v>
+        <v>-97773112</v>
       </c>
       <c r="L47" t="n">
-        <v>-3.67</v>
+        <v>-0</v>
       </c>
       <c r="M47" t="n">
-        <v>-94859099</v>
+        <v>-97773112</v>
       </c>
       <c r="N47" t="n">
-        <v>-3.67</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="48">
@@ -3918,34 +3918,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-2544336</v>
+        <v>-425319</v>
       </c>
       <c r="F48" t="n">
-        <v>-2544336</v>
+        <v>-425319</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>7484034</v>
+        <v>434281</v>
       </c>
       <c r="I48" t="n">
-        <v>394.14</v>
+        <v>202.11</v>
       </c>
       <c r="J48" t="n">
-        <v>10458290</v>
+        <v>11084040</v>
       </c>
       <c r="K48" t="n">
-        <v>10860313</v>
+        <v>11084040</v>
       </c>
       <c r="L48" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>10860313</v>
+        <v>11084040</v>
       </c>
       <c r="N48" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3970,34 +3970,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2572504</v>
+        <v>428576</v>
       </c>
       <c r="F49" t="n">
-        <v>2572504</v>
+        <v>428576</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H49" t="n">
-        <v>12600874</v>
+        <v>1288176</v>
       </c>
       <c r="I49" t="n">
-        <v>389.83</v>
+        <v>200.57</v>
       </c>
       <c r="J49" t="n">
-        <v>-10355551</v>
+        <v>-10978767</v>
       </c>
       <c r="K49" t="n">
-        <v>-10753898</v>
+        <v>-10978767</v>
       </c>
       <c r="L49" t="n">
-        <v>-3.85</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-10753898</v>
+        <v>-10978767</v>
       </c>
       <c r="N49" t="n">
-        <v>-3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4022,34 +4022,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-920592</v>
+        <v>-210876</v>
       </c>
       <c r="F50" t="n">
-        <v>-920592</v>
+        <v>-210876</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>9107778</v>
+        <v>648724</v>
       </c>
       <c r="I50" t="n">
-        <v>1089.34</v>
+        <v>407.63</v>
       </c>
       <c r="J50" t="n">
-        <v>-39824788</v>
+        <v>-42581994</v>
       </c>
       <c r="K50" t="n">
-        <v>-41266619</v>
+        <v>-42581994</v>
       </c>
       <c r="L50" t="n">
-        <v>-3.62</v>
+        <v>-0</v>
       </c>
       <c r="M50" t="n">
-        <v>-41266619</v>
+        <v>-42581994</v>
       </c>
       <c r="N50" t="n">
-        <v>-3.62</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="51">
@@ -4074,34 +4074,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>749555</v>
+        <v>1468465</v>
       </c>
       <c r="F51" t="n">
-        <v>749555</v>
+        <v>1421238</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-3.22</v>
       </c>
       <c r="H51" t="n">
-        <v>905819</v>
+        <v>4050900</v>
       </c>
       <c r="I51" t="n">
-        <v>20.85</v>
+        <v>175.86</v>
       </c>
       <c r="J51" t="n">
-        <v>-5002510</v>
+        <v>-6070731</v>
       </c>
       <c r="K51" t="n">
-        <v>-5002510</v>
+        <v>-6070731</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M51" t="n">
-        <v>-5002510</v>
+        <v>-6070731</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="52">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-5623883</v>
+        <v>-4611378</v>
       </c>
       <c r="F52" t="n">
-        <v>-5623883</v>
+        <v>-4673222</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-1.34</v>
       </c>
       <c r="H52" t="n">
-        <v>-5467619</v>
+        <v>-2043560</v>
       </c>
       <c r="I52" t="n">
-        <v>2.78</v>
+        <v>55.68</v>
       </c>
       <c r="J52" t="n">
-        <v>3148918</v>
+        <v>4246042</v>
       </c>
       <c r="K52" t="n">
-        <v>3140325</v>
+        <v>4246042</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.27</v>
+        <v>-0</v>
       </c>
       <c r="M52" t="n">
-        <v>3140325</v>
+        <v>4246042</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.27</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="53">
@@ -4178,31 +4178,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>-14010662</v>
+        <v>-11490710</v>
       </c>
       <c r="F53" t="n">
-        <v>-14010662</v>
+        <v>-11644405</v>
       </c>
       <c r="G53" t="n">
-        <v>-0</v>
+        <v>-1.34</v>
       </c>
       <c r="H53" t="n">
-        <v>-13854398</v>
+        <v>-9014743</v>
       </c>
       <c r="I53" t="n">
-        <v>1.12</v>
+        <v>21.55</v>
       </c>
       <c r="J53" t="n">
-        <v>7876742</v>
+        <v>10638145</v>
       </c>
       <c r="K53" t="n">
-        <v>7876741</v>
+        <v>10638145</v>
       </c>
       <c r="L53" t="n">
         <v>-0</v>
       </c>
       <c r="M53" t="n">
-        <v>7876741</v>
+        <v>10638145</v>
       </c>
       <c r="N53" t="n">
         <v>-0</v>
@@ -4230,31 +4230,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>14188000</v>
+        <v>11618557</v>
       </c>
       <c r="F54" t="n">
-        <v>14188000</v>
+        <v>11775235</v>
       </c>
       <c r="G54" t="n">
-        <v>-0</v>
+        <v>1.35</v>
       </c>
       <c r="H54" t="n">
-        <v>14344264</v>
+        <v>14404897</v>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>23.98</v>
       </c>
       <c r="J54" t="n">
-        <v>-7767111</v>
+        <v>-10497722</v>
       </c>
       <c r="K54" t="n">
-        <v>-7767111</v>
+        <v>-10497722</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-7767111</v>
+        <v>-10497722</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -4282,31 +4282,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>-6298053</v>
+        <v>-5922622</v>
       </c>
       <c r="F55" t="n">
-        <v>-6298053</v>
+        <v>-5943134</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="H55" t="n">
-        <v>-6141789</v>
+        <v>-3313472</v>
       </c>
       <c r="I55" t="n">
-        <v>2.48</v>
+        <v>44.05</v>
       </c>
       <c r="J55" t="n">
-        <v>7669586</v>
+        <v>9732389</v>
       </c>
       <c r="K55" t="n">
-        <v>7669586</v>
+        <v>9732389</v>
       </c>
       <c r="L55" t="n">
         <v>-0</v>
       </c>
       <c r="M55" t="n">
-        <v>7669586</v>
+        <v>9732389</v>
       </c>
       <c r="N55" t="n">
         <v>-0</v>
@@ -4334,31 +4334,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6342533</v>
+        <v>5957637</v>
       </c>
       <c r="F56" t="n">
-        <v>6342533</v>
+        <v>5978148</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="H56" t="n">
-        <v>6498797</v>
+        <v>8607810</v>
       </c>
       <c r="I56" t="n">
-        <v>2.46</v>
+        <v>44.48</v>
       </c>
       <c r="J56" t="n">
-        <v>-7579957</v>
+        <v>-9624967</v>
       </c>
       <c r="K56" t="n">
-        <v>-7579957</v>
+        <v>-9624967</v>
       </c>
       <c r="L56" t="n">
         <v>-0</v>
       </c>
       <c r="M56" t="n">
-        <v>-7579957</v>
+        <v>-9624967</v>
       </c>
       <c r="N56" t="n">
         <v>-0</v>
@@ -4386,34 +4386,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1073856</v>
+        <v>93082</v>
       </c>
       <c r="F57" t="n">
-        <v>1073856</v>
+        <v>155294</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>66.84</v>
       </c>
       <c r="H57" t="n">
-        <v>1230120</v>
+        <v>2784956</v>
       </c>
       <c r="I57" t="n">
-        <v>14.55</v>
+        <v>2891.94</v>
       </c>
       <c r="J57" t="n">
-        <v>3696065</v>
+        <v>4337249</v>
       </c>
       <c r="K57" t="n">
-        <v>3696065</v>
+        <v>4337249</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M57" t="n">
-        <v>3696065</v>
+        <v>4337249</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="58">
@@ -5110,34 +5110,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>794440</v>
+        <v>828757</v>
       </c>
       <c r="F72" t="n">
-        <v>801015</v>
+        <v>828904</v>
       </c>
       <c r="G72" t="n">
-        <v>0.83</v>
+        <v>0.02</v>
       </c>
       <c r="H72" t="n">
-        <v>12218729</v>
+        <v>11943502</v>
       </c>
       <c r="I72" t="n">
-        <v>1438.03</v>
+        <v>1341.13</v>
       </c>
       <c r="J72" t="n">
-        <v>1901001</v>
+        <v>1474277</v>
       </c>
       <c r="K72" t="n">
-        <v>1901000</v>
+        <v>1474277</v>
       </c>
       <c r="L72" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>1901000</v>
+        <v>1474277</v>
       </c>
       <c r="N72" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -5162,34 +5162,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>-4096083</v>
+        <v>-4064226</v>
       </c>
       <c r="F73" t="n">
-        <v>-4027202</v>
+        <v>-3969512</v>
       </c>
       <c r="G73" t="n">
-        <v>1.68</v>
+        <v>2.33</v>
       </c>
       <c r="H73" t="n">
-        <v>7390512</v>
+        <v>7145086</v>
       </c>
       <c r="I73" t="n">
-        <v>280.43</v>
+        <v>275.8</v>
       </c>
       <c r="J73" t="n">
-        <v>4389173</v>
+        <v>4115554</v>
       </c>
       <c r="K73" t="n">
-        <v>4389025</v>
+        <v>4114771</v>
       </c>
       <c r="L73" t="n">
-        <v>-0</v>
+        <v>-0.02</v>
       </c>
       <c r="M73" t="n">
-        <v>4389025</v>
+        <v>4114771</v>
       </c>
       <c r="N73" t="n">
-        <v>-0</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="74">
@@ -5214,31 +5214,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>-10128696</v>
+        <v>-10060797</v>
       </c>
       <c r="F74" t="n">
-        <v>-9962088</v>
+        <v>-9830185</v>
       </c>
       <c r="G74" t="n">
-        <v>1.64</v>
+        <v>2.29</v>
       </c>
       <c r="H74" t="n">
-        <v>1455626</v>
+        <v>1284413</v>
       </c>
       <c r="I74" t="n">
-        <v>114.37</v>
+        <v>112.77</v>
       </c>
       <c r="J74" t="n">
-        <v>11254091</v>
+        <v>10540913</v>
       </c>
       <c r="K74" t="n">
-        <v>11254091</v>
+        <v>10540913</v>
       </c>
       <c r="L74" t="n">
         <v>-0</v>
       </c>
       <c r="M74" t="n">
-        <v>11254091</v>
+        <v>10540913</v>
       </c>
       <c r="N74" t="n">
         <v>-0</v>
@@ -5266,31 +5266,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>10009209</v>
+        <v>9956590</v>
       </c>
       <c r="F75" t="n">
-        <v>9852007</v>
+        <v>9736403</v>
       </c>
       <c r="G75" t="n">
-        <v>-1.57</v>
+        <v>-2.21</v>
       </c>
       <c r="H75" t="n">
-        <v>21269721</v>
+        <v>20851001</v>
       </c>
       <c r="I75" t="n">
-        <v>112.5</v>
+        <v>109.42</v>
       </c>
       <c r="J75" t="n">
-        <v>-10312100</v>
+        <v>-9696218</v>
       </c>
       <c r="K75" t="n">
-        <v>-10312101</v>
+        <v>-9696219</v>
       </c>
       <c r="L75" t="n">
         <v>-0</v>
       </c>
       <c r="M75" t="n">
-        <v>-10312101</v>
+        <v>-9696219</v>
       </c>
       <c r="N75" t="n">
         <v>-0</v>
@@ -5318,34 +5318,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>-4876534</v>
+        <v>-4867446</v>
       </c>
       <c r="F76" t="n">
-        <v>-4809563</v>
+        <v>-4768504</v>
       </c>
       <c r="G76" t="n">
-        <v>1.37</v>
+        <v>2.03</v>
       </c>
       <c r="H76" t="n">
-        <v>6608151</v>
+        <v>6346094</v>
       </c>
       <c r="I76" t="n">
-        <v>235.51</v>
+        <v>230.38</v>
       </c>
       <c r="J76" t="n">
-        <v>2729219</v>
+        <v>2834002</v>
       </c>
       <c r="K76" t="n">
-        <v>2729217</v>
+        <v>2834002</v>
       </c>
       <c r="L76" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>2729217</v>
+        <v>2834002</v>
       </c>
       <c r="N76" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -5370,34 +5370,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4743361</v>
+        <v>4750578</v>
       </c>
       <c r="F77" t="n">
-        <v>4684877</v>
+        <v>4660952</v>
       </c>
       <c r="G77" t="n">
-        <v>-1.23</v>
+        <v>-1.89</v>
       </c>
       <c r="H77" t="n">
-        <v>16102591</v>
+        <v>15775550</v>
       </c>
       <c r="I77" t="n">
-        <v>239.48</v>
+        <v>232.08</v>
       </c>
       <c r="J77" t="n">
-        <v>-2687105</v>
+        <v>-2792658</v>
       </c>
       <c r="K77" t="n">
-        <v>-2687107</v>
+        <v>-2792658</v>
       </c>
       <c r="L77" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-2687107</v>
+        <v>-2792658</v>
       </c>
       <c r="N77" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -5422,31 +5422,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>386689</v>
+        <v>362208</v>
       </c>
       <c r="F78" t="n">
-        <v>368266</v>
+        <v>342649</v>
       </c>
       <c r="G78" t="n">
-        <v>-4.76</v>
+        <v>-5.4</v>
       </c>
       <c r="H78" t="n">
-        <v>11785980</v>
+        <v>11457247</v>
       </c>
       <c r="I78" t="n">
-        <v>2947.92</v>
+        <v>3063.17</v>
       </c>
       <c r="J78" t="n">
-        <v>-2884535</v>
+        <v>-2432342</v>
       </c>
       <c r="K78" t="n">
-        <v>-2884535</v>
+        <v>-2432342</v>
       </c>
       <c r="L78" t="n">
         <v>-0</v>
       </c>
       <c r="M78" t="n">
-        <v>-2884535</v>
+        <v>-2432342</v>
       </c>
       <c r="N78" t="n">
         <v>-0</v>
@@ -5474,31 +5474,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>514453</v>
+        <v>-453192</v>
       </c>
       <c r="F79" t="n">
-        <v>378360</v>
+        <v>-453192</v>
       </c>
       <c r="G79" t="n">
-        <v>-26.45</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-3114829</v>
+        <v>-3550880</v>
       </c>
       <c r="I79" t="n">
-        <v>-705.46</v>
+        <v>-683.53</v>
       </c>
       <c r="J79" t="n">
-        <v>6585076</v>
+        <v>6420267</v>
       </c>
       <c r="K79" t="n">
-        <v>6585076</v>
+        <v>6420267</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>6585076</v>
+        <v>6420267</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
@@ -5526,34 +5526,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5744814</v>
+        <v>5734281</v>
       </c>
       <c r="F80" t="n">
-        <v>5782301</v>
+        <v>5734281</v>
       </c>
       <c r="G80" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>2289112</v>
+        <v>2636593</v>
       </c>
       <c r="I80" t="n">
-        <v>-60.15</v>
+        <v>-54.02</v>
       </c>
       <c r="J80" t="n">
-        <v>-4581281</v>
+        <v>-4495486</v>
       </c>
       <c r="K80" t="n">
-        <v>-4581281</v>
+        <v>-4492938</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M80" t="n">
-        <v>-4581281</v>
+        <v>-4492938</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="81">
@@ -5578,31 +5578,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>14308649</v>
+        <v>14281976</v>
       </c>
       <c r="F81" t="n">
-        <v>14401984</v>
+        <v>14281976</v>
       </c>
       <c r="G81" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>10908795</v>
+        <v>11184288</v>
       </c>
       <c r="I81" t="n">
-        <v>-23.76</v>
+        <v>-21.69</v>
       </c>
       <c r="J81" t="n">
-        <v>-11472178</v>
+        <v>-11262652</v>
       </c>
       <c r="K81" t="n">
-        <v>-11472178</v>
+        <v>-11262652</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-11472178</v>
+        <v>-11262652</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
@@ -5630,31 +5630,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>-14487728</v>
+        <v>-14460445</v>
       </c>
       <c r="F82" t="n">
-        <v>-14582330</v>
+        <v>-14460445</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.65</v>
+        <v>-0</v>
       </c>
       <c r="H82" t="n">
-        <v>-18075519</v>
+        <v>-17558133</v>
       </c>
       <c r="I82" t="n">
-        <v>-24.76</v>
+        <v>-21.42</v>
       </c>
       <c r="J82" t="n">
-        <v>11312932</v>
+        <v>11114971</v>
       </c>
       <c r="K82" t="n">
-        <v>11312932</v>
+        <v>11114971</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>11312932</v>
+        <v>11114971</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
@@ -5682,34 +5682,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5301013</v>
+        <v>6144804</v>
       </c>
       <c r="F83" t="n">
-        <v>5459912</v>
+        <v>6144804</v>
       </c>
       <c r="G83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>1966723</v>
+        <v>3047116</v>
       </c>
       <c r="I83" t="n">
-        <v>-62.9</v>
+        <v>-50.41</v>
       </c>
       <c r="J83" t="n">
-        <v>-10535455</v>
+        <v>-10297762</v>
       </c>
       <c r="K83" t="n">
-        <v>-10535455</v>
+        <v>-10297762</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M83" t="n">
-        <v>-10535455</v>
+        <v>-10297762</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="84">
@@ -5734,34 +5734,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>-5330591</v>
+        <v>-6186706</v>
       </c>
       <c r="F84" t="n">
-        <v>-5490393</v>
+        <v>-6186706</v>
       </c>
       <c r="G84" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>-8983582</v>
+        <v>-9284394</v>
       </c>
       <c r="I84" t="n">
-        <v>-68.53</v>
+        <v>-50.07</v>
       </c>
       <c r="J84" t="n">
-        <v>10412130</v>
+        <v>10183894</v>
       </c>
       <c r="K84" t="n">
-        <v>10412130</v>
+        <v>10183894</v>
       </c>
       <c r="L84" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>10412130</v>
+        <v>10183894</v>
       </c>
       <c r="N84" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5786,31 +5786,31 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>-2274156</v>
+        <v>-1379950</v>
       </c>
       <c r="F85" t="n">
-        <v>-2159399</v>
+        <v>-1379950</v>
       </c>
       <c r="G85" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>-5652588</v>
+        <v>-4477638</v>
       </c>
       <c r="I85" t="n">
-        <v>-148.56</v>
+        <v>-224.48</v>
       </c>
       <c r="J85" t="n">
-        <v>-4721182</v>
+        <v>-4585124</v>
       </c>
       <c r="K85" t="n">
-        <v>-4721182</v>
+        <v>-4585124</v>
       </c>
       <c r="L85" t="n">
         <v>-0</v>
       </c>
       <c r="M85" t="n">
-        <v>-4721182</v>
+        <v>-4585124</v>
       </c>
       <c r="N85" t="n">
         <v>-0</v>
@@ -6827,13 +6827,13 @@
         <v>-64310528</v>
       </c>
       <c r="L108" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
         <v>-64310528</v>
       </c>
       <c r="N108" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -7098,31 +7098,31 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="F114" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>68115</v>
+        <v>31624</v>
       </c>
       <c r="K114" t="n">
-        <v>68115</v>
+        <v>31624</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>68115</v>
+        <v>31624</v>
       </c>
       <c r="N114" t="n">
         <v>0</v>
@@ -7150,31 +7150,31 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="F115" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>26623</v>
+        <v>-9868</v>
       </c>
       <c r="K115" t="n">
-        <v>26623</v>
+        <v>-9868</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>26623</v>
+        <v>-9868</v>
       </c>
       <c r="N115" t="n">
         <v>0</v>
@@ -7202,34 +7202,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="F116" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>10199</v>
+        <v>-26292</v>
       </c>
       <c r="K116" t="n">
-        <v>10199</v>
+        <v>-26292</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M116" t="n">
-        <v>10199</v>
+        <v>-26292</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="117">
@@ -7254,31 +7254,31 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="F117" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>64951</v>
+        <v>28460</v>
       </c>
       <c r="K117" t="n">
-        <v>64951</v>
+        <v>28460</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>64951</v>
+        <v>28460</v>
       </c>
       <c r="N117" t="n">
         <v>0</v>
@@ -7306,31 +7306,31 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="F118" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>-13</v>
+        <v>-36504</v>
       </c>
       <c r="K118" t="n">
-        <v>-13</v>
+        <v>-36504</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>-13</v>
+        <v>-36504</v>
       </c>
       <c r="N118" t="n">
         <v>0</v>
@@ -7358,31 +7358,31 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="F119" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>75795</v>
+        <v>39304</v>
       </c>
       <c r="K119" t="n">
-        <v>75795</v>
+        <v>39304</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>75795</v>
+        <v>39304</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
@@ -7410,31 +7410,31 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="F120" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>37591</v>
+        <v>1096</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>12771</v>
+        <v>-23720</v>
       </c>
       <c r="K120" t="n">
-        <v>12771</v>
+        <v>-23720</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>12771</v>
+        <v>-23720</v>
       </c>
       <c r="N120" t="n">
         <v>0</v>
@@ -7462,34 +7462,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>-23088081</v>
+        <v>-23057477</v>
       </c>
       <c r="F121" t="n">
-        <v>-23088081</v>
+        <v>-23057477</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>-29262208</v>
+        <v>-29094979</v>
       </c>
       <c r="I121" t="n">
-        <v>-26.74</v>
+        <v>-26.18</v>
       </c>
       <c r="J121" t="n">
-        <v>8907461</v>
+        <v>8924662</v>
       </c>
       <c r="K121" t="n">
-        <v>8974430</v>
+        <v>8992683</v>
       </c>
       <c r="L121" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="M121" t="n">
-        <v>8974430</v>
+        <v>8992683</v>
       </c>
       <c r="N121" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="122">
@@ -7514,31 +7514,31 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>11576718</v>
+        <v>11571024</v>
       </c>
       <c r="F122" t="n">
-        <v>11576718</v>
+        <v>11571024</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>5402591</v>
+        <v>5533522</v>
       </c>
       <c r="I122" t="n">
-        <v>-53.33</v>
+        <v>-52.18</v>
       </c>
       <c r="J122" t="n">
-        <v>-5345112</v>
+        <v>-5347843</v>
       </c>
       <c r="K122" t="n">
-        <v>-5372132</v>
+        <v>-5375288</v>
       </c>
       <c r="L122" t="n">
         <v>-0.51</v>
       </c>
       <c r="M122" t="n">
-        <v>-5372132</v>
+        <v>-5375288</v>
       </c>
       <c r="N122" t="n">
         <v>-0.51</v>
@@ -7566,34 +7566,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>28891896</v>
+        <v>28877562</v>
       </c>
       <c r="F123" t="n">
-        <v>28891896</v>
+        <v>28877562</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>22717769</v>
+        <v>22840060</v>
       </c>
       <c r="I123" t="n">
-        <v>-21.37</v>
+        <v>-20.91</v>
       </c>
       <c r="J123" t="n">
-        <v>-13397085</v>
+        <v>-13403840</v>
       </c>
       <c r="K123" t="n">
-        <v>-13464678</v>
+        <v>-13472495</v>
       </c>
       <c r="L123" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
       <c r="M123" t="n">
-        <v>-13464678</v>
+        <v>-13472495</v>
       </c>
       <c r="N123" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="124">
@@ -7618,34 +7618,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>-29059060</v>
+        <v>-29045040</v>
       </c>
       <c r="F124" t="n">
-        <v>-29059060</v>
+        <v>-29045040</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>-35233187</v>
+        <v>-35082542</v>
       </c>
       <c r="I124" t="n">
-        <v>-21.25</v>
+        <v>-20.79</v>
       </c>
       <c r="J124" t="n">
-        <v>13283388</v>
+        <v>13290402</v>
       </c>
       <c r="K124" t="n">
-        <v>13350840</v>
+        <v>13358914</v>
       </c>
       <c r="L124" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="M124" t="n">
-        <v>13350840</v>
+        <v>13358914</v>
       </c>
       <c r="N124" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="125">
@@ -7670,34 +7670,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>32074457</v>
+        <v>32041452</v>
       </c>
       <c r="F125" t="n">
-        <v>32074457</v>
+        <v>32041452</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>25900330</v>
+        <v>26003950</v>
       </c>
       <c r="I125" t="n">
-        <v>-19.25</v>
+        <v>-18.84</v>
       </c>
       <c r="J125" t="n">
-        <v>-13368738</v>
+        <v>-13386891</v>
       </c>
       <c r="K125" t="n">
-        <v>-13455729</v>
+        <v>-13475249</v>
       </c>
       <c r="L125" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="M125" t="n">
-        <v>-13455729</v>
+        <v>-13475249</v>
       </c>
       <c r="N125" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="126">
@@ -7722,34 +7722,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>-32266121</v>
+        <v>-32233270</v>
       </c>
       <c r="F126" t="n">
-        <v>-32266121</v>
+        <v>-32233270</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>-38440248</v>
+        <v>-38270772</v>
       </c>
       <c r="I126" t="n">
-        <v>-19.14</v>
+        <v>-18.73</v>
       </c>
       <c r="J126" t="n">
-        <v>13263749</v>
+        <v>13281875</v>
       </c>
       <c r="K126" t="n">
-        <v>13350507</v>
+        <v>13369996</v>
       </c>
       <c r="L126" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="M126" t="n">
-        <v>13350507</v>
+        <v>13369996</v>
       </c>
       <c r="N126" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="127">
@@ -7774,34 +7774,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>17656942</v>
+        <v>17630245</v>
       </c>
       <c r="F127" t="n">
-        <v>17656942</v>
+        <v>17630245</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>11482815</v>
+        <v>11592743</v>
       </c>
       <c r="I127" t="n">
-        <v>-34.97</v>
+        <v>-34.25</v>
       </c>
       <c r="J127" t="n">
-        <v>-6600313</v>
+        <v>-6615411</v>
       </c>
       <c r="K127" t="n">
-        <v>-6653872</v>
+        <v>-6669811</v>
       </c>
       <c r="L127" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.82</v>
       </c>
       <c r="M127" t="n">
-        <v>-6653872</v>
+        <v>-6669811</v>
       </c>
       <c r="N127" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="128">
@@ -7826,31 +7826,31 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4763387</v>
+        <v>4759372</v>
       </c>
       <c r="F128" t="n">
-        <v>4763387</v>
+        <v>4759372</v>
       </c>
       <c r="G128" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>8199718</v>
+        <v>8169056</v>
       </c>
       <c r="I128" t="n">
-        <v>72.14</v>
+        <v>71.64</v>
       </c>
       <c r="J128" t="n">
-        <v>-245440</v>
+        <v>-274469</v>
       </c>
       <c r="K128" t="n">
-        <v>-245440</v>
+        <v>-274469</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>-245440</v>
+        <v>-274469</v>
       </c>
       <c r="N128" t="n">
         <v>0</v>
@@ -7878,31 +7878,31 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>-1903369</v>
+        <v>-1891964</v>
       </c>
       <c r="F129" t="n">
-        <v>-1903369</v>
+        <v>-1891964</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>1532962</v>
+        <v>1517720</v>
       </c>
       <c r="I129" t="n">
-        <v>180.54</v>
+        <v>180.22</v>
       </c>
       <c r="J129" t="n">
-        <v>98394</v>
+        <v>110039</v>
       </c>
       <c r="K129" t="n">
-        <v>98394</v>
+        <v>110039</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>98394</v>
+        <v>110039</v>
       </c>
       <c r="N129" t="n">
         <v>0</v>
@@ -7930,31 +7930,31 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>-4756570</v>
+        <v>-4727906</v>
       </c>
       <c r="F130" t="n">
-        <v>-4756570</v>
+        <v>-4727906</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>-1320239</v>
+        <v>-1318222</v>
       </c>
       <c r="I130" t="n">
-        <v>72.23999999999999</v>
+        <v>72.12</v>
       </c>
       <c r="J130" t="n">
-        <v>246066</v>
+        <v>275312</v>
       </c>
       <c r="K130" t="n">
-        <v>246066</v>
+        <v>275312</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>246066</v>
+        <v>275312</v>
       </c>
       <c r="N130" t="n">
         <v>0</v>
@@ -7982,31 +7982,31 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4762308</v>
+        <v>4734365</v>
       </c>
       <c r="F131" t="n">
-        <v>4762308</v>
+        <v>4734365</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>8198639</v>
+        <v>8144049</v>
       </c>
       <c r="I131" t="n">
-        <v>72.16</v>
+        <v>72.02</v>
       </c>
       <c r="J131" t="n">
-        <v>-245695</v>
+        <v>-274955</v>
       </c>
       <c r="K131" t="n">
-        <v>-245695</v>
+        <v>-274955</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>-245695</v>
+        <v>-274955</v>
       </c>
       <c r="N131" t="n">
         <v>0</v>
@@ -8034,31 +8034,31 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>-6146385</v>
+        <v>-6125965</v>
       </c>
       <c r="F132" t="n">
-        <v>-6146385</v>
+        <v>-6125965</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>-2710054</v>
+        <v>-2716281</v>
       </c>
       <c r="I132" t="n">
-        <v>55.91</v>
+        <v>55.66</v>
       </c>
       <c r="J132" t="n">
-        <v>317864</v>
+        <v>355536</v>
       </c>
       <c r="K132" t="n">
-        <v>317864</v>
+        <v>355536</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>317864</v>
+        <v>355536</v>
       </c>
       <c r="N132" t="n">
         <v>0</v>
@@ -8086,31 +8086,31 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6159720</v>
+        <v>6145044</v>
       </c>
       <c r="F133" t="n">
-        <v>6159720</v>
+        <v>6145044</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>9596051</v>
+        <v>9554728</v>
       </c>
       <c r="I133" t="n">
-        <v>55.79</v>
+        <v>55.49</v>
       </c>
       <c r="J133" t="n">
-        <v>-317395</v>
+        <v>-354980</v>
       </c>
       <c r="K133" t="n">
-        <v>-317394</v>
+        <v>-354980</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>-317394</v>
+        <v>-354980</v>
       </c>
       <c r="N133" t="n">
         <v>0</v>
@@ -8138,31 +8138,31 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>-3802827</v>
+        <v>-3802093</v>
       </c>
       <c r="F134" t="n">
-        <v>-3802827</v>
+        <v>-3802093</v>
       </c>
       <c r="G134" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>-366496</v>
+        <v>-392409</v>
       </c>
       <c r="I134" t="n">
-        <v>90.36</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="J134" t="n">
-        <v>196389</v>
+        <v>219525</v>
       </c>
       <c r="K134" t="n">
-        <v>196389</v>
+        <v>219525</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>196389</v>
+        <v>219525</v>
       </c>
       <c r="N134" t="n">
         <v>0</v>
@@ -8190,34 +8190,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>-9908943</v>
+        <v>-9513107</v>
       </c>
       <c r="F135" t="n">
-        <v>-9908943</v>
+        <v>-9513107</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>-16491946</v>
+        <v>-16385265</v>
       </c>
       <c r="I135" t="n">
-        <v>-66.43000000000001</v>
+        <v>-72.23999999999999</v>
       </c>
       <c r="J135" t="n">
-        <v>351243</v>
+        <v>505782</v>
       </c>
       <c r="K135" t="n">
-        <v>351243</v>
+        <v>505782</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M135" t="n">
-        <v>351243</v>
+        <v>505782</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="136">
@@ -8242,31 +8242,31 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3861466</v>
+        <v>3800933</v>
       </c>
       <c r="F136" t="n">
-        <v>3861466</v>
+        <v>3800933</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>-2721537</v>
+        <v>-3071225</v>
       </c>
       <c r="I136" t="n">
-        <v>-170.48</v>
+        <v>-180.8</v>
       </c>
       <c r="J136" t="n">
-        <v>-140368</v>
+        <v>-202748</v>
       </c>
       <c r="K136" t="n">
-        <v>-140368</v>
+        <v>-202748</v>
       </c>
       <c r="L136" t="n">
         <v>-0</v>
       </c>
       <c r="M136" t="n">
-        <v>-140368</v>
+        <v>-202748</v>
       </c>
       <c r="N136" t="n">
         <v>-0</v>
@@ -8294,31 +8294,31 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>9650616</v>
+        <v>9498436</v>
       </c>
       <c r="F137" t="n">
-        <v>9650616</v>
+        <v>9498436</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>3067613</v>
+        <v>2626278</v>
       </c>
       <c r="I137" t="n">
-        <v>-68.20999999999999</v>
+        <v>-72.34999999999999</v>
       </c>
       <c r="J137" t="n">
-        <v>-351054</v>
+        <v>-507118</v>
       </c>
       <c r="K137" t="n">
-        <v>-351054</v>
+        <v>-507118</v>
       </c>
       <c r="L137" t="n">
         <v>-0</v>
       </c>
       <c r="M137" t="n">
-        <v>-351054</v>
+        <v>-507118</v>
       </c>
       <c r="N137" t="n">
         <v>-0</v>
@@ -8346,34 +8346,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>-9658983</v>
+        <v>-9510103</v>
       </c>
       <c r="F138" t="n">
-        <v>-9658983</v>
+        <v>-9510103</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>-16241986</v>
+        <v>-16382261</v>
       </c>
       <c r="I138" t="n">
-        <v>-68.15000000000001</v>
+        <v>-72.26000000000001</v>
       </c>
       <c r="J138" t="n">
-        <v>350638</v>
+        <v>506410</v>
       </c>
       <c r="K138" t="n">
-        <v>350638</v>
+        <v>506410</v>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M138" t="n">
-        <v>350638</v>
+        <v>506410</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="139">
@@ -8398,34 +8398,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>12644113</v>
+        <v>12274286</v>
       </c>
       <c r="F139" t="n">
-        <v>12644113</v>
+        <v>12274286</v>
       </c>
       <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>5402128</v>
+      </c>
+      <c r="I139" t="n">
+        <v>-55.99</v>
+      </c>
+      <c r="J139" t="n">
+        <v>-655035</v>
+      </c>
+      <c r="K139" t="n">
+        <v>-655035</v>
+      </c>
+      <c r="L139" t="n">
         <v>-0</v>
       </c>
-      <c r="H139" t="n">
-        <v>6061110</v>
-      </c>
-      <c r="I139" t="n">
-        <v>-52.06</v>
-      </c>
-      <c r="J139" t="n">
-        <v>-454159</v>
-      </c>
-      <c r="K139" t="n">
-        <v>-454159</v>
-      </c>
-      <c r="L139" t="n">
-        <v>0</v>
-      </c>
       <c r="M139" t="n">
-        <v>-454159</v>
+        <v>-655035</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="140">
@@ -8450,31 +8450,31 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>-12713682</v>
+        <v>-12301507</v>
       </c>
       <c r="F140" t="n">
-        <v>-12713682</v>
+        <v>-12301507</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>-19296685</v>
+        <v>-19173665</v>
       </c>
       <c r="I140" t="n">
-        <v>-51.78</v>
+        <v>-55.86</v>
       </c>
       <c r="J140" t="n">
-        <v>453830</v>
+        <v>654079</v>
       </c>
       <c r="K140" t="n">
-        <v>453830</v>
+        <v>654079</v>
       </c>
       <c r="L140" t="n">
         <v>-0</v>
       </c>
       <c r="M140" t="n">
-        <v>453830</v>
+        <v>654079</v>
       </c>
       <c r="N140" t="n">
         <v>-0</v>
@@ -8502,31 +8502,31 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>7944332</v>
+        <v>7594729</v>
       </c>
       <c r="F141" t="n">
-        <v>7944332</v>
+        <v>7594729</v>
       </c>
       <c r="G141" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>1361329</v>
+        <v>722571</v>
       </c>
       <c r="I141" t="n">
-        <v>-82.86</v>
+        <v>-90.48999999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>-281077</v>
+        <v>-404630</v>
       </c>
       <c r="K141" t="n">
-        <v>-281078</v>
+        <v>-404630</v>
       </c>
       <c r="L141" t="n">
         <v>-0</v>
       </c>
       <c r="M141" t="n">
-        <v>-281078</v>
+        <v>-404630</v>
       </c>
       <c r="N141" t="n">
         <v>-0</v>
@@ -8627,13 +8627,13 @@
         <v>-8143731</v>
       </c>
       <c r="L143" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
         <v>-8143731</v>
       </c>
       <c r="N143" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -8872,13 +8872,13 @@
         <v>5491903</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H148" t="n">
         <v>5491903</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J148" t="n">
         <v>6207952</v>
@@ -8954,13 +8954,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.7967</v>
+        <v>2.8046</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7967</v>
+        <v>2.8046</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
         <v>1.6147</v>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>528545794</v>
+        <v>537319930</v>
       </c>
       <c r="E2" t="n">
-        <v>528545794</v>
+        <v>537319930</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -9103,10 +9103,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2094998347</v>
+        <v>2171503039</v>
       </c>
       <c r="E3" t="n">
-        <v>2094998347</v>
+        <v>2171503039</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -9141,22 +9141,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38693708</v>
+        <v>33204891</v>
       </c>
       <c r="E4" t="n">
-        <v>38440086</v>
+        <v>33138954</v>
       </c>
       <c r="F4" t="n">
-        <v>3.22</v>
+        <v>2.77</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.66</v>
+        <v>-0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.021</v>
+        <v>-0.005</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -9187,26 +9187,26 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-121961997</v>
+        <v>-129744181</v>
       </c>
       <c r="E5" t="n">
-        <v>-125254792</v>
+        <v>-129675664</v>
       </c>
       <c r="F5" t="n">
-        <v>-10.16</v>
+        <v>-10.81</v>
       </c>
       <c r="G5" t="n">
-        <v>-10.44</v>
+        <v>-10.81</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.7</v>
+        <v>0.05</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.274</v>
+        <v>0.006</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -9233,22 +9233,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-42208099</v>
+        <v>-36949559</v>
       </c>
       <c r="E6" t="n">
-        <v>-41948327</v>
+        <v>-36872218</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.52</v>
+        <v>-3.08</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.5</v>
+        <v>-3.07</v>
       </c>
       <c r="H6" t="n">
-        <v>0.62</v>
+        <v>0.21</v>
       </c>
       <c r="I6" t="n">
-        <v>0.022</v>
+        <v>0.006</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -9279,26 +9279,26 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>134318193</v>
+        <v>141408971</v>
       </c>
       <c r="E7" t="n">
-        <v>137897907</v>
+        <v>141340319</v>
       </c>
       <c r="F7" t="n">
-        <v>11.19</v>
+        <v>11.78</v>
       </c>
       <c r="G7" t="n">
-        <v>11.49</v>
+        <v>11.78</v>
       </c>
       <c r="H7" t="n">
-        <v>2.67</v>
+        <v>-0.05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.298</v>
+        <v>-0.006</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -9325,22 +9325,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>23719591</v>
+        <v>24037177</v>
       </c>
       <c r="E8" t="n">
-        <v>23902649</v>
+        <v>24164877</v>
       </c>
       <c r="F8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="H8" t="n">
-        <v>0.77</v>
+        <v>0.53</v>
       </c>
       <c r="I8" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -9371,26 +9371,26 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-45472221</v>
+        <v>-46407742</v>
       </c>
       <c r="E9" t="n">
-        <v>-46967609</v>
+        <v>-46462133</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.79</v>
+        <v>-3.87</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.91</v>
+        <v>-3.87</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.29</v>
+        <v>-0.12</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.125</v>
+        <v>-0.005</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -9417,22 +9417,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-23887035</v>
+        <v>-25108558</v>
       </c>
       <c r="E10" t="n">
-        <v>-24112736</v>
+        <v>-25250102</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.99</v>
+        <v>-2.09</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.01</v>
+        <v>-2.1</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.019</v>
+        <v>-0.012</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -9463,26 +9463,26 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>34903233</v>
+        <v>34556911</v>
       </c>
       <c r="E11" t="n">
-        <v>36118876</v>
+        <v>34624930</v>
       </c>
       <c r="F11" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="G11" t="n">
-        <v>3.01</v>
+        <v>2.89</v>
       </c>
       <c r="H11" t="n">
-        <v>3.48</v>
+        <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.101</v>
+        <v>0.006</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -9509,22 +9509,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-5286286</v>
+        <v>-8558612</v>
       </c>
       <c r="E12" t="n">
-        <v>-5590832</v>
+        <v>-8712696</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.44</v>
+        <v>-0.71</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.47</v>
+        <v>-0.73</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.76</v>
+        <v>-1.8</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.025</v>
+        <v>-0.013</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -9555,26 +9555,26 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-21011285</v>
+        <v>-24200463</v>
       </c>
       <c r="E13" t="n">
-        <v>-21322875</v>
+        <v>-24112338</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.75</v>
+        <v>-2.02</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.78</v>
+        <v>-2.01</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.48</v>
+        <v>0.36</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.026</v>
+        <v>0.007</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -9601,22 +9601,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1547548</v>
+        <v>4684805</v>
       </c>
       <c r="E14" t="n">
-        <v>1857391</v>
+        <v>4845904</v>
       </c>
       <c r="F14" t="n">
-        <v>0.13</v>
+        <v>0.39</v>
       </c>
       <c r="G14" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="H14" t="n">
-        <v>20.02</v>
+        <v>3.44</v>
       </c>
       <c r="I14" t="n">
-        <v>0.026</v>
+        <v>0.013</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -9647,26 +9647,26 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>21478251</v>
+        <v>24623321</v>
       </c>
       <c r="E15" t="n">
-        <v>21793286</v>
+        <v>24534967</v>
       </c>
       <c r="F15" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="G15" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="H15" t="n">
-        <v>1.47</v>
+        <v>-0.36</v>
       </c>
       <c r="I15" t="n">
-        <v>0.026</v>
+        <v>-0.007</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -9693,22 +9693,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-17917160</v>
+        <v>-15844724</v>
       </c>
       <c r="E16" t="n">
-        <v>-17811471</v>
+        <v>-15812299</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.49</v>
+        <v>-1.32</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.48</v>
+        <v>-1.32</v>
       </c>
       <c r="H16" t="n">
-        <v>0.59</v>
+        <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -9739,26 +9739,26 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>52242634</v>
+        <v>55139885</v>
       </c>
       <c r="E17" t="n">
-        <v>53627928</v>
+        <v>55112114</v>
       </c>
       <c r="F17" t="n">
-        <v>4.35</v>
+        <v>4.59</v>
       </c>
       <c r="G17" t="n">
-        <v>4.47</v>
+        <v>4.59</v>
       </c>
       <c r="H17" t="n">
-        <v>2.65</v>
+        <v>-0.05</v>
       </c>
       <c r="I17" t="n">
-        <v>0.115</v>
+        <v>-0.002</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -9793,7 +9793,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
@@ -9940,20 +9940,20 @@
         <v>1500000000</v>
       </c>
       <c r="E2" t="n">
-        <v>13.7578</v>
+        <v>13.7486</v>
       </c>
       <c r="F2" t="n">
-        <v>13.7578</v>
+        <v>13.7486</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.19741</v>
+        <v>1.196192</v>
       </c>
       <c r="J2" t="n">
-        <v>1.19741</v>
+        <v>1.196192</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -9982,20 +9982,20 @@
         <v>900000000</v>
       </c>
       <c r="E3" t="n">
-        <v>11.5485</v>
+        <v>11.5493</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5485</v>
+        <v>11.5493</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.208419</v>
+        <v>1.207404</v>
       </c>
       <c r="J3" t="n">
-        <v>1.208419</v>
+        <v>1.207404</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -10024,20 +10024,20 @@
         <v>1000000000</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3282</v>
+        <v>6.3072</v>
       </c>
       <c r="F4" t="n">
-        <v>6.3282</v>
+        <v>6.3072</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1.044642</v>
+        <v>1.043021</v>
       </c>
       <c r="J4" t="n">
-        <v>1.044642</v>
+        <v>1.043021</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -10066,20 +10066,20 @@
         <v>2800000000</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7529</v>
+        <v>5.7584</v>
       </c>
       <c r="F5" t="n">
-        <v>5.7529</v>
+        <v>5.7584</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1.071996</v>
+        <v>1.072311</v>
       </c>
       <c r="J5" t="n">
-        <v>1.071996</v>
+        <v>1.072311</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -10108,20 +10108,20 @@
         <v>600000000</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3336</v>
+        <v>5.2727</v>
       </c>
       <c r="F6" t="n">
-        <v>5.3336</v>
+        <v>5.2727</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1.045279</v>
+        <v>1.040992</v>
       </c>
       <c r="J6" t="n">
-        <v>1.045279</v>
+        <v>1.040992</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -10150,22 +10150,24 @@
         <v>1500000000</v>
       </c>
       <c r="E7" t="n">
-        <v>4.8228</v>
+        <v>5.2575</v>
       </c>
       <c r="F7" t="n">
-        <v>4.8228</v>
+        <v>5.2575</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.994186</v>
+        <v>1.047301</v>
       </c>
       <c r="J7" t="n">
-        <v>0.994186</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>1.047301</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" t="b">
         <v>1</v>
       </c>
@@ -10230,20 +10232,20 @@
         <v>1100000000</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9212</v>
+        <v>4.0867</v>
       </c>
       <c r="F9" t="n">
-        <v>3.9212</v>
+        <v>4.0867</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.008482</v>
+        <v>1.009804</v>
       </c>
       <c r="J9" t="n">
-        <v>1.008482</v>
+        <v>1.009804</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -10272,10 +10274,10 @@
         <v>200000000</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7657</v>
+        <v>3.7523</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7657</v>
+        <v>3.7523</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="b">
@@ -10554,20 +10556,20 @@
         <v>400000000</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0094</v>
+        <v>-0.0003</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0094</v>
+        <v>-0.0003</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>-1</v>
+        <v>-0.999909</v>
       </c>
       <c r="J17" t="n">
-        <v>-1</v>
+        <v>-0.999909</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="b">
@@ -10634,20 +10636,20 @@
         <v>2100000000</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3306</v>
+        <v>-3.3301</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.3306</v>
+        <v>-3.3301</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.983425</v>
+        <v>-0.983182</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.983425</v>
+        <v>-0.983182</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="b">
@@ -10674,20 +10676,20 @@
         <v>400000000</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6932</v>
+        <v>-3.7655</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.6932</v>
+        <v>-3.7655</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.000007</v>
+        <v>-1.000005</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.000007</v>
+        <v>-1.000005</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -10756,20 +10758,20 @@
         <v>1200000000</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0073</v>
+        <v>-3.903</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.0073</v>
+        <v>-3.903</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.006866</v>
+        <v>-1.006132</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.006866</v>
+        <v>-1.006132</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>

--- a/optimize_prep/output/approx_accuracy_report.xlsx
+++ b/optimize_prep/output/approx_accuracy_report.xlsx
@@ -598,34 +598,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>63071710</v>
+        <v>66433964</v>
       </c>
       <c r="E4" t="n">
-        <v>63071710</v>
+        <v>66433964</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>56481516</v>
+        <v>57254522</v>
       </c>
       <c r="H4" t="n">
-        <v>-10.45</v>
+        <v>-13.82</v>
       </c>
       <c r="I4" t="n">
-        <v>6590194</v>
+        <v>9179442</v>
       </c>
       <c r="J4" t="n">
-        <v>1043020538</v>
+        <v>1043146798</v>
       </c>
       <c r="K4" t="n">
-        <v>1043020538</v>
+        <v>1043146798</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -645,34 +645,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>161236335</v>
+        <v>164885641</v>
       </c>
       <c r="E5" t="n">
-        <v>161236335</v>
+        <v>164885641</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>107791520</v>
+        <v>107746730</v>
       </c>
       <c r="H5" t="n">
-        <v>-33.15</v>
+        <v>-34.65</v>
       </c>
       <c r="I5" t="n">
-        <v>53444815</v>
+        <v>57138911</v>
       </c>
       <c r="J5" t="n">
-        <v>3002470635</v>
+        <v>3002180524</v>
       </c>
       <c r="K5" t="n">
-        <v>3002470635</v>
+        <v>3002180524</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -692,34 +692,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>103943612</v>
+        <v>92643144</v>
       </c>
       <c r="E6" t="n">
-        <v>103943612</v>
+        <v>92643144</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>93659666</v>
+        <v>85619425</v>
       </c>
       <c r="H6" t="n">
-        <v>-9.890000000000001</v>
+        <v>-7.58</v>
       </c>
       <c r="I6" t="n">
-        <v>10283946</v>
+        <v>7023719</v>
       </c>
       <c r="J6" t="n">
-        <v>1086663745</v>
+        <v>1060091176</v>
       </c>
       <c r="K6" t="n">
-        <v>1086663745</v>
+        <v>1060091176</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -739,28 +739,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>206228546</v>
+        <v>154477297</v>
       </c>
       <c r="E7" t="n">
-        <v>206228546</v>
+        <v>154477297</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>183866388</v>
+        <v>80202054</v>
       </c>
       <c r="H7" t="n">
-        <v>-10.84</v>
+        <v>-48.08</v>
       </c>
       <c r="I7" t="n">
-        <v>22362158</v>
+        <v>74275242</v>
       </c>
       <c r="J7" t="n">
-        <v>1794288389</v>
+        <v>1676720105</v>
       </c>
       <c r="K7" t="n">
-        <v>1794288389</v>
+        <v>1676720105</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -786,34 +786,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78861997</v>
+        <v>67658549</v>
       </c>
       <c r="E8" t="n">
-        <v>78861997</v>
+        <v>67658549</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G8" t="n">
-        <v>78002396</v>
+        <v>63444985</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.09</v>
+        <v>-6.23</v>
       </c>
       <c r="I8" t="n">
-        <v>859600</v>
+        <v>4213564</v>
       </c>
       <c r="J8" t="n">
-        <v>1570951150</v>
+        <v>1479763824</v>
       </c>
       <c r="K8" t="n">
-        <v>1570951150</v>
+        <v>1479763824</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -833,34 +833,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>44953916</v>
+        <v>43924306</v>
       </c>
       <c r="E9" t="n">
-        <v>44953916</v>
+        <v>43924306</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>42324254</v>
+        <v>42636355</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.85</v>
+        <v>-2.93</v>
       </c>
       <c r="I9" t="n">
-        <v>2629662</v>
+        <v>1287951</v>
       </c>
       <c r="J9" t="n">
-        <v>1110784884</v>
+        <v>1106594600</v>
       </c>
       <c r="K9" t="n">
-        <v>1110784884</v>
+        <v>1106594600</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -880,28 +880,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6016986</v>
+        <v>5980000</v>
       </c>
       <c r="E10" t="n">
-        <v>6016986</v>
+        <v>5980000</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7479859</v>
+        <v>5979887</v>
       </c>
       <c r="H10" t="n">
-        <v>24.31</v>
+        <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-1462873</v>
+        <v>113</v>
       </c>
       <c r="J10" t="n">
-        <v>199999668</v>
+        <v>199962716</v>
       </c>
       <c r="K10" t="n">
-        <v>199999668</v>
+        <v>199962716</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -968,28 +968,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31636106</v>
+        <v>27774559</v>
       </c>
       <c r="E12" t="n">
-        <v>31636106</v>
+        <v>27774559</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>20521508</v>
+        <v>19616512</v>
       </c>
       <c r="H12" t="n">
-        <v>-35.13</v>
+        <v>-29.37</v>
       </c>
       <c r="I12" t="n">
-        <v>11114598</v>
+        <v>8158048</v>
       </c>
       <c r="J12" t="n">
-        <v>624595350</v>
+        <v>611831340</v>
       </c>
       <c r="K12" t="n">
-        <v>624595350</v>
+        <v>611831340</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1015,28 +1015,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-46835551</v>
+        <v>-47487862</v>
       </c>
       <c r="E13" t="n">
-        <v>-46835551</v>
+        <v>-47487862</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-43737863</v>
+        <v>-45552669</v>
       </c>
       <c r="H13" t="n">
-        <v>6.61</v>
+        <v>4.08</v>
       </c>
       <c r="I13" t="n">
-        <v>-3097688</v>
+        <v>-1935193</v>
       </c>
       <c r="J13" t="n">
-        <v>-1207358083</v>
+        <v>-1207888863</v>
       </c>
       <c r="K13" t="n">
-        <v>-1207358083</v>
+        <v>-1207888863</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-1096</v>
+        <v>-400000</v>
       </c>
       <c r="E18" t="n">
-        <v>-1096</v>
+        <v>-400000</v>
       </c>
       <c r="F18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-1096</v>
+        <v>-400000</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1275,28 +1275,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-69931279</v>
+        <v>-69987510</v>
       </c>
       <c r="E19" t="n">
-        <v>-69931279</v>
+        <v>-69987510</v>
       </c>
       <c r="F19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-63893777</v>
+        <v>-64001096</v>
       </c>
       <c r="H19" t="n">
-        <v>8.630000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-6037502</v>
+        <v>-5986414</v>
       </c>
       <c r="J19" t="n">
-        <v>-2064682015</v>
+        <v>-2066815357</v>
       </c>
       <c r="K19" t="n">
-        <v>-2064682015</v>
+        <v>-2066815357</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1322,31 +1322,31 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7504692</v>
+        <v>7513798</v>
       </c>
       <c r="E20" t="n">
-        <v>7504692</v>
+        <v>7513798</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>4095008</v>
+        <v>4095007</v>
       </c>
       <c r="H20" t="n">
-        <v>-45.43</v>
+        <v>-45.5</v>
       </c>
       <c r="I20" t="n">
-        <v>3409684</v>
+        <v>3418791</v>
       </c>
       <c r="J20" t="n">
-        <v>200000936</v>
+        <v>200001320</v>
       </c>
       <c r="K20" t="n">
-        <v>200000936</v>
+        <v>200001320</v>
       </c>
       <c r="L20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1369,28 +1369,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-15062077</v>
+        <v>-14996405</v>
       </c>
       <c r="E21" t="n">
-        <v>-15062077</v>
+        <v>-14996405</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-8189919</v>
+        <v>-8190034</v>
       </c>
       <c r="H21" t="n">
-        <v>45.63</v>
+        <v>45.39</v>
       </c>
       <c r="I21" t="n">
-        <v>-6872158</v>
+        <v>-6806371</v>
       </c>
       <c r="J21" t="n">
-        <v>-400002071</v>
+        <v>-400002036</v>
       </c>
       <c r="K21" t="n">
-        <v>-400002071</v>
+        <v>-400002036</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2254,34 +2254,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>499376</v>
+        <v>430564</v>
       </c>
       <c r="F16" t="n">
-        <v>499376</v>
+        <v>430564</v>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>7089570</v>
+        <v>9610006</v>
       </c>
       <c r="I16" t="n">
-        <v>1319.69</v>
+        <v>2131.96</v>
       </c>
       <c r="J16" t="n">
-        <v>19120304</v>
+        <v>19002876</v>
       </c>
       <c r="K16" t="n">
-        <v>19120305</v>
+        <v>19002876</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M16" t="n">
-        <v>19120305</v>
+        <v>19002876</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="17">
@@ -2306,34 +2306,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-2142960</v>
+        <v>-2191248</v>
       </c>
       <c r="F17" t="n">
-        <v>-2142960</v>
+        <v>-2191248</v>
       </c>
       <c r="G17" t="n">
         <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>4447234</v>
+        <v>6988194</v>
       </c>
       <c r="I17" t="n">
-        <v>307.53</v>
+        <v>418.91</v>
       </c>
       <c r="J17" t="n">
-        <v>24569067</v>
+        <v>24485629</v>
       </c>
       <c r="K17" t="n">
-        <v>24569068</v>
+        <v>24485628</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M17" t="n">
-        <v>24569068</v>
+        <v>24485628</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -2358,34 +2358,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>-3990697</v>
+        <v>-4029924</v>
       </c>
       <c r="F18" t="n">
-        <v>-3990697</v>
+        <v>-4029924</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H18" t="n">
-        <v>2599497</v>
+        <v>5149518</v>
       </c>
       <c r="I18" t="n">
-        <v>165.14</v>
+        <v>227.78</v>
       </c>
       <c r="J18" t="n">
-        <v>63153444</v>
+        <v>62930026</v>
       </c>
       <c r="K18" t="n">
-        <v>63153447</v>
+        <v>62930024</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
-        <v>63153447</v>
+        <v>62930024</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="19">
@@ -2410,31 +2410,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2176760</v>
+        <v>2107295</v>
       </c>
       <c r="F19" t="n">
-        <v>2176760</v>
+        <v>2107295</v>
       </c>
       <c r="G19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>8766954</v>
+        <v>11286737</v>
       </c>
       <c r="I19" t="n">
-        <v>302.75</v>
+        <v>435.6</v>
       </c>
       <c r="J19" t="n">
-        <v>-57675768</v>
+        <v>-57497801</v>
       </c>
       <c r="K19" t="n">
-        <v>-57675766</v>
+        <v>-57497801</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-57675766</v>
+        <v>-57497801</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2462,34 +2462,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-3400070</v>
+        <v>-3435361</v>
       </c>
       <c r="F20" t="n">
-        <v>-3400070</v>
+        <v>-3435361</v>
       </c>
       <c r="G20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3190124</v>
+        <v>5744081</v>
       </c>
       <c r="I20" t="n">
-        <v>193.83</v>
+        <v>267.2</v>
       </c>
       <c r="J20" t="n">
-        <v>7597734</v>
+        <v>7618238</v>
       </c>
       <c r="K20" t="n">
-        <v>7597734</v>
+        <v>7618237</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M20" t="n">
-        <v>7597734</v>
+        <v>7618237</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="21">
@@ -2514,31 +2514,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1585460</v>
+        <v>1512138</v>
       </c>
       <c r="F21" t="n">
-        <v>1585460</v>
+        <v>1512138</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H21" t="n">
-        <v>8175654</v>
+        <v>10691580</v>
       </c>
       <c r="I21" t="n">
-        <v>415.66</v>
+        <v>607.05</v>
       </c>
       <c r="J21" t="n">
-        <v>-7524320</v>
+        <v>-7544580</v>
       </c>
       <c r="K21" t="n">
-        <v>-7524322</v>
+        <v>-7544582</v>
       </c>
       <c r="L21" t="n">
         <v>-0</v>
       </c>
       <c r="M21" t="n">
-        <v>-7524322</v>
+        <v>-7544582</v>
       </c>
       <c r="N21" t="n">
         <v>-0</v>
@@ -2566,34 +2566,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-1826420</v>
+        <v>-1869275</v>
       </c>
       <c r="F22" t="n">
-        <v>-1826420</v>
+        <v>-1869275</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>4763774</v>
+        <v>7310167</v>
       </c>
       <c r="I22" t="n">
-        <v>360.83</v>
+        <v>491.07</v>
       </c>
       <c r="J22" t="n">
-        <v>-24079680</v>
+        <v>-23957566</v>
       </c>
       <c r="K22" t="n">
-        <v>-24079678</v>
+        <v>-23957568</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M22" t="n">
-        <v>-24079678</v>
+        <v>-23957568</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="23">
@@ -2618,31 +2618,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3795608</v>
+        <v>3804409</v>
       </c>
       <c r="F23" t="n">
-        <v>3795608</v>
+        <v>3804409</v>
       </c>
       <c r="G23" t="n">
         <v>-0</v>
       </c>
       <c r="H23" t="n">
-        <v>57240423</v>
+        <v>60943320</v>
       </c>
       <c r="I23" t="n">
-        <v>1408.07</v>
+        <v>1501.91</v>
       </c>
       <c r="J23" t="n">
-        <v>-1975186</v>
+        <v>-2001499</v>
       </c>
       <c r="K23" t="n">
-        <v>-1975185</v>
+        <v>-2001495</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1975185</v>
+        <v>-2001495</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2670,31 +2670,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-23413591</v>
+        <v>-23403623</v>
       </c>
       <c r="F24" t="n">
-        <v>-23413591</v>
+        <v>-23403623</v>
       </c>
       <c r="G24" t="n">
         <v>-0</v>
       </c>
       <c r="H24" t="n">
-        <v>30031224</v>
+        <v>33735288</v>
       </c>
       <c r="I24" t="n">
-        <v>228.26</v>
+        <v>244.15</v>
       </c>
       <c r="J24" t="n">
-        <v>10446248</v>
+        <v>10423090</v>
       </c>
       <c r="K24" t="n">
-        <v>10444496</v>
+        <v>10421025</v>
       </c>
       <c r="L24" t="n">
         <v>-0.02</v>
       </c>
       <c r="M24" t="n">
-        <v>10444496</v>
+        <v>10421025</v>
       </c>
       <c r="N24" t="n">
         <v>-0.02</v>
@@ -2722,31 +2722,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-57925950</v>
+        <v>-57902610</v>
       </c>
       <c r="F25" t="n">
-        <v>-57925950</v>
+        <v>-57902610</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-4481135</v>
+        <v>-763699</v>
       </c>
       <c r="I25" t="n">
-        <v>92.26000000000001</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>27074775</v>
+        <v>27012576</v>
       </c>
       <c r="K25" t="n">
-        <v>27074775</v>
+        <v>27012579</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>27074775</v>
+        <v>27012579</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2774,31 +2774,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>57282372</v>
+        <v>57261057</v>
       </c>
       <c r="F26" t="n">
-        <v>57282372</v>
+        <v>57261057</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H26" t="n">
-        <v>110727187</v>
+        <v>114399968</v>
       </c>
       <c r="I26" t="n">
-        <v>93.3</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-23902403</v>
+        <v>-23852215</v>
       </c>
       <c r="K26" t="n">
-        <v>-23902399</v>
+        <v>-23852212</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-23902399</v>
+        <v>-23852212</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2826,34 +2826,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-27194036</v>
+        <v>-27190918</v>
       </c>
       <c r="F27" t="n">
-        <v>-27194036</v>
+        <v>-27190918</v>
       </c>
       <c r="G27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>26250779</v>
+        <v>29947993</v>
       </c>
       <c r="I27" t="n">
-        <v>196.53</v>
+        <v>210.14</v>
       </c>
       <c r="J27" t="n">
-        <v>12397680</v>
+        <v>12398110</v>
       </c>
       <c r="K27" t="n">
-        <v>12397684</v>
+        <v>12398110</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M27" t="n">
-        <v>12397684</v>
+        <v>12398110</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="28">
@@ -2878,31 +2878,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>26470091</v>
+        <v>26469091</v>
       </c>
       <c r="F28" t="n">
-        <v>26470091</v>
+        <v>26469091</v>
       </c>
       <c r="G28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>79914906</v>
+        <v>83608002</v>
       </c>
       <c r="I28" t="n">
-        <v>201.91</v>
+        <v>215.87</v>
       </c>
       <c r="J28" t="n">
-        <v>-12197310</v>
+        <v>-12197188</v>
       </c>
       <c r="K28" t="n">
-        <v>-12197304</v>
+        <v>-12197188</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-12197304</v>
+        <v>-12197188</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2930,31 +2930,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2941110</v>
+        <v>2932211</v>
       </c>
       <c r="F29" t="n">
-        <v>2941111</v>
+        <v>2932211</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H29" t="n">
-        <v>56385926</v>
+        <v>60071122</v>
       </c>
       <c r="I29" t="n">
-        <v>1817.16</v>
+        <v>1948.66</v>
       </c>
       <c r="J29" t="n">
-        <v>-493911</v>
+        <v>-465165</v>
       </c>
       <c r="K29" t="n">
-        <v>-493901</v>
+        <v>-465160</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-493901</v>
+        <v>-465160</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2982,34 +2982,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1401842</v>
+        <v>715648</v>
       </c>
       <c r="F30" t="n">
-        <v>1401842</v>
+        <v>715648</v>
       </c>
       <c r="G30" t="n">
         <v>-0</v>
       </c>
       <c r="H30" t="n">
-        <v>11685788</v>
+        <v>7739367</v>
       </c>
       <c r="I30" t="n">
-        <v>733.6</v>
+        <v>981.45</v>
       </c>
       <c r="J30" t="n">
-        <v>27108471</v>
+        <v>26443001</v>
       </c>
       <c r="K30" t="n">
-        <v>27108467</v>
+        <v>26443002</v>
       </c>
       <c r="L30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>27108467</v>
+        <v>26443002</v>
       </c>
       <c r="N30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3034,34 +3034,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-1501357</v>
+        <v>-771242</v>
       </c>
       <c r="F31" t="n">
-        <v>-1501357</v>
+        <v>-771242</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" t="n">
-        <v>8782589</v>
+        <v>6252477</v>
       </c>
       <c r="I31" t="n">
-        <v>684.98</v>
+        <v>910.7</v>
       </c>
       <c r="J31" t="n">
-        <v>30973964</v>
+        <v>30213071</v>
       </c>
       <c r="K31" t="n">
-        <v>30973962</v>
+        <v>30213072</v>
       </c>
       <c r="L31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>30973962</v>
+        <v>30213072</v>
       </c>
       <c r="N31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3086,34 +3086,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-3598711</v>
+        <v>-1843105</v>
       </c>
       <c r="F32" t="n">
-        <v>-3598711</v>
+        <v>-1843105</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>6685235</v>
+        <v>5180614</v>
       </c>
       <c r="I32" t="n">
-        <v>285.77</v>
+        <v>381.08</v>
       </c>
       <c r="J32" t="n">
-        <v>79868570</v>
+        <v>77908278</v>
       </c>
       <c r="K32" t="n">
-        <v>79868567</v>
+        <v>77908278</v>
       </c>
       <c r="L32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>79868567</v>
+        <v>77908278</v>
       </c>
       <c r="N32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3138,34 +3138,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3402086</v>
+        <v>1734686</v>
       </c>
       <c r="F33" t="n">
-        <v>3402086</v>
+        <v>1734686</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>13686032</v>
+        <v>8758405</v>
       </c>
       <c r="I33" t="n">
-        <v>302.28</v>
+        <v>404.9</v>
       </c>
       <c r="J33" t="n">
-        <v>-72188151</v>
+        <v>-70411472</v>
       </c>
       <c r="K33" t="n">
-        <v>-72188154</v>
+        <v>-70411472</v>
       </c>
       <c r="L33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-72188154</v>
+        <v>-70411472</v>
       </c>
       <c r="N33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3190,34 +3190,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-2842868</v>
+        <v>-1459681</v>
       </c>
       <c r="F34" t="n">
-        <v>-2842868</v>
+        <v>-1459681</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H34" t="n">
-        <v>7441078</v>
+        <v>5564038</v>
       </c>
       <c r="I34" t="n">
-        <v>361.75</v>
+        <v>481.18</v>
       </c>
       <c r="J34" t="n">
-        <v>6912030</v>
+        <v>6741951</v>
       </c>
       <c r="K34" t="n">
-        <v>6912027</v>
+        <v>6741952</v>
       </c>
       <c r="L34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>6912027</v>
+        <v>6741952</v>
       </c>
       <c r="N34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3242,34 +3242,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2645071</v>
+        <v>1350662</v>
       </c>
       <c r="F35" t="n">
-        <v>2645071</v>
+        <v>1350662</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>12929017</v>
+        <v>8374381</v>
       </c>
       <c r="I35" t="n">
-        <v>388.8</v>
+        <v>520.02</v>
       </c>
       <c r="J35" t="n">
-        <v>-6847757</v>
+        <v>-6679264</v>
       </c>
       <c r="K35" t="n">
-        <v>-6847760</v>
+        <v>-6679263</v>
       </c>
       <c r="L35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-6847760</v>
+        <v>-6679263</v>
       </c>
       <c r="N35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3294,34 +3294,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-1053280</v>
+        <v>-545200</v>
       </c>
       <c r="F36" t="n">
-        <v>-1053280</v>
+        <v>-545200</v>
       </c>
       <c r="G36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>9230666</v>
+        <v>6478519</v>
       </c>
       <c r="I36" t="n">
-        <v>976.37</v>
+        <v>1288.28</v>
       </c>
       <c r="J36" t="n">
-        <v>-32882440</v>
+        <v>-32073591</v>
       </c>
       <c r="K36" t="n">
-        <v>-32882443</v>
+        <v>-32073590</v>
       </c>
       <c r="L36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-32882443</v>
+        <v>-32073590</v>
       </c>
       <c r="N36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3346,34 +3346,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-507620</v>
+        <v>-356232</v>
       </c>
       <c r="F37" t="n">
-        <v>-602084</v>
+        <v>-450129</v>
       </c>
       <c r="G37" t="n">
-        <v>-18.61</v>
+        <v>-26.36</v>
       </c>
       <c r="H37" t="n">
-        <v>21760074</v>
+        <v>73825113</v>
       </c>
       <c r="I37" t="n">
-        <v>4386.69</v>
+        <v>20823.87</v>
       </c>
       <c r="J37" t="n">
-        <v>-5487565</v>
+        <v>-6375645</v>
       </c>
       <c r="K37" t="n">
-        <v>-5487564</v>
+        <v>-6375647</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M37" t="n">
-        <v>-5487564</v>
+        <v>-6375647</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="38">
@@ -3398,31 +3398,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-9741662</v>
+        <v>-9751659</v>
       </c>
       <c r="F38" t="n">
-        <v>-9742106</v>
+        <v>-9752279</v>
       </c>
       <c r="G38" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="H38" t="n">
-        <v>12620052</v>
+        <v>64522963</v>
       </c>
       <c r="I38" t="n">
-        <v>229.55</v>
+        <v>761.66</v>
       </c>
       <c r="J38" t="n">
-        <v>9669408</v>
+        <v>7809893</v>
       </c>
       <c r="K38" t="n">
-        <v>9669070</v>
+        <v>7809642</v>
       </c>
       <c r="L38" t="n">
         <v>-0</v>
       </c>
       <c r="M38" t="n">
-        <v>9669070</v>
+        <v>7809642</v>
       </c>
       <c r="N38" t="n">
         <v>-0</v>
@@ -3450,34 +3450,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-23794617</v>
+        <v>-23821566</v>
       </c>
       <c r="F39" t="n">
-        <v>-23794192</v>
+        <v>-23821570</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1432034</v>
+        <v>50453672</v>
       </c>
       <c r="I39" t="n">
-        <v>93.98</v>
+        <v>311.8</v>
       </c>
       <c r="J39" t="n">
-        <v>24612672</v>
+        <v>19875132</v>
       </c>
       <c r="K39" t="n">
-        <v>24612675</v>
+        <v>19875130</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M39" t="n">
-        <v>24612675</v>
+        <v>19875130</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="40">
@@ -3502,34 +3502,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>23116208</v>
+        <v>23145825</v>
       </c>
       <c r="F40" t="n">
-        <v>23113779</v>
+        <v>23143810</v>
       </c>
       <c r="G40" t="n">
         <v>-0.01</v>
       </c>
       <c r="H40" t="n">
-        <v>45475937</v>
+        <v>97419052</v>
       </c>
       <c r="I40" t="n">
-        <v>96.73</v>
+        <v>320.89</v>
       </c>
       <c r="J40" t="n">
-        <v>-23115869</v>
+        <v>-18667041</v>
       </c>
       <c r="K40" t="n">
-        <v>-23115866</v>
+        <v>-18667042</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M40" t="n">
-        <v>-23115866</v>
+        <v>-18667042</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="41">
@@ -3554,34 +3554,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-9636853</v>
+        <v>-9780474</v>
       </c>
       <c r="F41" t="n">
-        <v>-9554185</v>
+        <v>-9698482</v>
       </c>
       <c r="G41" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="H41" t="n">
-        <v>12807973</v>
+        <v>64576760</v>
       </c>
       <c r="I41" t="n">
-        <v>232.91</v>
+        <v>760.26</v>
       </c>
       <c r="J41" t="n">
-        <v>14713726</v>
+        <v>13640090</v>
       </c>
       <c r="K41" t="n">
-        <v>14713728</v>
+        <v>13640089</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M41" t="n">
-        <v>14713728</v>
+        <v>13640089</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="42">
@@ -3606,31 +3606,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>8923345</v>
+        <v>9069934</v>
       </c>
       <c r="F42" t="n">
-        <v>8838377</v>
+        <v>8985639</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.95</v>
+        <v>-0.93</v>
       </c>
       <c r="H42" t="n">
-        <v>31200535</v>
+        <v>83260881</v>
       </c>
       <c r="I42" t="n">
-        <v>249.65</v>
+        <v>817.99</v>
       </c>
       <c r="J42" t="n">
-        <v>-14517901</v>
+        <v>-13456425</v>
       </c>
       <c r="K42" t="n">
-        <v>-14517900</v>
+        <v>-13456425</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-14517900</v>
+        <v>-13456425</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3658,34 +3658,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2693701</v>
+        <v>2560014</v>
       </c>
       <c r="F43" t="n">
-        <v>2778748</v>
+        <v>2644577</v>
       </c>
       <c r="G43" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="H43" t="n">
-        <v>25140906</v>
+        <v>76919819</v>
       </c>
       <c r="I43" t="n">
-        <v>833.3200000000001</v>
+        <v>2904.66</v>
       </c>
       <c r="J43" t="n">
-        <v>2471276</v>
+        <v>3814606</v>
       </c>
       <c r="K43" t="n">
-        <v>2471277</v>
+        <v>3814604</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M43" t="n">
-        <v>2471277</v>
+        <v>3814604</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="44">
@@ -3710,34 +3710,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>287047</v>
+        <v>1859680</v>
       </c>
       <c r="F44" t="n">
-        <v>287047</v>
+        <v>1859680</v>
       </c>
       <c r="G44" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1146647</v>
+        <v>6073244</v>
       </c>
       <c r="I44" t="n">
-        <v>299.46</v>
+        <v>226.57</v>
       </c>
       <c r="J44" t="n">
-        <v>34078764</v>
+        <v>36635099</v>
       </c>
       <c r="K44" t="n">
-        <v>34078764</v>
+        <v>38042106</v>
       </c>
       <c r="L44" t="n">
-        <v>-0</v>
+        <v>3.84</v>
       </c>
       <c r="M44" t="n">
-        <v>34078764</v>
+        <v>38042106</v>
       </c>
       <c r="N44" t="n">
-        <v>-0</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="45">
@@ -3762,34 +3762,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-170755</v>
+        <v>-997155</v>
       </c>
       <c r="F45" t="n">
-        <v>-170755</v>
+        <v>-997155</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>688845</v>
+        <v>3216409</v>
       </c>
       <c r="I45" t="n">
-        <v>503.41</v>
+        <v>422.56</v>
       </c>
       <c r="J45" t="n">
-        <v>41380880</v>
+        <v>41207527</v>
       </c>
       <c r="K45" t="n">
-        <v>41380880</v>
+        <v>42950525</v>
       </c>
       <c r="L45" t="n">
-        <v>-0</v>
+        <v>4.23</v>
       </c>
       <c r="M45" t="n">
-        <v>41380880</v>
+        <v>42950525</v>
       </c>
       <c r="N45" t="n">
-        <v>-0</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="46">
@@ -3814,34 +3814,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-425751</v>
+        <v>-2487722</v>
       </c>
       <c r="F46" t="n">
-        <v>-425751</v>
+        <v>-2487722</v>
       </c>
       <c r="G46" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>433849</v>
+        <v>1725842</v>
       </c>
       <c r="I46" t="n">
-        <v>201.9</v>
+        <v>169.37</v>
       </c>
       <c r="J46" t="n">
-        <v>106036598</v>
+        <v>105696101</v>
       </c>
       <c r="K46" t="n">
-        <v>106036598</v>
+        <v>110163704</v>
       </c>
       <c r="L46" t="n">
-        <v>-0</v>
+        <v>4.23</v>
       </c>
       <c r="M46" t="n">
-        <v>106036598</v>
+        <v>110163704</v>
       </c>
       <c r="N46" t="n">
-        <v>-0</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="47">
@@ -3866,34 +3866,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>429566</v>
+        <v>2505024</v>
       </c>
       <c r="F47" t="n">
-        <v>429566</v>
+        <v>2505024</v>
       </c>
       <c r="G47" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1289166</v>
+        <v>6718588</v>
       </c>
       <c r="I47" t="n">
-        <v>200.11</v>
+        <v>168.2</v>
       </c>
       <c r="J47" t="n">
-        <v>-97773111</v>
+        <v>-97141265</v>
       </c>
       <c r="K47" t="n">
-        <v>-97773112</v>
+        <v>-101257236</v>
       </c>
       <c r="L47" t="n">
-        <v>-0</v>
+        <v>-4.24</v>
       </c>
       <c r="M47" t="n">
-        <v>-97773112</v>
+        <v>-101257236</v>
       </c>
       <c r="N47" t="n">
-        <v>-0</v>
+        <v>-4.24</v>
       </c>
     </row>
     <row r="48">
@@ -3918,34 +3918,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-425319</v>
+        <v>-2646450</v>
       </c>
       <c r="F48" t="n">
-        <v>-425319</v>
+        <v>-2646450</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>434281</v>
+        <v>1567114</v>
       </c>
       <c r="I48" t="n">
-        <v>202.11</v>
+        <v>159.22</v>
       </c>
       <c r="J48" t="n">
-        <v>11084040</v>
+        <v>8614222</v>
       </c>
       <c r="K48" t="n">
-        <v>11084040</v>
+        <v>9106661</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="M48" t="n">
-        <v>11084040</v>
+        <v>9106661</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="49">
@@ -3970,34 +3970,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>428576</v>
+        <v>2665460</v>
       </c>
       <c r="F49" t="n">
-        <v>428576</v>
+        <v>2665460</v>
       </c>
       <c r="G49" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1288176</v>
+        <v>6879024</v>
       </c>
       <c r="I49" t="n">
-        <v>200.57</v>
+        <v>158.08</v>
       </c>
       <c r="J49" t="n">
-        <v>-10978767</v>
+        <v>-8549200</v>
       </c>
       <c r="K49" t="n">
-        <v>-10978767</v>
+        <v>-9037136</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>-5.71</v>
       </c>
       <c r="M49" t="n">
-        <v>-10978767</v>
+        <v>-9037136</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>-5.71</v>
       </c>
     </row>
     <row r="50">
@@ -4022,34 +4022,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-210876</v>
+        <v>-1400145</v>
       </c>
       <c r="F50" t="n">
-        <v>-210876</v>
+        <v>-1400145</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>648724</v>
+        <v>2813419</v>
       </c>
       <c r="I50" t="n">
-        <v>407.63</v>
+        <v>300.94</v>
       </c>
       <c r="J50" t="n">
-        <v>-42581994</v>
+        <v>-44803536</v>
       </c>
       <c r="K50" t="n">
-        <v>-42581994</v>
+        <v>-46569638</v>
       </c>
       <c r="L50" t="n">
-        <v>-0</v>
+        <v>-3.94</v>
       </c>
       <c r="M50" t="n">
-        <v>-42581994</v>
+        <v>-46569638</v>
       </c>
       <c r="N50" t="n">
-        <v>-0</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="51">
@@ -4074,31 +4074,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1468465</v>
+        <v>-264153</v>
       </c>
       <c r="F51" t="n">
-        <v>1421238</v>
+        <v>-223933</v>
       </c>
       <c r="G51" t="n">
-        <v>-3.22</v>
+        <v>15.23</v>
       </c>
       <c r="H51" t="n">
-        <v>4050900</v>
+        <v>1064018</v>
       </c>
       <c r="I51" t="n">
-        <v>175.86</v>
+        <v>502.8</v>
       </c>
       <c r="J51" t="n">
-        <v>-6070731</v>
+        <v>-5968037</v>
       </c>
       <c r="K51" t="n">
-        <v>-6070731</v>
+        <v>-5968037</v>
       </c>
       <c r="L51" t="n">
         <v>-0</v>
       </c>
       <c r="M51" t="n">
-        <v>-6070731</v>
+        <v>-5968037</v>
       </c>
       <c r="N51" t="n">
         <v>-0</v>
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-4611378</v>
+        <v>-5612786</v>
       </c>
       <c r="F52" t="n">
-        <v>-4673222</v>
+        <v>-5612009</v>
       </c>
       <c r="G52" t="n">
-        <v>-1.34</v>
+        <v>0.01</v>
       </c>
       <c r="H52" t="n">
-        <v>-2043560</v>
+        <v>-4324058</v>
       </c>
       <c r="I52" t="n">
-        <v>55.68</v>
+        <v>22.96</v>
       </c>
       <c r="J52" t="n">
-        <v>4246042</v>
+        <v>4065438</v>
       </c>
       <c r="K52" t="n">
-        <v>4246042</v>
+        <v>4065438</v>
       </c>
       <c r="L52" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4246042</v>
+        <v>4065438</v>
       </c>
       <c r="N52" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4178,31 +4178,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>-11490710</v>
+        <v>-13982049</v>
       </c>
       <c r="F53" t="n">
-        <v>-11644405</v>
+        <v>-13980011</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.34</v>
+        <v>0.01</v>
       </c>
       <c r="H53" t="n">
-        <v>-9014743</v>
+        <v>-12692060</v>
       </c>
       <c r="I53" t="n">
-        <v>21.55</v>
+        <v>9.23</v>
       </c>
       <c r="J53" t="n">
-        <v>10638145</v>
+        <v>10181091</v>
       </c>
       <c r="K53" t="n">
-        <v>10638145</v>
+        <v>10181091</v>
       </c>
       <c r="L53" t="n">
         <v>-0</v>
       </c>
       <c r="M53" t="n">
-        <v>10638145</v>
+        <v>10181091</v>
       </c>
       <c r="N53" t="n">
         <v>-0</v>
@@ -4230,31 +4230,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>11618557</v>
+        <v>14150512</v>
       </c>
       <c r="F54" t="n">
-        <v>11775235</v>
+        <v>14148751</v>
       </c>
       <c r="G54" t="n">
-        <v>1.35</v>
+        <v>-0.01</v>
       </c>
       <c r="H54" t="n">
-        <v>14404897</v>
+        <v>15436702</v>
       </c>
       <c r="I54" t="n">
-        <v>23.98</v>
+        <v>9.09</v>
       </c>
       <c r="J54" t="n">
-        <v>-10497722</v>
+        <v>-10044425</v>
       </c>
       <c r="K54" t="n">
-        <v>-10497722</v>
+        <v>-10044425</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-10497722</v>
+        <v>-10044425</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -4282,34 +4282,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>-5922622</v>
+        <v>-5390580</v>
       </c>
       <c r="F55" t="n">
-        <v>-5943134</v>
+        <v>-5425702</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.35</v>
+        <v>-0.65</v>
       </c>
       <c r="H55" t="n">
-        <v>-3313472</v>
+        <v>-4137751</v>
       </c>
       <c r="I55" t="n">
-        <v>44.05</v>
+        <v>23.24</v>
       </c>
       <c r="J55" t="n">
-        <v>9732389</v>
+        <v>9459173</v>
       </c>
       <c r="K55" t="n">
-        <v>9732389</v>
+        <v>9459173</v>
       </c>
       <c r="L55" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>9732389</v>
+        <v>9459173</v>
       </c>
       <c r="N55" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4334,34 +4334,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5957637</v>
+        <v>5418891</v>
       </c>
       <c r="F56" t="n">
-        <v>5978148</v>
+        <v>5454288</v>
       </c>
       <c r="G56" t="n">
-        <v>0.34</v>
+        <v>0.65</v>
       </c>
       <c r="H56" t="n">
-        <v>8607810</v>
+        <v>6742239</v>
       </c>
       <c r="I56" t="n">
-        <v>44.48</v>
+        <v>24.42</v>
       </c>
       <c r="J56" t="n">
-        <v>-9624967</v>
+        <v>-9352416</v>
       </c>
       <c r="K56" t="n">
-        <v>-9624967</v>
+        <v>-9352416</v>
       </c>
       <c r="L56" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-9624967</v>
+        <v>-9352416</v>
       </c>
       <c r="N56" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -4386,34 +4386,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>93082</v>
+        <v>2004038</v>
       </c>
       <c r="F57" t="n">
-        <v>155294</v>
+        <v>1966262</v>
       </c>
       <c r="G57" t="n">
-        <v>66.84</v>
+        <v>-1.88</v>
       </c>
       <c r="H57" t="n">
-        <v>2784956</v>
+        <v>3254213</v>
       </c>
       <c r="I57" t="n">
-        <v>2891.94</v>
+        <v>62.38</v>
       </c>
       <c r="J57" t="n">
-        <v>4337249</v>
+        <v>4302418</v>
       </c>
       <c r="K57" t="n">
-        <v>4337249</v>
+        <v>4302418</v>
       </c>
       <c r="L57" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>4337249</v>
+        <v>4302418</v>
       </c>
       <c r="N57" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -4447,22 +4447,22 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>3458573</v>
+        <v>4921559</v>
       </c>
       <c r="I58" t="n">
-        <v>-29.72</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>-123901</v>
+        <v>-123878</v>
       </c>
       <c r="K58" t="n">
-        <v>-123901</v>
+        <v>-123878</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-123901</v>
+        <v>-123878</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
@@ -4496,28 +4496,28 @@
         <v>-1937096</v>
       </c>
       <c r="G59" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-3399969</v>
+        <v>-1936983</v>
       </c>
       <c r="I59" t="n">
-        <v>-75.52</v>
+        <v>0.01</v>
       </c>
       <c r="J59" t="n">
-        <v>49268</v>
+        <v>49259</v>
       </c>
       <c r="K59" t="n">
-        <v>49268</v>
+        <v>49259</v>
       </c>
       <c r="L59" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>49268</v>
+        <v>49259</v>
       </c>
       <c r="N59" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -4551,25 +4551,25 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-6325334</v>
+        <v>-4862348</v>
       </c>
       <c r="I60" t="n">
-        <v>-30.09</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>123220</v>
+        <v>123198</v>
       </c>
       <c r="K60" t="n">
-        <v>123220</v>
+        <v>123198</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M60" t="n">
-        <v>123220</v>
+        <v>123198</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="61">
@@ -4603,22 +4603,22 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>3430231</v>
+        <v>4893217</v>
       </c>
       <c r="I61" t="n">
-        <v>-29.9</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>-123186</v>
+        <v>-123163</v>
       </c>
       <c r="K61" t="n">
-        <v>-123186</v>
+        <v>-123163</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-123186</v>
+        <v>-123163</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-7769682</v>
+        <v>-6306696</v>
       </c>
       <c r="I62" t="n">
-        <v>-23.2</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>159753</v>
+        <v>159724</v>
       </c>
       <c r="K62" t="n">
-        <v>159753</v>
+        <v>159724</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>159753</v>
+        <v>159724</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -4704,25 +4704,25 @@
         <v>6348583</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H63" t="n">
-        <v>4885710</v>
+        <v>6348696</v>
       </c>
       <c r="I63" t="n">
-        <v>-23.04</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>-159896</v>
+        <v>-159867</v>
       </c>
       <c r="K63" t="n">
-        <v>-159896</v>
+        <v>-159867</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-159896</v>
+        <v>-159867</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -4759,25 +4759,25 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-5372490</v>
+        <v>-3909504</v>
       </c>
       <c r="I64" t="n">
-        <v>-37.42</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>99127</v>
+        <v>99108</v>
       </c>
       <c r="K64" t="n">
-        <v>99127</v>
+        <v>99108</v>
       </c>
       <c r="L64" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>99127</v>
+        <v>99108</v>
       </c>
       <c r="N64" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5110,34 +5110,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>828757</v>
+        <v>685950</v>
       </c>
       <c r="F72" t="n">
-        <v>828904</v>
+        <v>700526</v>
       </c>
       <c r="G72" t="n">
-        <v>0.02</v>
+        <v>2.12</v>
       </c>
       <c r="H72" t="n">
-        <v>11943502</v>
+        <v>8858574</v>
       </c>
       <c r="I72" t="n">
-        <v>1341.13</v>
+        <v>1191.43</v>
       </c>
       <c r="J72" t="n">
-        <v>1474277</v>
+        <v>1410307</v>
       </c>
       <c r="K72" t="n">
-        <v>1474277</v>
+        <v>1410307</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M72" t="n">
-        <v>1474277</v>
+        <v>1410307</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="73">
@@ -5162,34 +5162,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>-4064226</v>
+        <v>-4040895</v>
       </c>
       <c r="F73" t="n">
-        <v>-3969512</v>
+        <v>-3922720</v>
       </c>
       <c r="G73" t="n">
-        <v>2.33</v>
+        <v>2.92</v>
       </c>
       <c r="H73" t="n">
-        <v>7145086</v>
+        <v>4235328</v>
       </c>
       <c r="I73" t="n">
-        <v>275.8</v>
+        <v>204.81</v>
       </c>
       <c r="J73" t="n">
-        <v>4115554</v>
+        <v>3997660</v>
       </c>
       <c r="K73" t="n">
-        <v>4114771</v>
+        <v>3997642</v>
       </c>
       <c r="L73" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="M73" t="n">
-        <v>4114771</v>
+        <v>3997642</v>
       </c>
       <c r="N73" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="74">
@@ -5214,31 +5214,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>-10060797</v>
+        <v>-10002266</v>
       </c>
       <c r="F74" t="n">
-        <v>-9830185</v>
+        <v>-9712874</v>
       </c>
       <c r="G74" t="n">
-        <v>2.29</v>
+        <v>2.89</v>
       </c>
       <c r="H74" t="n">
-        <v>1284413</v>
+        <v>-1554826</v>
       </c>
       <c r="I74" t="n">
-        <v>112.77</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>10540913</v>
+        <v>10244778</v>
       </c>
       <c r="K74" t="n">
-        <v>10540913</v>
+        <v>10244777</v>
       </c>
       <c r="L74" t="n">
         <v>-0</v>
       </c>
       <c r="M74" t="n">
-        <v>10540913</v>
+        <v>10244777</v>
       </c>
       <c r="N74" t="n">
         <v>-0</v>
@@ -5266,31 +5266,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>9956590</v>
+        <v>9897644</v>
       </c>
       <c r="F75" t="n">
-        <v>9736403</v>
+        <v>9617776</v>
       </c>
       <c r="G75" t="n">
-        <v>-2.21</v>
+        <v>-2.83</v>
       </c>
       <c r="H75" t="n">
-        <v>20851001</v>
+        <v>17775824</v>
       </c>
       <c r="I75" t="n">
-        <v>109.42</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="J75" t="n">
-        <v>-9696218</v>
+        <v>-9404980</v>
       </c>
       <c r="K75" t="n">
-        <v>-9696219</v>
+        <v>-9404980</v>
       </c>
       <c r="L75" t="n">
         <v>-0</v>
       </c>
       <c r="M75" t="n">
-        <v>-9696219</v>
+        <v>-9404980</v>
       </c>
       <c r="N75" t="n">
         <v>-0</v>
@@ -5318,34 +5318,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>-4867446</v>
+        <v>-4715759</v>
       </c>
       <c r="F76" t="n">
-        <v>-4768504</v>
+        <v>-4606442</v>
       </c>
       <c r="G76" t="n">
-        <v>2.03</v>
+        <v>2.32</v>
       </c>
       <c r="H76" t="n">
-        <v>6346094</v>
+        <v>3551606</v>
       </c>
       <c r="I76" t="n">
-        <v>230.38</v>
+        <v>175.31</v>
       </c>
       <c r="J76" t="n">
-        <v>2834002</v>
+        <v>2773543</v>
       </c>
       <c r="K76" t="n">
-        <v>2834002</v>
+        <v>2773543</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M76" t="n">
-        <v>2834002</v>
+        <v>2773543</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="77">
@@ -5370,34 +5370,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4750578</v>
+        <v>4599548</v>
       </c>
       <c r="F77" t="n">
-        <v>4660952</v>
+        <v>4498974</v>
       </c>
       <c r="G77" t="n">
-        <v>-1.89</v>
+        <v>-2.19</v>
       </c>
       <c r="H77" t="n">
-        <v>15775550</v>
+        <v>12657022</v>
       </c>
       <c r="I77" t="n">
-        <v>232.08</v>
+        <v>175.18</v>
       </c>
       <c r="J77" t="n">
-        <v>-2792658</v>
+        <v>-2733139</v>
       </c>
       <c r="K77" t="n">
-        <v>-2792658</v>
+        <v>-2733139</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M77" t="n">
-        <v>-2792658</v>
+        <v>-2733139</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="78">
@@ -5422,34 +5422,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>362208</v>
+        <v>486314</v>
       </c>
       <c r="F78" t="n">
-        <v>342649</v>
+        <v>445637</v>
       </c>
       <c r="G78" t="n">
-        <v>-5.4</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>11457247</v>
+        <v>8603685</v>
       </c>
       <c r="I78" t="n">
-        <v>3063.17</v>
+        <v>1669.16</v>
       </c>
       <c r="J78" t="n">
-        <v>-2432342</v>
+        <v>-2334757</v>
       </c>
       <c r="K78" t="n">
-        <v>-2432342</v>
+        <v>-2334756</v>
       </c>
       <c r="L78" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-2432342</v>
+        <v>-2334756</v>
       </c>
       <c r="N78" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -5474,31 +5474,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>-453192</v>
+        <v>-80541</v>
       </c>
       <c r="F79" t="n">
-        <v>-453192</v>
+        <v>-100930</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>-25.32</v>
       </c>
       <c r="H79" t="n">
-        <v>-3550880</v>
+        <v>-2036123</v>
       </c>
       <c r="I79" t="n">
-        <v>-683.53</v>
+        <v>-2428.07</v>
       </c>
       <c r="J79" t="n">
-        <v>6420267</v>
+        <v>6195844</v>
       </c>
       <c r="K79" t="n">
-        <v>6420267</v>
+        <v>6195844</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>6420267</v>
+        <v>6195844</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
@@ -5526,34 +5526,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5734281</v>
+        <v>5839745</v>
       </c>
       <c r="F80" t="n">
-        <v>5734281</v>
+        <v>5847361</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="H80" t="n">
-        <v>2636593</v>
+        <v>3912168</v>
       </c>
       <c r="I80" t="n">
-        <v>-54.02</v>
+        <v>-33.01</v>
       </c>
       <c r="J80" t="n">
-        <v>-4495486</v>
+        <v>-4419244</v>
       </c>
       <c r="K80" t="n">
-        <v>-4492938</v>
+        <v>-4413204</v>
       </c>
       <c r="L80" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="M80" t="n">
-        <v>-4492938</v>
+        <v>-4413204</v>
       </c>
       <c r="N80" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="81">
@@ -5578,34 +5578,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>14281976</v>
+        <v>14547712</v>
       </c>
       <c r="F81" t="n">
-        <v>14281976</v>
+        <v>14566597</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="H81" t="n">
-        <v>11184288</v>
+        <v>12631404</v>
       </c>
       <c r="I81" t="n">
-        <v>-21.69</v>
+        <v>-13.17</v>
       </c>
       <c r="J81" t="n">
-        <v>-11262652</v>
+        <v>-11074196</v>
       </c>
       <c r="K81" t="n">
-        <v>-11262652</v>
+        <v>-11074196</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M81" t="n">
-        <v>-11262652</v>
+        <v>-11074196</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="82">
@@ -5630,31 +5630,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>-14460445</v>
+        <v>-14729104</v>
       </c>
       <c r="F82" t="n">
-        <v>-14460445</v>
+        <v>-14748273</v>
       </c>
       <c r="G82" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="H82" t="n">
-        <v>-17558133</v>
+        <v>-16683466</v>
       </c>
       <c r="I82" t="n">
-        <v>-21.42</v>
+        <v>-13.27</v>
       </c>
       <c r="J82" t="n">
-        <v>11114971</v>
+        <v>10924960</v>
       </c>
       <c r="K82" t="n">
-        <v>11114971</v>
+        <v>10924960</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>11114971</v>
+        <v>10924960</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
@@ -5682,34 +5682,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6144804</v>
+        <v>5918996</v>
       </c>
       <c r="F83" t="n">
-        <v>6144804</v>
+        <v>5945027</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H83" t="n">
-        <v>3047116</v>
+        <v>4009834</v>
       </c>
       <c r="I83" t="n">
-        <v>-50.41</v>
+        <v>-32.25</v>
       </c>
       <c r="J83" t="n">
-        <v>-10297762</v>
+        <v>-10019521</v>
       </c>
       <c r="K83" t="n">
-        <v>-10297762</v>
+        <v>-10019521</v>
       </c>
       <c r="L83" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>-10297762</v>
+        <v>-10019521</v>
       </c>
       <c r="N83" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5734,31 +5734,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>-6186706</v>
+        <v>-5959061</v>
       </c>
       <c r="F84" t="n">
-        <v>-6186706</v>
+        <v>-5985038</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="H84" t="n">
-        <v>-9284394</v>
+        <v>-7920231</v>
       </c>
       <c r="I84" t="n">
-        <v>-50.07</v>
+        <v>-32.91</v>
       </c>
       <c r="J84" t="n">
-        <v>10183894</v>
+        <v>9908194</v>
       </c>
       <c r="K84" t="n">
-        <v>10183894</v>
+        <v>9908194</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>10183894</v>
+        <v>9908194</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -5786,31 +5786,31 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>-1379950</v>
+        <v>-1761763</v>
       </c>
       <c r="F85" t="n">
-        <v>-1379950</v>
+        <v>-1744880</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="H85" t="n">
-        <v>-4477638</v>
+        <v>-3680073</v>
       </c>
       <c r="I85" t="n">
-        <v>-224.48</v>
+        <v>-108.89</v>
       </c>
       <c r="J85" t="n">
-        <v>-4585124</v>
+        <v>-4399754</v>
       </c>
       <c r="K85" t="n">
-        <v>-4585124</v>
+        <v>-4399754</v>
       </c>
       <c r="L85" t="n">
         <v>-0</v>
       </c>
       <c r="M85" t="n">
-        <v>-4585124</v>
+        <v>-4399754</v>
       </c>
       <c r="N85" t="n">
         <v>-0</v>
@@ -6971,13 +6971,13 @@
         <v>-13034099</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M111" t="n">
         <v>-13034099</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="112">
@@ -7019,13 +7019,13 @@
         <v>12920318</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M112" t="n">
         <v>12920318</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="113">
@@ -7098,31 +7098,27 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1096</v>
+        <v>-0</v>
       </c>
       <c r="F114" t="n">
-        <v>1096</v>
-      </c>
-      <c r="G114" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>1096</v>
-      </c>
-      <c r="I114" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
-        <v>31624</v>
+        <v>30528</v>
       </c>
       <c r="K114" t="n">
-        <v>31624</v>
+        <v>30528</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>31624</v>
+        <v>30528</v>
       </c>
       <c r="N114" t="n">
         <v>0</v>
@@ -7150,31 +7146,27 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1096</v>
+        <v>-0</v>
       </c>
       <c r="F115" t="n">
-        <v>1096</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>1096</v>
-      </c>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
-        <v>-9868</v>
+        <v>-10964</v>
       </c>
       <c r="K115" t="n">
-        <v>-9868</v>
+        <v>-10964</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>-9868</v>
+        <v>-10964</v>
       </c>
       <c r="N115" t="n">
         <v>0</v>
@@ -7202,31 +7194,31 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1096</v>
+        <v>27215</v>
       </c>
       <c r="F116" t="n">
-        <v>1096</v>
+        <v>27215</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>1096</v>
+        <v>27215</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>-26292</v>
+        <v>-27313</v>
       </c>
       <c r="K116" t="n">
-        <v>-26292</v>
+        <v>-27313</v>
       </c>
       <c r="L116" t="n">
         <v>-0</v>
       </c>
       <c r="M116" t="n">
-        <v>-26292</v>
+        <v>-27313</v>
       </c>
       <c r="N116" t="n">
         <v>-0</v>
@@ -7254,31 +7246,27 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1096</v>
+        <v>-0</v>
       </c>
       <c r="F117" t="n">
-        <v>1096</v>
-      </c>
-      <c r="G117" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>1096</v>
-      </c>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="n">
-        <v>28460</v>
+        <v>27364</v>
       </c>
       <c r="K117" t="n">
-        <v>28460</v>
+        <v>27364</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>28460</v>
+        <v>27364</v>
       </c>
       <c r="N117" t="n">
         <v>0</v>
@@ -7306,16 +7294,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1096</v>
+        <v>398904</v>
       </c>
       <c r="F118" t="n">
-        <v>1096</v>
+        <v>398904</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>1096</v>
+        <v>398904</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -7358,31 +7346,27 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1096</v>
+        <v>-0</v>
       </c>
       <c r="F119" t="n">
-        <v>1096</v>
-      </c>
-      <c r="G119" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>1096</v>
-      </c>
-      <c r="I119" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="n">
-        <v>39304</v>
+        <v>38208</v>
       </c>
       <c r="K119" t="n">
-        <v>39304</v>
+        <v>38208</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>39304</v>
+        <v>38208</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
@@ -7410,31 +7394,27 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1096</v>
+        <v>-0</v>
       </c>
       <c r="F120" t="n">
-        <v>1096</v>
-      </c>
-      <c r="G120" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>1096</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
-        <v>-23720</v>
+        <v>-24816</v>
       </c>
       <c r="K120" t="n">
-        <v>-23720</v>
+        <v>-24816</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>-23720</v>
+        <v>-24816</v>
       </c>
       <c r="N120" t="n">
         <v>0</v>
@@ -7462,34 +7442,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>-23057477</v>
+        <v>-23200844</v>
       </c>
       <c r="F121" t="n">
-        <v>-23057477</v>
+        <v>-23200844</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H121" t="n">
-        <v>-29094979</v>
+        <v>-29187258</v>
       </c>
       <c r="I121" t="n">
-        <v>-26.18</v>
+        <v>-25.8</v>
       </c>
       <c r="J121" t="n">
-        <v>8924662</v>
+        <v>8878491</v>
       </c>
       <c r="K121" t="n">
-        <v>8992683</v>
+        <v>8942131</v>
       </c>
       <c r="L121" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="M121" t="n">
-        <v>8992683</v>
+        <v>8942131</v>
       </c>
       <c r="N121" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="122">
@@ -7514,34 +7494,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>11571024</v>
+        <v>11610773</v>
       </c>
       <c r="F122" t="n">
-        <v>11571024</v>
+        <v>11610773</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>5533522</v>
+        <v>5624359</v>
       </c>
       <c r="I122" t="n">
-        <v>-52.18</v>
+        <v>-51.56</v>
       </c>
       <c r="J122" t="n">
-        <v>-5347843</v>
+        <v>-5315372</v>
       </c>
       <c r="K122" t="n">
-        <v>-5375288</v>
+        <v>-5341049</v>
       </c>
       <c r="L122" t="n">
-        <v>-0.51</v>
+        <v>-0.48</v>
       </c>
       <c r="M122" t="n">
-        <v>-5375288</v>
+        <v>-5341049</v>
       </c>
       <c r="N122" t="n">
-        <v>-0.51</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="123">
@@ -7566,34 +7546,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>28877562</v>
+        <v>28977216</v>
       </c>
       <c r="F123" t="n">
-        <v>28877562</v>
+        <v>28977216</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>22840060</v>
+        <v>22990802</v>
       </c>
       <c r="I123" t="n">
-        <v>-20.91</v>
+        <v>-20.66</v>
       </c>
       <c r="J123" t="n">
-        <v>-13403840</v>
+        <v>-13322407</v>
       </c>
       <c r="K123" t="n">
-        <v>-13472495</v>
+        <v>-13386640</v>
       </c>
       <c r="L123" t="n">
-        <v>-0.51</v>
+        <v>-0.48</v>
       </c>
       <c r="M123" t="n">
-        <v>-13472495</v>
+        <v>-13386640</v>
       </c>
       <c r="N123" t="n">
-        <v>-0.51</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="124">
@@ -7618,34 +7598,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>-29045040</v>
+        <v>-29143817</v>
       </c>
       <c r="F124" t="n">
-        <v>-29045040</v>
+        <v>-29143817</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>-35082542</v>
+        <v>-35130231</v>
       </c>
       <c r="I124" t="n">
-        <v>-20.79</v>
+        <v>-20.54</v>
       </c>
       <c r="J124" t="n">
-        <v>13290402</v>
+        <v>13209812</v>
       </c>
       <c r="K124" t="n">
-        <v>13358914</v>
+        <v>13273911</v>
       </c>
       <c r="L124" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="M124" t="n">
-        <v>13358914</v>
+        <v>13273911</v>
       </c>
       <c r="N124" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="125">
@@ -7670,34 +7650,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>32041452</v>
+        <v>32208709</v>
       </c>
       <c r="F125" t="n">
-        <v>32041452</v>
+        <v>32208709</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>26003950</v>
+        <v>26222295</v>
       </c>
       <c r="I125" t="n">
-        <v>-18.84</v>
+        <v>-18.59</v>
       </c>
       <c r="J125" t="n">
-        <v>-13386891</v>
+        <v>-13312668</v>
       </c>
       <c r="K125" t="n">
-        <v>-13475249</v>
+        <v>-13395334</v>
       </c>
       <c r="L125" t="n">
-        <v>-0.66</v>
+        <v>-0.62</v>
       </c>
       <c r="M125" t="n">
-        <v>-13475249</v>
+        <v>-13395334</v>
       </c>
       <c r="N125" t="n">
-        <v>-0.66</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="126">
@@ -7722,34 +7702,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>-32233270</v>
+        <v>-32400695</v>
       </c>
       <c r="F126" t="n">
-        <v>-32233270</v>
+        <v>-32400695</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>-38270772</v>
+        <v>-38387109</v>
       </c>
       <c r="I126" t="n">
-        <v>-18.73</v>
+        <v>-18.48</v>
       </c>
       <c r="J126" t="n">
-        <v>13281875</v>
+        <v>13208438</v>
       </c>
       <c r="K126" t="n">
-        <v>13369996</v>
+        <v>13290883</v>
       </c>
       <c r="L126" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="M126" t="n">
-        <v>13369996</v>
+        <v>13290883</v>
       </c>
       <c r="N126" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="127">
@@ -7774,34 +7754,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>17630245</v>
+        <v>17750436</v>
       </c>
       <c r="F127" t="n">
-        <v>17630245</v>
+        <v>17750436</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>11592743</v>
+        <v>11764022</v>
       </c>
       <c r="I127" t="n">
-        <v>-34.25</v>
+        <v>-33.73</v>
       </c>
       <c r="J127" t="n">
-        <v>-6615411</v>
+        <v>-6582613</v>
       </c>
       <c r="K127" t="n">
-        <v>-6669811</v>
+        <v>-6633509</v>
       </c>
       <c r="L127" t="n">
-        <v>-0.82</v>
+        <v>-0.77</v>
       </c>
       <c r="M127" t="n">
-        <v>-6669811</v>
+        <v>-6633509</v>
       </c>
       <c r="N127" t="n">
-        <v>-0.82</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="128">
@@ -7826,34 +7806,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4759372</v>
+        <v>4819367</v>
       </c>
       <c r="F128" t="n">
-        <v>4759372</v>
+        <v>4819367</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>8169056</v>
+        <v>8238158</v>
       </c>
       <c r="I128" t="n">
-        <v>71.64</v>
+        <v>70.94</v>
       </c>
       <c r="J128" t="n">
-        <v>-274469</v>
+        <v>-201955</v>
       </c>
       <c r="K128" t="n">
-        <v>-274469</v>
+        <v>-201955</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M128" t="n">
-        <v>-274469</v>
+        <v>-201955</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="129">
@@ -7878,34 +7858,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>-1891964</v>
+        <v>-1920362</v>
       </c>
       <c r="F129" t="n">
-        <v>-1891964</v>
+        <v>-1920362</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>1517720</v>
+        <v>1498429</v>
       </c>
       <c r="I129" t="n">
-        <v>180.22</v>
+        <v>178.03</v>
       </c>
       <c r="J129" t="n">
-        <v>110039</v>
+        <v>80757</v>
       </c>
       <c r="K129" t="n">
-        <v>110039</v>
+        <v>80757</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M129" t="n">
-        <v>110039</v>
+        <v>80757</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="130">
@@ -7930,31 +7910,31 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>-4727906</v>
+        <v>-4799439</v>
       </c>
       <c r="F130" t="n">
-        <v>-4727906</v>
+        <v>-4799439</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>-1318222</v>
+        <v>-1380648</v>
       </c>
       <c r="I130" t="n">
-        <v>72.12</v>
+        <v>71.23</v>
       </c>
       <c r="J130" t="n">
-        <v>275312</v>
+        <v>202022</v>
       </c>
       <c r="K130" t="n">
-        <v>275312</v>
+        <v>202022</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>275312</v>
+        <v>202022</v>
       </c>
       <c r="N130" t="n">
         <v>0</v>
@@ -7982,34 +7962,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4734365</v>
+        <v>4804333</v>
       </c>
       <c r="F131" t="n">
-        <v>4734365</v>
+        <v>4804333</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>8144049</v>
+        <v>8223124</v>
       </c>
       <c r="I131" t="n">
-        <v>72.02</v>
+        <v>71.16</v>
       </c>
       <c r="J131" t="n">
-        <v>-274955</v>
+        <v>-201863</v>
       </c>
       <c r="K131" t="n">
-        <v>-274955</v>
+        <v>-201863</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M131" t="n">
-        <v>-274955</v>
+        <v>-201863</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="132">
@@ -8034,34 +8014,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>-6125965</v>
+        <v>-6211727</v>
       </c>
       <c r="F132" t="n">
-        <v>-6125965</v>
+        <v>-6211727</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>-2716281</v>
+        <v>-2792936</v>
       </c>
       <c r="I132" t="n">
-        <v>55.66</v>
+        <v>55.04</v>
       </c>
       <c r="J132" t="n">
-        <v>355536</v>
+        <v>261185</v>
       </c>
       <c r="K132" t="n">
-        <v>355536</v>
+        <v>261185</v>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M132" t="n">
-        <v>355536</v>
+        <v>261185</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="133">
@@ -8086,34 +8066,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6145044</v>
+        <v>6226302</v>
       </c>
       <c r="F133" t="n">
-        <v>6145044</v>
+        <v>6226302</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>9554728</v>
+        <v>9645093</v>
       </c>
       <c r="I133" t="n">
-        <v>55.49</v>
+        <v>54.91</v>
       </c>
       <c r="J133" t="n">
-        <v>-354980</v>
+        <v>-261034</v>
       </c>
       <c r="K133" t="n">
-        <v>-354980</v>
+        <v>-261034</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M133" t="n">
-        <v>-354980</v>
+        <v>-261034</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="134">
@@ -8138,34 +8118,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>-3802093</v>
+        <v>-3849882</v>
       </c>
       <c r="F134" t="n">
-        <v>-3802093</v>
+        <v>-3849882</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>-392409</v>
+        <v>-431091</v>
       </c>
       <c r="I134" t="n">
-        <v>89.68000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="J134" t="n">
-        <v>219525</v>
+        <v>161509</v>
       </c>
       <c r="K134" t="n">
-        <v>219525</v>
+        <v>161509</v>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M134" t="n">
-        <v>219525</v>
+        <v>161509</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="135">
@@ -8190,31 +8170,31 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>-9513107</v>
+        <v>-9579136</v>
       </c>
       <c r="F135" t="n">
-        <v>-9513107</v>
+        <v>-9579136</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>-16385265</v>
+        <v>-16385507</v>
       </c>
       <c r="I135" t="n">
-        <v>-72.23999999999999</v>
+        <v>-71.05</v>
       </c>
       <c r="J135" t="n">
-        <v>505782</v>
+        <v>496357</v>
       </c>
       <c r="K135" t="n">
-        <v>505782</v>
+        <v>496357</v>
       </c>
       <c r="L135" t="n">
         <v>-0</v>
       </c>
       <c r="M135" t="n">
-        <v>505782</v>
+        <v>496357</v>
       </c>
       <c r="N135" t="n">
         <v>-0</v>
@@ -8242,34 +8222,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3800933</v>
+        <v>3804480</v>
       </c>
       <c r="F136" t="n">
-        <v>3800933</v>
+        <v>3804480</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>-3071225</v>
+        <v>-3001891</v>
       </c>
       <c r="I136" t="n">
-        <v>-180.8</v>
+        <v>-178.9</v>
       </c>
       <c r="J136" t="n">
-        <v>-202748</v>
+        <v>-198954</v>
       </c>
       <c r="K136" t="n">
-        <v>-202748</v>
+        <v>-198954</v>
       </c>
       <c r="L136" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>-202748</v>
+        <v>-198954</v>
       </c>
       <c r="N136" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -8294,31 +8274,31 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>9498436</v>
+        <v>9507572</v>
       </c>
       <c r="F137" t="n">
-        <v>9498436</v>
+        <v>9507572</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>2626278</v>
+        <v>2701201</v>
       </c>
       <c r="I137" t="n">
-        <v>-72.34999999999999</v>
+        <v>-71.59</v>
       </c>
       <c r="J137" t="n">
-        <v>-507118</v>
+        <v>-497659</v>
       </c>
       <c r="K137" t="n">
-        <v>-507118</v>
+        <v>-497659</v>
       </c>
       <c r="L137" t="n">
         <v>-0</v>
       </c>
       <c r="M137" t="n">
-        <v>-507118</v>
+        <v>-497659</v>
       </c>
       <c r="N137" t="n">
         <v>-0</v>
@@ -8346,34 +8326,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>-9510103</v>
+        <v>-9519330</v>
       </c>
       <c r="F138" t="n">
-        <v>-9510103</v>
+        <v>-9519330</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>-16382261</v>
+        <v>-16325701</v>
       </c>
       <c r="I138" t="n">
-        <v>-72.26000000000001</v>
+        <v>-71.5</v>
       </c>
       <c r="J138" t="n">
-        <v>506410</v>
+        <v>496910</v>
       </c>
       <c r="K138" t="n">
-        <v>506410</v>
+        <v>496910</v>
       </c>
       <c r="L138" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>506410</v>
+        <v>496910</v>
       </c>
       <c r="N138" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -8398,34 +8378,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>12274286</v>
+        <v>12325875</v>
       </c>
       <c r="F139" t="n">
-        <v>12274286</v>
+        <v>12325875</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>5402128</v>
+        <v>5519504</v>
       </c>
       <c r="I139" t="n">
-        <v>-55.99</v>
+        <v>-55.22</v>
       </c>
       <c r="J139" t="n">
-        <v>-655035</v>
+        <v>-642874</v>
       </c>
       <c r="K139" t="n">
-        <v>-655035</v>
+        <v>-642874</v>
       </c>
       <c r="L139" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>-655035</v>
+        <v>-642874</v>
       </c>
       <c r="N139" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -8450,31 +8430,31 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>-12301507</v>
+        <v>-12364019</v>
       </c>
       <c r="F140" t="n">
-        <v>-12301507</v>
+        <v>-12364019</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>-19173665</v>
+        <v>-19170390</v>
       </c>
       <c r="I140" t="n">
-        <v>-55.86</v>
+        <v>-55.05</v>
       </c>
       <c r="J140" t="n">
-        <v>654079</v>
+        <v>641851</v>
       </c>
       <c r="K140" t="n">
-        <v>654079</v>
+        <v>641851</v>
       </c>
       <c r="L140" t="n">
         <v>-0</v>
       </c>
       <c r="M140" t="n">
-        <v>654079</v>
+        <v>641851</v>
       </c>
       <c r="N140" t="n">
         <v>-0</v>
@@ -8502,34 +8482,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>7594729</v>
+        <v>7654488</v>
       </c>
       <c r="F141" t="n">
-        <v>7594729</v>
+        <v>7654488</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>722571</v>
+        <v>848117</v>
       </c>
       <c r="I141" t="n">
-        <v>-90.48999999999999</v>
+        <v>-88.92</v>
       </c>
       <c r="J141" t="n">
-        <v>-404630</v>
+        <v>-397134</v>
       </c>
       <c r="K141" t="n">
-        <v>-404630</v>
+        <v>-397134</v>
       </c>
       <c r="L141" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>-404630</v>
+        <v>-397134</v>
       </c>
       <c r="N141" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -8627,13 +8607,13 @@
         <v>-8143731</v>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M143" t="n">
         <v>-8143731</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="144">
@@ -8954,10 +8934,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.8046</v>
+        <v>2.7826</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8046</v>
+        <v>2.7826</v>
       </c>
       <c r="D2" t="n">
         <v>-0</v>
@@ -9065,10 +9045,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>537319930</v>
+        <v>464115515</v>
       </c>
       <c r="E2" t="n">
-        <v>537319930</v>
+        <v>464115515</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -9103,10 +9083,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2171503039</v>
+        <v>1916356062</v>
       </c>
       <c r="E3" t="n">
-        <v>2171503039</v>
+        <v>1916356062</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -9141,22 +9121,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33204891</v>
+        <v>35717003</v>
       </c>
       <c r="E4" t="n">
-        <v>33138954</v>
+        <v>35414190</v>
       </c>
       <c r="F4" t="n">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
       <c r="G4" t="n">
-        <v>2.76</v>
+        <v>2.95</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2</v>
+        <v>-0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.005</v>
+        <v>-0.025</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -9187,26 +9167,26 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-129744181</v>
+        <v>-122122222</v>
       </c>
       <c r="E5" t="n">
-        <v>-129675664</v>
+        <v>-126174091</v>
       </c>
       <c r="F5" t="n">
-        <v>-10.81</v>
+        <v>-10.18</v>
       </c>
       <c r="G5" t="n">
-        <v>-10.81</v>
+        <v>-10.51</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05</v>
+        <v>-3.32</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006</v>
+        <v>-0.338</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -9233,22 +9213,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-36949559</v>
+        <v>-39402457</v>
       </c>
       <c r="E6" t="n">
-        <v>-36872218</v>
+        <v>-39092145</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.08</v>
+        <v>-3.28</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.07</v>
+        <v>-3.26</v>
       </c>
       <c r="H6" t="n">
-        <v>0.21</v>
+        <v>0.79</v>
       </c>
       <c r="I6" t="n">
-        <v>0.006</v>
+        <v>0.026</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -9279,26 +9259,26 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>141408971</v>
+        <v>133536849</v>
       </c>
       <c r="E7" t="n">
-        <v>141340319</v>
+        <v>137940218</v>
       </c>
       <c r="F7" t="n">
-        <v>11.78</v>
+        <v>11.13</v>
       </c>
       <c r="G7" t="n">
-        <v>11.78</v>
+        <v>11.5</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.05</v>
+        <v>3.3</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.006</v>
+        <v>0.367</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -9325,22 +9305,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24037177</v>
+        <v>24954859</v>
       </c>
       <c r="E8" t="n">
-        <v>24164877</v>
+        <v>24977852</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="H8" t="n">
-        <v>0.53</v>
+        <v>0.09</v>
       </c>
       <c r="I8" t="n">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -9371,26 +9351,26 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-46407742</v>
+        <v>-46096958</v>
       </c>
       <c r="E9" t="n">
-        <v>-46462133</v>
+        <v>-47913953</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.87</v>
+        <v>-3.84</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.87</v>
+        <v>-3.99</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.12</v>
+        <v>-3.94</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.005</v>
+        <v>-0.151</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -9417,22 +9397,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-25108558</v>
+        <v>-25784012</v>
       </c>
       <c r="E10" t="n">
-        <v>-25250102</v>
+        <v>-25843503</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.09</v>
+        <v>-2.15</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1</v>
+        <v>-2.15</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.23</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.012</v>
+        <v>-0.005</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -9463,26 +9443,26 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>34556911</v>
+        <v>35246098</v>
       </c>
       <c r="E11" t="n">
-        <v>34624930</v>
+        <v>36716749</v>
       </c>
       <c r="F11" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="G11" t="n">
-        <v>2.89</v>
+        <v>3.06</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2</v>
+        <v>4.17</v>
       </c>
       <c r="I11" t="n">
-        <v>0.006</v>
+        <v>0.123</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -9509,22 +9489,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-8558612</v>
+        <v>-8155775</v>
       </c>
       <c r="E12" t="n">
-        <v>-8712696</v>
+        <v>-8331223</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.71</v>
+        <v>-0.68</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.73</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.8</v>
+        <v>-2.15</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.013</v>
+        <v>-0.015</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -9555,26 +9535,26 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-24200463</v>
+        <v>-20497479</v>
       </c>
       <c r="E13" t="n">
-        <v>-24112338</v>
+        <v>-20902971</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.02</v>
+        <v>-1.71</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.01</v>
+        <v>-1.74</v>
       </c>
       <c r="H13" t="n">
-        <v>0.36</v>
+        <v>-1.98</v>
       </c>
       <c r="I13" t="n">
-        <v>0.007</v>
+        <v>-0.034</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -9601,10 +9581,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4684805</v>
+        <v>4659881</v>
       </c>
       <c r="E14" t="n">
-        <v>4845904</v>
+        <v>4842098</v>
       </c>
       <c r="F14" t="n">
         <v>0.39</v>
@@ -9613,10 +9593,10 @@
         <v>0.4</v>
       </c>
       <c r="H14" t="n">
-        <v>3.44</v>
+        <v>3.91</v>
       </c>
       <c r="I14" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -9647,26 +9627,26 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24623321</v>
+        <v>20867291</v>
       </c>
       <c r="E15" t="n">
-        <v>24534967</v>
+        <v>21277061</v>
       </c>
       <c r="F15" t="n">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="G15" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.36</v>
+        <v>1.96</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.007</v>
+        <v>0.034</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -9693,22 +9673,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-15844724</v>
+        <v>-16848137</v>
       </c>
       <c r="E16" t="n">
-        <v>-15812299</v>
+        <v>-16722189</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.32</v>
+        <v>-1.4</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.32</v>
+        <v>-1.39</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="I16" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -9739,26 +9719,26 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>55139885</v>
+        <v>52023150</v>
       </c>
       <c r="E17" t="n">
-        <v>55112114</v>
+        <v>53744178</v>
       </c>
       <c r="F17" t="n">
-        <v>4.59</v>
+        <v>4.34</v>
       </c>
       <c r="G17" t="n">
-        <v>4.59</v>
+        <v>4.48</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.05</v>
+        <v>3.31</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.002</v>
+        <v>0.143</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -9940,20 +9920,20 @@
         <v>1500000000</v>
       </c>
       <c r="E2" t="n">
-        <v>13.7486</v>
+        <v>10.2985</v>
       </c>
       <c r="F2" t="n">
-        <v>13.7486</v>
+        <v>10.2985</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.196192</v>
+        <v>1.117813</v>
       </c>
       <c r="J2" t="n">
-        <v>1.196192</v>
+        <v>1.117813</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -9982,20 +9962,20 @@
         <v>900000000</v>
       </c>
       <c r="E3" t="n">
-        <v>11.5493</v>
+        <v>10.2937</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5493</v>
+        <v>10.2937</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.207404</v>
+        <v>1.177879</v>
       </c>
       <c r="J3" t="n">
-        <v>1.207404</v>
+        <v>1.177879</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -10024,20 +10004,20 @@
         <v>1000000000</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3072</v>
+        <v>6.6434</v>
       </c>
       <c r="F4" t="n">
-        <v>6.3072</v>
+        <v>6.6434</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1.043021</v>
+        <v>1.043147</v>
       </c>
       <c r="J4" t="n">
-        <v>1.043021</v>
+        <v>1.043147</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -10066,20 +10046,20 @@
         <v>2800000000</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7584</v>
+        <v>5.8888</v>
       </c>
       <c r="F5" t="n">
-        <v>5.7584</v>
+        <v>5.8888</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1.072311</v>
+        <v>1.072207</v>
       </c>
       <c r="J5" t="n">
-        <v>1.072311</v>
+        <v>1.072207</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -10108,20 +10088,20 @@
         <v>600000000</v>
       </c>
       <c r="E6" t="n">
-        <v>5.2727</v>
+        <v>4.6291</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2727</v>
+        <v>4.6291</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1.040992</v>
+        <v>1.019719</v>
       </c>
       <c r="J6" t="n">
-        <v>1.040992</v>
+        <v>1.019719</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -10150,24 +10130,22 @@
         <v>1500000000</v>
       </c>
       <c r="E7" t="n">
-        <v>5.2575</v>
+        <v>4.5106</v>
       </c>
       <c r="F7" t="n">
-        <v>5.2575</v>
+        <v>4.5106</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1.047301</v>
+        <v>0.986509</v>
       </c>
       <c r="J7" t="n">
-        <v>1.047301</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
+        <v>0.986509</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="b">
         <v>1</v>
       </c>
@@ -10232,20 +10210,20 @@
         <v>1100000000</v>
       </c>
       <c r="E9" t="n">
-        <v>4.0867</v>
+        <v>3.9931</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0867</v>
+        <v>3.9931</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.009804</v>
+        <v>1.005995</v>
       </c>
       <c r="J9" t="n">
-        <v>1.009804</v>
+        <v>1.005995</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -10274,20 +10252,20 @@
         <v>200000000</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7523</v>
+        <v>3.7569</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7523</v>
+        <v>3.7569</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.000005</v>
+        <v>1.000007</v>
       </c>
       <c r="J10" t="n">
-        <v>1.000005</v>
+        <v>1.000007</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -10316,20 +10294,20 @@
         <v>200000000</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0085</v>
+        <v>2.99</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0085</v>
+        <v>2.99</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9999980000000001</v>
+        <v>0.999814</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9999980000000001</v>
+        <v>0.999814</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="b">
@@ -10556,10 +10534,10 @@
         <v>400000000</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0003</v>
+        <v>-0.1</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0003</v>
+        <v>-0.1</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="b">
@@ -10636,20 +10614,20 @@
         <v>2100000000</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3301</v>
+        <v>-3.3327</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.3301</v>
+        <v>-3.3327</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.983182</v>
+        <v>-0.984198</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.983182</v>
+        <v>-0.984198</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="b">
@@ -10676,10 +10654,10 @@
         <v>400000000</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.7655</v>
+        <v>-3.7491</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.7655</v>
+        <v>-3.7491</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="b">
@@ -10758,20 +10736,20 @@
         <v>1200000000</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.903</v>
+        <v>-3.9573</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.903</v>
+        <v>-3.9573</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.006132</v>
+        <v>-1.006574</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.006132</v>
+        <v>-1.006574</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>

--- a/optimize_prep/output/approx_accuracy_report.xlsx
+++ b/optimize_prep/output/approx_accuracy_report.xlsx
@@ -598,28 +598,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>66433964</v>
+        <v>65253624</v>
       </c>
       <c r="E4" t="n">
-        <v>66433964</v>
+        <v>65253624</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G4" t="n">
-        <v>57254522</v>
+        <v>56288687</v>
       </c>
       <c r="H4" t="n">
-        <v>-13.82</v>
+        <v>-13.74</v>
       </c>
       <c r="I4" t="n">
-        <v>9179442</v>
+        <v>8964937</v>
       </c>
       <c r="J4" t="n">
-        <v>1043146798</v>
+        <v>1042283026</v>
       </c>
       <c r="K4" t="n">
-        <v>1043146798</v>
+        <v>1042283026</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
@@ -645,34 +645,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>164885641</v>
+        <v>164885287</v>
       </c>
       <c r="E5" t="n">
-        <v>164885641</v>
+        <v>164885287</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>107746730</v>
+        <v>107706034</v>
       </c>
       <c r="H5" t="n">
-        <v>-34.65</v>
+        <v>-34.68</v>
       </c>
       <c r="I5" t="n">
-        <v>57138911</v>
+        <v>57179252</v>
       </c>
       <c r="J5" t="n">
-        <v>3002180524</v>
+        <v>3001937537</v>
       </c>
       <c r="K5" t="n">
-        <v>3002180524</v>
+        <v>3001937537</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -692,34 +692,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>92643144</v>
+        <v>92105700</v>
       </c>
       <c r="E6" t="n">
-        <v>92643144</v>
+        <v>92105700</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>85619425</v>
+        <v>85103123</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.58</v>
+        <v>-7.6</v>
       </c>
       <c r="I6" t="n">
-        <v>7023719</v>
+        <v>7002577</v>
       </c>
       <c r="J6" t="n">
-        <v>1060091176</v>
+        <v>1058263829</v>
       </c>
       <c r="K6" t="n">
-        <v>1060091176</v>
+        <v>1058263829</v>
       </c>
       <c r="L6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -739,28 +739,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>154477297</v>
+        <v>154887878</v>
       </c>
       <c r="E7" t="n">
-        <v>154477297</v>
+        <v>154887878</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>80202054</v>
+        <v>80260490</v>
       </c>
       <c r="H7" t="n">
-        <v>-48.08</v>
+        <v>-48.18</v>
       </c>
       <c r="I7" t="n">
-        <v>74275242</v>
+        <v>74627388</v>
       </c>
       <c r="J7" t="n">
-        <v>1676720105</v>
+        <v>1677452673</v>
       </c>
       <c r="K7" t="n">
-        <v>1676720105</v>
+        <v>1677452673</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -786,31 +786,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>67658549</v>
+        <v>76477448</v>
       </c>
       <c r="E8" t="n">
-        <v>67658549</v>
+        <v>76477448</v>
       </c>
       <c r="F8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>63444985</v>
+        <v>71409164</v>
       </c>
       <c r="H8" t="n">
-        <v>-6.23</v>
+        <v>-6.63</v>
       </c>
       <c r="I8" t="n">
-        <v>4213564</v>
+        <v>5068283</v>
       </c>
       <c r="J8" t="n">
-        <v>1479763824</v>
+        <v>1568568600</v>
       </c>
       <c r="K8" t="n">
-        <v>1479763824</v>
+        <v>1568568600</v>
       </c>
       <c r="L8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -833,28 +833,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>43924306</v>
+        <v>43186104</v>
       </c>
       <c r="E9" t="n">
-        <v>43924306</v>
+        <v>43186104</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>42636355</v>
+        <v>42960888</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.93</v>
+        <v>-0.52</v>
       </c>
       <c r="I9" t="n">
-        <v>1287951</v>
+        <v>225216</v>
       </c>
       <c r="J9" t="n">
-        <v>1106594600</v>
+        <v>1113622270</v>
       </c>
       <c r="K9" t="n">
-        <v>1106594600</v>
+        <v>1113622270</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -968,28 +968,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>27774559</v>
+        <v>28060724</v>
       </c>
       <c r="E12" t="n">
-        <v>27774559</v>
+        <v>28060724</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>19616512</v>
+        <v>19451527</v>
       </c>
       <c r="H12" t="n">
-        <v>-29.37</v>
+        <v>-30.68</v>
       </c>
       <c r="I12" t="n">
-        <v>8158048</v>
+        <v>8609198</v>
       </c>
       <c r="J12" t="n">
-        <v>611831340</v>
+        <v>612118920</v>
       </c>
       <c r="K12" t="n">
-        <v>611831340</v>
+        <v>612118920</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1015,28 +1015,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-47487862</v>
+        <v>-48173434</v>
       </c>
       <c r="E13" t="n">
-        <v>-47487862</v>
+        <v>-48173434</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-45552669</v>
+        <v>-45909607</v>
       </c>
       <c r="H13" t="n">
-        <v>4.08</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>-1935193</v>
+        <v>-2263827</v>
       </c>
       <c r="J13" t="n">
-        <v>-1207888863</v>
+        <v>-1212705704</v>
       </c>
       <c r="K13" t="n">
-        <v>-1207888863</v>
+        <v>-1212705704</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1275,34 +1275,34 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-69987510</v>
+        <v>-71131080</v>
       </c>
       <c r="E19" t="n">
-        <v>-69987510</v>
+        <v>-71131080</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-64001096</v>
+        <v>-64819313</v>
       </c>
       <c r="H19" t="n">
-        <v>8.550000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-5986414</v>
+        <v>-6311767</v>
       </c>
       <c r="J19" t="n">
-        <v>-2066815357</v>
+        <v>-2097526175</v>
       </c>
       <c r="K19" t="n">
-        <v>-2066815357</v>
+        <v>-2097526175</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="20">
@@ -1322,28 +1322,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7513798</v>
+        <v>7525633</v>
       </c>
       <c r="E20" t="n">
-        <v>7513798</v>
+        <v>7525633</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>4095007</v>
+        <v>4095011</v>
       </c>
       <c r="H20" t="n">
-        <v>-45.5</v>
+        <v>-45.59</v>
       </c>
       <c r="I20" t="n">
-        <v>3418791</v>
+        <v>3430622</v>
       </c>
       <c r="J20" t="n">
-        <v>200001320</v>
+        <v>200001276</v>
       </c>
       <c r="K20" t="n">
-        <v>200001320</v>
+        <v>200001276</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1369,34 +1369,34 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-14996405</v>
+        <v>-15032414</v>
       </c>
       <c r="E21" t="n">
-        <v>-14996405</v>
+        <v>-15032414</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-8190034</v>
+        <v>-8190037</v>
       </c>
       <c r="H21" t="n">
-        <v>45.39</v>
+        <v>45.52</v>
       </c>
       <c r="I21" t="n">
-        <v>-6806371</v>
+        <v>-6842376</v>
       </c>
       <c r="J21" t="n">
-        <v>-400002036</v>
+        <v>-400002685</v>
       </c>
       <c r="K21" t="n">
-        <v>-400002036</v>
+        <v>-400002685</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2254,34 +2254,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>430564</v>
+        <v>473638</v>
       </c>
       <c r="F16" t="n">
-        <v>430564</v>
+        <v>473638</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9610006</v>
+        <v>9438575</v>
       </c>
       <c r="I16" t="n">
-        <v>2131.96</v>
+        <v>1892.78</v>
       </c>
       <c r="J16" t="n">
-        <v>19002876</v>
+        <v>19194820</v>
       </c>
       <c r="K16" t="n">
-        <v>19002876</v>
+        <v>19194821</v>
       </c>
       <c r="L16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>19002876</v>
+        <v>19194821</v>
       </c>
       <c r="N16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2306,34 +2306,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-2191248</v>
+        <v>-2130070</v>
       </c>
       <c r="F17" t="n">
-        <v>-2191248</v>
+        <v>-2130070</v>
       </c>
       <c r="G17" t="n">
         <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>6988194</v>
+        <v>6834867</v>
       </c>
       <c r="I17" t="n">
-        <v>418.91</v>
+        <v>420.88</v>
       </c>
       <c r="J17" t="n">
-        <v>24485629</v>
+        <v>24623878</v>
       </c>
       <c r="K17" t="n">
-        <v>24485628</v>
+        <v>24623880</v>
       </c>
       <c r="L17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>24485628</v>
+        <v>24623880</v>
       </c>
       <c r="N17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2358,31 +2358,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>-4029924</v>
+        <v>-3958537</v>
       </c>
       <c r="F18" t="n">
-        <v>-4029924</v>
+        <v>-3958537</v>
       </c>
       <c r="G18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>5149518</v>
+        <v>5006400</v>
       </c>
       <c r="I18" t="n">
-        <v>227.78</v>
+        <v>226.47</v>
       </c>
       <c r="J18" t="n">
-        <v>62930026</v>
+        <v>63295493</v>
       </c>
       <c r="K18" t="n">
-        <v>62930024</v>
+        <v>63295491</v>
       </c>
       <c r="L18" t="n">
         <v>-0</v>
       </c>
       <c r="M18" t="n">
-        <v>62930024</v>
+        <v>63295491</v>
       </c>
       <c r="N18" t="n">
         <v>-0</v>
@@ -2410,31 +2410,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2107295</v>
+        <v>2144614</v>
       </c>
       <c r="F19" t="n">
-        <v>2107295</v>
+        <v>2144614</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>11286737</v>
+        <v>11109551</v>
       </c>
       <c r="I19" t="n">
-        <v>435.6</v>
+        <v>418.02</v>
       </c>
       <c r="J19" t="n">
-        <v>-57497801</v>
+        <v>-57801918</v>
       </c>
       <c r="K19" t="n">
-        <v>-57497801</v>
+        <v>-57801917</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-57497801</v>
+        <v>-57801917</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2462,34 +2462,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-3435361</v>
+        <v>-3364278</v>
       </c>
       <c r="F20" t="n">
-        <v>-3435361</v>
+        <v>-3364278</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5744081</v>
+        <v>5600659</v>
       </c>
       <c r="I20" t="n">
-        <v>267.2</v>
+        <v>266.47</v>
       </c>
       <c r="J20" t="n">
-        <v>7618238</v>
+        <v>7586251</v>
       </c>
       <c r="K20" t="n">
-        <v>7618237</v>
+        <v>7586254</v>
       </c>
       <c r="L20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7618237</v>
+        <v>7586254</v>
       </c>
       <c r="N20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2514,34 +2514,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1512138</v>
+        <v>1549594</v>
       </c>
       <c r="F21" t="n">
-        <v>1512138</v>
+        <v>1549594</v>
       </c>
       <c r="G21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>10691580</v>
+        <v>10514531</v>
       </c>
       <c r="I21" t="n">
-        <v>607.05</v>
+        <v>578.53</v>
       </c>
       <c r="J21" t="n">
-        <v>-7544580</v>
+        <v>-7512977</v>
       </c>
       <c r="K21" t="n">
-        <v>-7544582</v>
+        <v>-7512975</v>
       </c>
       <c r="L21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-7544582</v>
+        <v>-7512975</v>
       </c>
       <c r="N21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2566,34 +2566,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-1869275</v>
+        <v>-1806609</v>
       </c>
       <c r="F22" t="n">
-        <v>-1869275</v>
+        <v>-1806609</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>7310167</v>
+        <v>7158328</v>
       </c>
       <c r="I22" t="n">
-        <v>491.07</v>
+        <v>496.23</v>
       </c>
       <c r="J22" t="n">
-        <v>-23957566</v>
+        <v>-24161601</v>
       </c>
       <c r="K22" t="n">
-        <v>-23957568</v>
+        <v>-24161599</v>
       </c>
       <c r="L22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-23957568</v>
+        <v>-24161599</v>
       </c>
       <c r="N22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2618,31 +2618,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3804409</v>
+        <v>3990503</v>
       </c>
       <c r="F23" t="n">
-        <v>3804409</v>
+        <v>3990503</v>
       </c>
       <c r="G23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>60943320</v>
+        <v>61169755</v>
       </c>
       <c r="I23" t="n">
-        <v>1501.91</v>
+        <v>1432.88</v>
       </c>
       <c r="J23" t="n">
-        <v>-2001499</v>
+        <v>-1857125</v>
       </c>
       <c r="K23" t="n">
-        <v>-2001495</v>
+        <v>-1857123</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-2001495</v>
+        <v>-1857123</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2670,31 +2670,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-23403623</v>
+        <v>-23473924</v>
       </c>
       <c r="F24" t="n">
-        <v>-23403623</v>
+        <v>-23473923</v>
       </c>
       <c r="G24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>33735288</v>
+        <v>33705329</v>
       </c>
       <c r="I24" t="n">
-        <v>244.15</v>
+        <v>243.59</v>
       </c>
       <c r="J24" t="n">
-        <v>10423090</v>
+        <v>10323152</v>
       </c>
       <c r="K24" t="n">
-        <v>10421025</v>
+        <v>10321273</v>
       </c>
       <c r="L24" t="n">
         <v>-0.02</v>
       </c>
       <c r="M24" t="n">
-        <v>10421025</v>
+        <v>10321273</v>
       </c>
       <c r="N24" t="n">
         <v>-0.02</v>
@@ -2722,31 +2722,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-57902610</v>
+        <v>-58075390</v>
       </c>
       <c r="F25" t="n">
-        <v>-57902610</v>
+        <v>-58075390</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-763699</v>
+        <v>-896138</v>
       </c>
       <c r="I25" t="n">
-        <v>98.68000000000001</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>27012576</v>
+        <v>26759481</v>
       </c>
       <c r="K25" t="n">
-        <v>27012579</v>
+        <v>26759481</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>27012579</v>
+        <v>26759481</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2774,31 +2774,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>57261057</v>
+        <v>57430370</v>
       </c>
       <c r="F26" t="n">
-        <v>57261057</v>
+        <v>57430370</v>
       </c>
       <c r="G26" t="n">
         <v>-0</v>
       </c>
       <c r="H26" t="n">
-        <v>114399968</v>
+        <v>114609622</v>
       </c>
       <c r="I26" t="n">
-        <v>99.79000000000001</v>
+        <v>99.56</v>
       </c>
       <c r="J26" t="n">
-        <v>-23852215</v>
+        <v>-23604934</v>
       </c>
       <c r="K26" t="n">
-        <v>-23852212</v>
+        <v>-23604932</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-23852212</v>
+        <v>-23604932</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2826,34 +2826,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-27190918</v>
+        <v>-27428696</v>
       </c>
       <c r="F27" t="n">
-        <v>-27190918</v>
+        <v>-27428696</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H27" t="n">
-        <v>29947993</v>
+        <v>29750556</v>
       </c>
       <c r="I27" t="n">
-        <v>210.14</v>
+        <v>208.47</v>
       </c>
       <c r="J27" t="n">
-        <v>12398110</v>
+        <v>12168985</v>
       </c>
       <c r="K27" t="n">
-        <v>12398110</v>
+        <v>12168986</v>
       </c>
       <c r="L27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>12398110</v>
+        <v>12168986</v>
       </c>
       <c r="N27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2878,31 +2878,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>26469091</v>
+        <v>26703617</v>
       </c>
       <c r="F28" t="n">
-        <v>26469091</v>
+        <v>26703617</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>83608002</v>
+        <v>83882869</v>
       </c>
       <c r="I28" t="n">
-        <v>215.87</v>
+        <v>214.13</v>
       </c>
       <c r="J28" t="n">
-        <v>-12197188</v>
+        <v>-11967674</v>
       </c>
       <c r="K28" t="n">
-        <v>-12197188</v>
+        <v>-11967671</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-12197188</v>
+        <v>-11967671</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2930,34 +2930,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2932211</v>
+        <v>2778121</v>
       </c>
       <c r="F29" t="n">
-        <v>2932211</v>
+        <v>2778121</v>
       </c>
       <c r="G29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>60071122</v>
+        <v>59957373</v>
       </c>
       <c r="I29" t="n">
-        <v>1948.66</v>
+        <v>2058.2</v>
       </c>
       <c r="J29" t="n">
-        <v>-465165</v>
+        <v>-568119</v>
       </c>
       <c r="K29" t="n">
-        <v>-465160</v>
+        <v>-568121</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M29" t="n">
-        <v>-465160</v>
+        <v>-568121</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="30">
@@ -2982,31 +2982,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>715648</v>
+        <v>718913</v>
       </c>
       <c r="F30" t="n">
-        <v>715648</v>
+        <v>718913</v>
       </c>
       <c r="G30" t="n">
         <v>-0</v>
       </c>
       <c r="H30" t="n">
-        <v>7739367</v>
+        <v>7721490</v>
       </c>
       <c r="I30" t="n">
-        <v>981.45</v>
+        <v>974.05</v>
       </c>
       <c r="J30" t="n">
-        <v>26443001</v>
+        <v>26388806</v>
       </c>
       <c r="K30" t="n">
-        <v>26443002</v>
+        <v>26388806</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>26443002</v>
+        <v>26388806</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3034,31 +3034,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-771242</v>
+        <v>-767885</v>
       </c>
       <c r="F31" t="n">
-        <v>-771242</v>
+        <v>-767885</v>
       </c>
       <c r="G31" t="n">
         <v>-0</v>
       </c>
       <c r="H31" t="n">
-        <v>6252477</v>
+        <v>6234692</v>
       </c>
       <c r="I31" t="n">
-        <v>910.7</v>
+        <v>911.9299999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>30213071</v>
+        <v>30154667</v>
       </c>
       <c r="K31" t="n">
-        <v>30213072</v>
+        <v>30154667</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>30213072</v>
+        <v>30154667</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -3086,31 +3086,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-1843105</v>
+        <v>-1840040</v>
       </c>
       <c r="F32" t="n">
-        <v>-1843105</v>
+        <v>-1840040</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>5180614</v>
+        <v>5162537</v>
       </c>
       <c r="I32" t="n">
-        <v>381.08</v>
+        <v>380.57</v>
       </c>
       <c r="J32" t="n">
-        <v>77908278</v>
+        <v>77756948</v>
       </c>
       <c r="K32" t="n">
-        <v>77908278</v>
+        <v>77756949</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>77908278</v>
+        <v>77756949</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3138,31 +3138,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1734686</v>
+        <v>1738729</v>
       </c>
       <c r="F33" t="n">
-        <v>1734686</v>
+        <v>1738729</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H33" t="n">
-        <v>8758405</v>
+        <v>8741306</v>
       </c>
       <c r="I33" t="n">
-        <v>404.9</v>
+        <v>402.74</v>
       </c>
       <c r="J33" t="n">
-        <v>-70411472</v>
+        <v>-70276790</v>
       </c>
       <c r="K33" t="n">
-        <v>-70411472</v>
+        <v>-70276788</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-70411472</v>
+        <v>-70276788</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -3190,31 +3190,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-1459681</v>
+        <v>-1456054</v>
       </c>
       <c r="F34" t="n">
-        <v>-1459681</v>
+        <v>-1456054</v>
       </c>
       <c r="G34" t="n">
         <v>-0</v>
       </c>
       <c r="H34" t="n">
-        <v>5564038</v>
+        <v>5546523</v>
       </c>
       <c r="I34" t="n">
-        <v>481.18</v>
+        <v>480.93</v>
       </c>
       <c r="J34" t="n">
-        <v>6741951</v>
+        <v>6731618</v>
       </c>
       <c r="K34" t="n">
-        <v>6741952</v>
+        <v>6731620</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>6741952</v>
+        <v>6731620</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -3242,34 +3242,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1350662</v>
+        <v>1354155</v>
       </c>
       <c r="F35" t="n">
-        <v>1350662</v>
+        <v>1354155</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H35" t="n">
-        <v>8374381</v>
+        <v>8356732</v>
       </c>
       <c r="I35" t="n">
-        <v>520.02</v>
+        <v>517.12</v>
       </c>
       <c r="J35" t="n">
-        <v>-6679264</v>
+        <v>-6669023</v>
       </c>
       <c r="K35" t="n">
-        <v>-6679263</v>
+        <v>-6669023</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M35" t="n">
-        <v>-6679263</v>
+        <v>-6669023</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="36">
@@ -3294,31 +3294,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-545200</v>
+        <v>-541320</v>
       </c>
       <c r="F36" t="n">
-        <v>-545200</v>
+        <v>-541320</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H36" t="n">
-        <v>6478519</v>
+        <v>6461257</v>
       </c>
       <c r="I36" t="n">
-        <v>1288.28</v>
+        <v>1293.61</v>
       </c>
       <c r="J36" t="n">
-        <v>-32073591</v>
+        <v>-32009396</v>
       </c>
       <c r="K36" t="n">
-        <v>-32073590</v>
+        <v>-32009396</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-32073590</v>
+        <v>-32009396</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -3346,31 +3346,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-356232</v>
+        <v>-346899</v>
       </c>
       <c r="F37" t="n">
-        <v>-450129</v>
+        <v>-442922</v>
       </c>
       <c r="G37" t="n">
-        <v>-26.36</v>
+        <v>-27.68</v>
       </c>
       <c r="H37" t="n">
-        <v>73825113</v>
+        <v>74184466</v>
       </c>
       <c r="I37" t="n">
-        <v>20823.87</v>
+        <v>21485.02</v>
       </c>
       <c r="J37" t="n">
-        <v>-6375645</v>
+        <v>-6363699</v>
       </c>
       <c r="K37" t="n">
-        <v>-6375647</v>
+        <v>-6363701</v>
       </c>
       <c r="L37" t="n">
         <v>-0</v>
       </c>
       <c r="M37" t="n">
-        <v>-6375647</v>
+        <v>-6363701</v>
       </c>
       <c r="N37" t="n">
         <v>-0</v>
@@ -3398,31 +3398,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-9751659</v>
+        <v>-9763715</v>
       </c>
       <c r="F38" t="n">
-        <v>-9752279</v>
+        <v>-9764310</v>
       </c>
       <c r="G38" t="n">
         <v>-0.01</v>
       </c>
       <c r="H38" t="n">
-        <v>64522963</v>
+        <v>64863078</v>
       </c>
       <c r="I38" t="n">
-        <v>761.66</v>
+        <v>764.33</v>
       </c>
       <c r="J38" t="n">
-        <v>7809893</v>
+        <v>7808258</v>
       </c>
       <c r="K38" t="n">
-        <v>7809642</v>
+        <v>7807938</v>
       </c>
       <c r="L38" t="n">
         <v>-0</v>
       </c>
       <c r="M38" t="n">
-        <v>7809642</v>
+        <v>7807938</v>
       </c>
       <c r="N38" t="n">
         <v>-0</v>
@@ -3450,34 +3450,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-23821566</v>
+        <v>-23849478</v>
       </c>
       <c r="F39" t="n">
-        <v>-23821570</v>
+        <v>-23849468</v>
       </c>
       <c r="G39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>50453672</v>
+        <v>50777920</v>
       </c>
       <c r="I39" t="n">
-        <v>311.8</v>
+        <v>312.91</v>
       </c>
       <c r="J39" t="n">
-        <v>19875132</v>
+        <v>19871161</v>
       </c>
       <c r="K39" t="n">
-        <v>19875130</v>
+        <v>19871161</v>
       </c>
       <c r="L39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>19875130</v>
+        <v>19871161</v>
       </c>
       <c r="N39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3502,31 +3502,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>23145825</v>
+        <v>23170842</v>
       </c>
       <c r="F40" t="n">
-        <v>23143810</v>
+        <v>23168880</v>
       </c>
       <c r="G40" t="n">
         <v>-0.01</v>
       </c>
       <c r="H40" t="n">
-        <v>97419052</v>
+        <v>97796268</v>
       </c>
       <c r="I40" t="n">
-        <v>320.89</v>
+        <v>322.07</v>
       </c>
       <c r="J40" t="n">
-        <v>-18667041</v>
+        <v>-18662843</v>
       </c>
       <c r="K40" t="n">
-        <v>-18667042</v>
+        <v>-18662844</v>
       </c>
       <c r="L40" t="n">
         <v>-0</v>
       </c>
       <c r="M40" t="n">
-        <v>-18667042</v>
+        <v>-18662844</v>
       </c>
       <c r="N40" t="n">
         <v>-0</v>
@@ -3554,31 +3554,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-9780474</v>
+        <v>-9802175</v>
       </c>
       <c r="F41" t="n">
-        <v>-9698482</v>
+        <v>-9718246</v>
       </c>
       <c r="G41" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="H41" t="n">
-        <v>64576760</v>
+        <v>64909142</v>
       </c>
       <c r="I41" t="n">
-        <v>760.26</v>
+        <v>762.1900000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>13640090</v>
+        <v>13627582</v>
       </c>
       <c r="K41" t="n">
-        <v>13640089</v>
+        <v>13627582</v>
       </c>
       <c r="L41" t="n">
         <v>-0</v>
       </c>
       <c r="M41" t="n">
-        <v>13640089</v>
+        <v>13627582</v>
       </c>
       <c r="N41" t="n">
         <v>-0</v>
@@ -3606,34 +3606,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>9069934</v>
+        <v>9088727</v>
       </c>
       <c r="F42" t="n">
-        <v>8985639</v>
+        <v>9002548</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.93</v>
+        <v>-0.95</v>
       </c>
       <c r="H42" t="n">
-        <v>83260881</v>
+        <v>83629936</v>
       </c>
       <c r="I42" t="n">
-        <v>817.99</v>
+        <v>820.15</v>
       </c>
       <c r="J42" t="n">
-        <v>-13456425</v>
+        <v>-13444108</v>
       </c>
       <c r="K42" t="n">
-        <v>-13456425</v>
+        <v>-13444110</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M42" t="n">
-        <v>-13456425</v>
+        <v>-13444110</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="43">
@@ -3658,31 +3658,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2560014</v>
+        <v>2551857</v>
       </c>
       <c r="F43" t="n">
-        <v>2644577</v>
+        <v>2638446</v>
       </c>
       <c r="G43" t="n">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="H43" t="n">
-        <v>76919819</v>
+        <v>77265834</v>
       </c>
       <c r="I43" t="n">
-        <v>2904.66</v>
+        <v>2927.83</v>
       </c>
       <c r="J43" t="n">
-        <v>3814606</v>
+        <v>3803835</v>
       </c>
       <c r="K43" t="n">
-        <v>3814604</v>
+        <v>3803833</v>
       </c>
       <c r="L43" t="n">
         <v>-0</v>
       </c>
       <c r="M43" t="n">
-        <v>3814604</v>
+        <v>3803833</v>
       </c>
       <c r="N43" t="n">
         <v>-0</v>
@@ -3710,34 +3710,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1859680</v>
+        <v>1086828</v>
       </c>
       <c r="F44" t="n">
-        <v>1859680</v>
+        <v>1086828</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H44" t="n">
-        <v>6073244</v>
+        <v>6155111</v>
       </c>
       <c r="I44" t="n">
-        <v>226.57</v>
+        <v>466.34</v>
       </c>
       <c r="J44" t="n">
-        <v>36635099</v>
+        <v>32343493</v>
       </c>
       <c r="K44" t="n">
-        <v>38042106</v>
+        <v>32343493</v>
       </c>
       <c r="L44" t="n">
-        <v>3.84</v>
+        <v>-0</v>
       </c>
       <c r="M44" t="n">
-        <v>38042106</v>
+        <v>32343493</v>
       </c>
       <c r="N44" t="n">
-        <v>3.84</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="45">
@@ -3762,34 +3762,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-997155</v>
+        <v>-862123</v>
       </c>
       <c r="F45" t="n">
-        <v>-997155</v>
+        <v>-862123</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>3216409</v>
+        <v>4206160</v>
       </c>
       <c r="I45" t="n">
-        <v>422.56</v>
+        <v>587.88</v>
       </c>
       <c r="J45" t="n">
-        <v>41207527</v>
+        <v>39648423</v>
       </c>
       <c r="K45" t="n">
-        <v>42950525</v>
+        <v>39648423</v>
       </c>
       <c r="L45" t="n">
-        <v>4.23</v>
+        <v>-0</v>
       </c>
       <c r="M45" t="n">
-        <v>42950525</v>
+        <v>39648423</v>
       </c>
       <c r="N45" t="n">
-        <v>4.23</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="46">
@@ -3814,34 +3814,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-2487722</v>
+        <v>-2147008</v>
       </c>
       <c r="F46" t="n">
-        <v>-2487722</v>
+        <v>-2147008</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1725842</v>
+        <v>2921275</v>
       </c>
       <c r="I46" t="n">
-        <v>169.37</v>
+        <v>236.06</v>
       </c>
       <c r="J46" t="n">
-        <v>105696101</v>
+        <v>101562807</v>
       </c>
       <c r="K46" t="n">
-        <v>110163704</v>
+        <v>101562807</v>
       </c>
       <c r="L46" t="n">
-        <v>4.23</v>
+        <v>-0</v>
       </c>
       <c r="M46" t="n">
-        <v>110163704</v>
+        <v>101562807</v>
       </c>
       <c r="N46" t="n">
-        <v>4.23</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="47">
@@ -3866,34 +3866,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2505024</v>
+        <v>2174868</v>
       </c>
       <c r="F47" t="n">
-        <v>2505024</v>
+        <v>2174868</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>6718588</v>
+        <v>7243151</v>
       </c>
       <c r="I47" t="n">
-        <v>168.2</v>
+        <v>233.04</v>
       </c>
       <c r="J47" t="n">
-        <v>-97141265</v>
+        <v>-93751037</v>
       </c>
       <c r="K47" t="n">
-        <v>-101257236</v>
+        <v>-93751037</v>
       </c>
       <c r="L47" t="n">
-        <v>-4.24</v>
+        <v>-0</v>
       </c>
       <c r="M47" t="n">
-        <v>-101257236</v>
+        <v>-93751037</v>
       </c>
       <c r="N47" t="n">
-        <v>-4.24</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="48">
@@ -3918,34 +3918,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-2646450</v>
+        <v>-1824330</v>
       </c>
       <c r="F48" t="n">
-        <v>-2646450</v>
+        <v>-1824330</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1567114</v>
+        <v>3243953</v>
       </c>
       <c r="I48" t="n">
-        <v>159.22</v>
+        <v>277.82</v>
       </c>
       <c r="J48" t="n">
-        <v>8614222</v>
+        <v>10893821</v>
       </c>
       <c r="K48" t="n">
-        <v>9106661</v>
+        <v>10893821</v>
       </c>
       <c r="L48" t="n">
-        <v>5.72</v>
+        <v>-0</v>
       </c>
       <c r="M48" t="n">
-        <v>9106661</v>
+        <v>10893821</v>
       </c>
       <c r="N48" t="n">
-        <v>5.72</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="49">
@@ -3970,34 +3970,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2665460</v>
+        <v>1842637</v>
       </c>
       <c r="F49" t="n">
-        <v>2665460</v>
+        <v>1842637</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>6879024</v>
+        <v>6910920</v>
       </c>
       <c r="I49" t="n">
-        <v>158.08</v>
+        <v>275.06</v>
       </c>
       <c r="J49" t="n">
-        <v>-8549200</v>
+        <v>-10795343</v>
       </c>
       <c r="K49" t="n">
-        <v>-9037136</v>
+        <v>-10795343</v>
       </c>
       <c r="L49" t="n">
-        <v>-5.71</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-9037136</v>
+        <v>-10795343</v>
       </c>
       <c r="N49" t="n">
-        <v>-5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4022,34 +4022,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-1400145</v>
+        <v>-730600</v>
       </c>
       <c r="F50" t="n">
-        <v>-1400145</v>
+        <v>-730600</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2813419</v>
+        <v>4337683</v>
       </c>
       <c r="I50" t="n">
-        <v>300.94</v>
+        <v>693.72</v>
       </c>
       <c r="J50" t="n">
-        <v>-44803536</v>
+        <v>-40539623</v>
       </c>
       <c r="K50" t="n">
-        <v>-46569638</v>
+        <v>-40539623</v>
       </c>
       <c r="L50" t="n">
-        <v>-3.94</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-46569638</v>
+        <v>-40539623</v>
       </c>
       <c r="N50" t="n">
-        <v>-3.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4074,31 +4074,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-264153</v>
+        <v>3208053</v>
       </c>
       <c r="F51" t="n">
-        <v>-223933</v>
+        <v>3059168</v>
       </c>
       <c r="G51" t="n">
-        <v>15.23</v>
+        <v>-4.64</v>
       </c>
       <c r="H51" t="n">
-        <v>1064018</v>
+        <v>3284384</v>
       </c>
       <c r="I51" t="n">
-        <v>502.8</v>
+        <v>2.38</v>
       </c>
       <c r="J51" t="n">
-        <v>-5968037</v>
+        <v>-3597367</v>
       </c>
       <c r="K51" t="n">
-        <v>-5968037</v>
+        <v>-3597367</v>
       </c>
       <c r="L51" t="n">
         <v>-0</v>
       </c>
       <c r="M51" t="n">
-        <v>-5968037</v>
+        <v>-3597367</v>
       </c>
       <c r="N51" t="n">
         <v>-0</v>
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-5612786</v>
+        <v>-5752729</v>
       </c>
       <c r="F52" t="n">
-        <v>-5612009</v>
+        <v>-5748072</v>
       </c>
       <c r="G52" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="H52" t="n">
-        <v>-4324058</v>
+        <v>-5522856</v>
       </c>
       <c r="I52" t="n">
-        <v>22.96</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
-        <v>4065438</v>
+        <v>1943229</v>
       </c>
       <c r="K52" t="n">
-        <v>4065438</v>
+        <v>1943229</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M52" t="n">
-        <v>4065438</v>
+        <v>1943229</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="53">
@@ -4178,31 +4178,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>-13982049</v>
+        <v>-14330200</v>
       </c>
       <c r="F53" t="n">
-        <v>-13980011</v>
+        <v>-14318538</v>
       </c>
       <c r="G53" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="H53" t="n">
-        <v>-12692060</v>
+        <v>-14093322</v>
       </c>
       <c r="I53" t="n">
-        <v>9.23</v>
+        <v>1.65</v>
       </c>
       <c r="J53" t="n">
-        <v>10181091</v>
+        <v>4845693</v>
       </c>
       <c r="K53" t="n">
-        <v>10181091</v>
+        <v>4845693</v>
       </c>
       <c r="L53" t="n">
         <v>-0</v>
       </c>
       <c r="M53" t="n">
-        <v>10181091</v>
+        <v>4845693</v>
       </c>
       <c r="N53" t="n">
         <v>-0</v>
@@ -4230,31 +4230,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>14150512</v>
+        <v>14502319</v>
       </c>
       <c r="F54" t="n">
-        <v>14148751</v>
+        <v>14490748</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="H54" t="n">
-        <v>15436702</v>
+        <v>14715964</v>
       </c>
       <c r="I54" t="n">
-        <v>9.09</v>
+        <v>1.47</v>
       </c>
       <c r="J54" t="n">
-        <v>-10044425</v>
+        <v>-4770320</v>
       </c>
       <c r="K54" t="n">
-        <v>-10044425</v>
+        <v>-4770320</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-10044425</v>
+        <v>-4770320</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -4282,34 +4282,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>-5390580</v>
+        <v>-8608801</v>
       </c>
       <c r="F55" t="n">
-        <v>-5425702</v>
+        <v>-8472099</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.65</v>
+        <v>1.59</v>
       </c>
       <c r="H55" t="n">
-        <v>-4137751</v>
+        <v>-8246883</v>
       </c>
       <c r="I55" t="n">
-        <v>23.24</v>
+        <v>4.2</v>
       </c>
       <c r="J55" t="n">
-        <v>9459173</v>
+        <v>5192962</v>
       </c>
       <c r="K55" t="n">
-        <v>9459173</v>
+        <v>5192962</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M55" t="n">
-        <v>9459173</v>
+        <v>5192962</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="56">
@@ -4334,31 +4334,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5418891</v>
+        <v>8670470</v>
       </c>
       <c r="F56" t="n">
-        <v>5454288</v>
+        <v>8532468</v>
       </c>
       <c r="G56" t="n">
-        <v>0.65</v>
+        <v>-1.59</v>
       </c>
       <c r="H56" t="n">
-        <v>6742239</v>
+        <v>8757684</v>
       </c>
       <c r="I56" t="n">
-        <v>24.42</v>
+        <v>1.01</v>
       </c>
       <c r="J56" t="n">
-        <v>-9352416</v>
+        <v>-5127137</v>
       </c>
       <c r="K56" t="n">
-        <v>-9352416</v>
+        <v>-5127137</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-9352416</v>
+        <v>-5127137</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2004038</v>
+        <v>-1160384</v>
       </c>
       <c r="F57" t="n">
-        <v>1966262</v>
+        <v>-1024282</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.88</v>
+        <v>11.73</v>
       </c>
       <c r="H57" t="n">
-        <v>3254213</v>
+        <v>-799066</v>
       </c>
       <c r="I57" t="n">
-        <v>62.38</v>
+        <v>31.14</v>
       </c>
       <c r="J57" t="n">
-        <v>4302418</v>
+        <v>2771068</v>
       </c>
       <c r="K57" t="n">
-        <v>4302418</v>
+        <v>2771068</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>4302418</v>
+        <v>2771068</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -5110,31 +5110,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>685950</v>
+        <v>738338</v>
       </c>
       <c r="F72" t="n">
-        <v>700526</v>
+        <v>335710</v>
       </c>
       <c r="G72" t="n">
-        <v>2.12</v>
+        <v>-54.53</v>
       </c>
       <c r="H72" t="n">
-        <v>8858574</v>
+        <v>8944908</v>
       </c>
       <c r="I72" t="n">
-        <v>1191.43</v>
+        <v>1111.49</v>
       </c>
       <c r="J72" t="n">
-        <v>1410307</v>
+        <v>1323434</v>
       </c>
       <c r="K72" t="n">
-        <v>1410307</v>
+        <v>1323433</v>
       </c>
       <c r="L72" t="n">
         <v>-0</v>
       </c>
       <c r="M72" t="n">
-        <v>1410307</v>
+        <v>1323433</v>
       </c>
       <c r="N72" t="n">
         <v>-0</v>
@@ -5162,31 +5162,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>-4040895</v>
+        <v>-4048983</v>
       </c>
       <c r="F73" t="n">
-        <v>-3922720</v>
+        <v>-4038203</v>
       </c>
       <c r="G73" t="n">
-        <v>2.92</v>
+        <v>0.27</v>
       </c>
       <c r="H73" t="n">
-        <v>4235328</v>
+        <v>4570995</v>
       </c>
       <c r="I73" t="n">
-        <v>204.81</v>
+        <v>212.89</v>
       </c>
       <c r="J73" t="n">
-        <v>3997660</v>
+        <v>3951547</v>
       </c>
       <c r="K73" t="n">
-        <v>3997642</v>
+        <v>3951468</v>
       </c>
       <c r="L73" t="n">
         <v>-0</v>
       </c>
       <c r="M73" t="n">
-        <v>3997642</v>
+        <v>3951468</v>
       </c>
       <c r="N73" t="n">
         <v>-0</v>
@@ -5214,31 +5214,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>-10002266</v>
+        <v>-10019702</v>
       </c>
       <c r="F74" t="n">
-        <v>-9712874</v>
+        <v>-9987994</v>
       </c>
       <c r="G74" t="n">
-        <v>2.89</v>
+        <v>0.32</v>
       </c>
       <c r="H74" t="n">
-        <v>-1554826</v>
+        <v>-1378796</v>
       </c>
       <c r="I74" t="n">
-        <v>84.45999999999999</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>10244778</v>
+        <v>10124744</v>
       </c>
       <c r="K74" t="n">
-        <v>10244777</v>
+        <v>10124744</v>
       </c>
       <c r="L74" t="n">
         <v>-0</v>
       </c>
       <c r="M74" t="n">
-        <v>10244777</v>
+        <v>10124744</v>
       </c>
       <c r="N74" t="n">
         <v>-0</v>
@@ -5266,31 +5266,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>9897644</v>
+        <v>9911677</v>
       </c>
       <c r="F75" t="n">
-        <v>9617776</v>
+        <v>9873579</v>
       </c>
       <c r="G75" t="n">
-        <v>-2.83</v>
+        <v>-0.38</v>
       </c>
       <c r="H75" t="n">
-        <v>17775824</v>
+        <v>18482777</v>
       </c>
       <c r="I75" t="n">
-        <v>79.59999999999999</v>
+        <v>86.47</v>
       </c>
       <c r="J75" t="n">
-        <v>-9404980</v>
+        <v>-9299598</v>
       </c>
       <c r="K75" t="n">
-        <v>-9404980</v>
+        <v>-9299598</v>
       </c>
       <c r="L75" t="n">
         <v>-0</v>
       </c>
       <c r="M75" t="n">
-        <v>-9404980</v>
+        <v>-9299598</v>
       </c>
       <c r="N75" t="n">
         <v>-0</v>
@@ -5318,31 +5318,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>-4715759</v>
+        <v>-4774489</v>
       </c>
       <c r="F76" t="n">
-        <v>-4606442</v>
+        <v>-4408167</v>
       </c>
       <c r="G76" t="n">
-        <v>2.32</v>
+        <v>7.67</v>
       </c>
       <c r="H76" t="n">
-        <v>3551606</v>
+        <v>4201031</v>
       </c>
       <c r="I76" t="n">
-        <v>175.31</v>
+        <v>187.99</v>
       </c>
       <c r="J76" t="n">
-        <v>2773543</v>
+        <v>2804969</v>
       </c>
       <c r="K76" t="n">
-        <v>2773543</v>
+        <v>2804969</v>
       </c>
       <c r="L76" t="n">
         <v>-0</v>
       </c>
       <c r="M76" t="n">
-        <v>2773543</v>
+        <v>2804969</v>
       </c>
       <c r="N76" t="n">
         <v>-0</v>
@@ -5370,34 +5370,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4599548</v>
+        <v>4652507</v>
       </c>
       <c r="F77" t="n">
-        <v>4498974</v>
+        <v>4278865</v>
       </c>
       <c r="G77" t="n">
-        <v>-2.19</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>12657022</v>
+        <v>12888063</v>
       </c>
       <c r="I77" t="n">
-        <v>175.18</v>
+        <v>177.01</v>
       </c>
       <c r="J77" t="n">
-        <v>-2733139</v>
+        <v>-2764648</v>
       </c>
       <c r="K77" t="n">
-        <v>-2733139</v>
+        <v>-2764648</v>
       </c>
       <c r="L77" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-2733139</v>
+        <v>-2764648</v>
       </c>
       <c r="N77" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -5422,34 +5422,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>486314</v>
+        <v>436560</v>
       </c>
       <c r="F78" t="n">
-        <v>445637</v>
+        <v>797577</v>
       </c>
       <c r="G78" t="n">
-        <v>-8.359999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="H78" t="n">
-        <v>8603685</v>
+        <v>9406775</v>
       </c>
       <c r="I78" t="n">
-        <v>1669.16</v>
+        <v>2054.75</v>
       </c>
       <c r="J78" t="n">
-        <v>-2334757</v>
+        <v>-2242994</v>
       </c>
       <c r="K78" t="n">
-        <v>-2334756</v>
+        <v>-2242995</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M78" t="n">
-        <v>-2334756</v>
+        <v>-2242995</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="79">
@@ -5474,31 +5474,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>-80541</v>
+        <v>-3091044</v>
       </c>
       <c r="F79" t="n">
-        <v>-100930</v>
+        <v>-3202297</v>
       </c>
       <c r="G79" t="n">
-        <v>-25.32</v>
+        <v>-3.6</v>
       </c>
       <c r="H79" t="n">
-        <v>-2036123</v>
+        <v>-5466124</v>
       </c>
       <c r="I79" t="n">
-        <v>-2428.07</v>
+        <v>-76.84</v>
       </c>
       <c r="J79" t="n">
-        <v>6195844</v>
+        <v>4759019</v>
       </c>
       <c r="K79" t="n">
-        <v>6195844</v>
+        <v>4759019</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>6195844</v>
+        <v>4759019</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
@@ -5526,34 +5526,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5839745</v>
+        <v>6517463</v>
       </c>
       <c r="F80" t="n">
-        <v>5847361</v>
+        <v>6494118</v>
       </c>
       <c r="G80" t="n">
-        <v>0.13</v>
+        <v>-0.36</v>
       </c>
       <c r="H80" t="n">
-        <v>3912168</v>
+        <v>4230291</v>
       </c>
       <c r="I80" t="n">
-        <v>-33.01</v>
+        <v>-35.09</v>
       </c>
       <c r="J80" t="n">
-        <v>-4419244</v>
+        <v>-2700482</v>
       </c>
       <c r="K80" t="n">
-        <v>-4413204</v>
+        <v>-2700482</v>
       </c>
       <c r="L80" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-4413204</v>
+        <v>-2700482</v>
       </c>
       <c r="N80" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5578,34 +5578,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>14547712</v>
+        <v>16234608</v>
       </c>
       <c r="F81" t="n">
-        <v>14566597</v>
+        <v>16176360</v>
       </c>
       <c r="G81" t="n">
-        <v>0.13</v>
+        <v>-0.36</v>
       </c>
       <c r="H81" t="n">
-        <v>12631404</v>
+        <v>13912533</v>
       </c>
       <c r="I81" t="n">
-        <v>-13.17</v>
+        <v>-14.3</v>
       </c>
       <c r="J81" t="n">
-        <v>-11074196</v>
+        <v>-6750162</v>
       </c>
       <c r="K81" t="n">
-        <v>-11074196</v>
+        <v>-6750162</v>
       </c>
       <c r="L81" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-11074196</v>
+        <v>-6750162</v>
       </c>
       <c r="N81" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -5630,34 +5630,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>-14729104</v>
+        <v>-16431857</v>
       </c>
       <c r="F82" t="n">
-        <v>-14748273</v>
+        <v>-16373268</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.13</v>
+        <v>0.36</v>
       </c>
       <c r="H82" t="n">
-        <v>-16683466</v>
+        <v>-18637095</v>
       </c>
       <c r="I82" t="n">
-        <v>-13.27</v>
+        <v>-13.42</v>
       </c>
       <c r="J82" t="n">
-        <v>10924960</v>
+        <v>6665897</v>
       </c>
       <c r="K82" t="n">
-        <v>10924960</v>
+        <v>6665897</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M82" t="n">
-        <v>10924960</v>
+        <v>6665897</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="83">
@@ -5682,34 +5682,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5918996</v>
+        <v>9268549</v>
       </c>
       <c r="F83" t="n">
-        <v>5945027</v>
+        <v>9343538</v>
       </c>
       <c r="G83" t="n">
-        <v>0.44</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H83" t="n">
-        <v>4009834</v>
+        <v>7079711</v>
       </c>
       <c r="I83" t="n">
-        <v>-32.25</v>
+        <v>-23.62</v>
       </c>
       <c r="J83" t="n">
-        <v>-10019521</v>
+        <v>-6995541</v>
       </c>
       <c r="K83" t="n">
-        <v>-10019521</v>
+        <v>-6995541</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M83" t="n">
-        <v>-10019521</v>
+        <v>-6995541</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="84">
@@ -5734,31 +5734,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>-5959061</v>
+        <v>-9337767</v>
       </c>
       <c r="F84" t="n">
-        <v>-5985038</v>
+        <v>-9414075</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.44</v>
+        <v>-0.82</v>
       </c>
       <c r="H84" t="n">
-        <v>-7920231</v>
+        <v>-11677902</v>
       </c>
       <c r="I84" t="n">
-        <v>-32.91</v>
+        <v>-25.06</v>
       </c>
       <c r="J84" t="n">
-        <v>9908194</v>
+        <v>6920403</v>
       </c>
       <c r="K84" t="n">
-        <v>9908194</v>
+        <v>6920403</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>9908194</v>
+        <v>6920403</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -5786,34 +5786,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>-1761763</v>
+        <v>811131</v>
       </c>
       <c r="F85" t="n">
-        <v>-1744880</v>
+        <v>921099</v>
       </c>
       <c r="G85" t="n">
-        <v>0.96</v>
+        <v>13.56</v>
       </c>
       <c r="H85" t="n">
-        <v>-3680073</v>
+        <v>-1342728</v>
       </c>
       <c r="I85" t="n">
-        <v>-108.89</v>
+        <v>-265.54</v>
       </c>
       <c r="J85" t="n">
-        <v>-4399754</v>
+        <v>-3604866</v>
       </c>
       <c r="K85" t="n">
-        <v>-4399754</v>
+        <v>-3604866</v>
       </c>
       <c r="L85" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>-4399754</v>
+        <v>-3604866</v>
       </c>
       <c r="N85" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -6971,13 +6971,13 @@
         <v>-13034099</v>
       </c>
       <c r="L111" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
         <v>-13034099</v>
       </c>
       <c r="N111" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -7019,13 +7019,13 @@
         <v>12920318</v>
       </c>
       <c r="L112" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
         <v>12920318</v>
       </c>
       <c r="N112" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -7215,13 +7215,13 @@
         <v>-27313</v>
       </c>
       <c r="L116" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
         <v>-27313</v>
       </c>
       <c r="N116" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -7411,13 +7411,13 @@
         <v>-24816</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M120" t="n">
         <v>-24816</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="121">
@@ -7442,34 +7442,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>-23200844</v>
+        <v>-23069223</v>
       </c>
       <c r="F121" t="n">
-        <v>-23200844</v>
+        <v>-23069223</v>
       </c>
       <c r="G121" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>-29187258</v>
+        <v>-29380990</v>
       </c>
       <c r="I121" t="n">
-        <v>-25.8</v>
+        <v>-27.36</v>
       </c>
       <c r="J121" t="n">
-        <v>8878491</v>
+        <v>9246710</v>
       </c>
       <c r="K121" t="n">
-        <v>8942131</v>
+        <v>9246710</v>
       </c>
       <c r="L121" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>8942131</v>
+        <v>9246710</v>
       </c>
       <c r="N121" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -7494,34 +7494,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>11610773</v>
+        <v>11681064</v>
       </c>
       <c r="F122" t="n">
-        <v>11610773</v>
+        <v>11681064</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H122" t="n">
-        <v>5624359</v>
+        <v>5369297</v>
       </c>
       <c r="I122" t="n">
-        <v>-51.56</v>
+        <v>-54.03</v>
       </c>
       <c r="J122" t="n">
-        <v>-5315372</v>
+        <v>-5534453</v>
       </c>
       <c r="K122" t="n">
-        <v>-5341049</v>
+        <v>-5534453</v>
       </c>
       <c r="L122" t="n">
-        <v>-0.48</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>-5341049</v>
+        <v>-5534453</v>
       </c>
       <c r="N122" t="n">
-        <v>-0.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -7546,34 +7546,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>28977216</v>
+        <v>29150936</v>
       </c>
       <c r="F123" t="n">
-        <v>28977216</v>
+        <v>29150936</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>22990802</v>
+        <v>22839170</v>
       </c>
       <c r="I123" t="n">
-        <v>-20.66</v>
+        <v>-21.65</v>
       </c>
       <c r="J123" t="n">
-        <v>-13322407</v>
+        <v>-13871488</v>
       </c>
       <c r="K123" t="n">
-        <v>-13386640</v>
+        <v>-13871488</v>
       </c>
       <c r="L123" t="n">
-        <v>-0.48</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>-13386640</v>
+        <v>-13871488</v>
       </c>
       <c r="N123" t="n">
-        <v>-0.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -7598,34 +7598,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>-29143817</v>
+        <v>-29324358</v>
       </c>
       <c r="F124" t="n">
-        <v>-29143817</v>
+        <v>-29324358</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>-35130231</v>
+        <v>-35636125</v>
       </c>
       <c r="I124" t="n">
-        <v>-20.54</v>
+        <v>-21.52</v>
       </c>
       <c r="J124" t="n">
-        <v>13209812</v>
+        <v>13754294</v>
       </c>
       <c r="K124" t="n">
-        <v>13273911</v>
+        <v>13754294</v>
       </c>
       <c r="L124" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>13273911</v>
+        <v>13754294</v>
       </c>
       <c r="N124" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -7650,34 +7650,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>32208709</v>
+        <v>32168797</v>
       </c>
       <c r="F125" t="n">
-        <v>32208709</v>
+        <v>32168797</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H125" t="n">
-        <v>26222295</v>
+        <v>25857030</v>
       </c>
       <c r="I125" t="n">
-        <v>-18.59</v>
+        <v>-19.62</v>
       </c>
       <c r="J125" t="n">
-        <v>-13312668</v>
+        <v>-13863554</v>
       </c>
       <c r="K125" t="n">
-        <v>-13395334</v>
+        <v>-13863554</v>
       </c>
       <c r="L125" t="n">
-        <v>-0.62</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>-13395334</v>
+        <v>-13863554</v>
       </c>
       <c r="N125" t="n">
-        <v>-0.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -7702,34 +7702,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>-32400695</v>
+        <v>-32356462</v>
       </c>
       <c r="F126" t="n">
-        <v>-32400695</v>
+        <v>-32356462</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>-38387109</v>
+        <v>-38668229</v>
       </c>
       <c r="I126" t="n">
-        <v>-18.48</v>
+        <v>-19.51</v>
       </c>
       <c r="J126" t="n">
-        <v>13208438</v>
+        <v>13754869</v>
       </c>
       <c r="K126" t="n">
-        <v>13290883</v>
+        <v>13754869</v>
       </c>
       <c r="L126" t="n">
-        <v>0.62</v>
+        <v>-0</v>
       </c>
       <c r="M126" t="n">
-        <v>13290883</v>
+        <v>13754869</v>
       </c>
       <c r="N126" t="n">
-        <v>0.62</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="127">
@@ -7754,34 +7754,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>17750436</v>
+        <v>17604316</v>
       </c>
       <c r="F127" t="n">
-        <v>17750436</v>
+        <v>17604316</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H127" t="n">
-        <v>11764022</v>
+        <v>11292549</v>
       </c>
       <c r="I127" t="n">
-        <v>-33.73</v>
+        <v>-35.85</v>
       </c>
       <c r="J127" t="n">
-        <v>-6582613</v>
+        <v>-6856088</v>
       </c>
       <c r="K127" t="n">
-        <v>-6633509</v>
+        <v>-6856087</v>
       </c>
       <c r="L127" t="n">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>-6633509</v>
+        <v>-6856087</v>
       </c>
       <c r="N127" t="n">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -7806,31 +7806,31 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4819367</v>
+        <v>4794091</v>
       </c>
       <c r="F128" t="n">
-        <v>4819367</v>
+        <v>4794091</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>8238158</v>
+        <v>8224713</v>
       </c>
       <c r="I128" t="n">
-        <v>70.94</v>
+        <v>71.56</v>
       </c>
       <c r="J128" t="n">
-        <v>-201955</v>
+        <v>-218039</v>
       </c>
       <c r="K128" t="n">
-        <v>-201955</v>
+        <v>-218039</v>
       </c>
       <c r="L128" t="n">
         <v>-0</v>
       </c>
       <c r="M128" t="n">
-        <v>-201955</v>
+        <v>-218039</v>
       </c>
       <c r="N128" t="n">
         <v>-0</v>
@@ -7858,31 +7858,31 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>-1920362</v>
+        <v>-1914113</v>
       </c>
       <c r="F129" t="n">
-        <v>-1920362</v>
+        <v>-1914113</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>1498429</v>
+        <v>1516509</v>
       </c>
       <c r="I129" t="n">
-        <v>178.03</v>
+        <v>179.23</v>
       </c>
       <c r="J129" t="n">
-        <v>80757</v>
+        <v>87217</v>
       </c>
       <c r="K129" t="n">
-        <v>80757</v>
+        <v>87217</v>
       </c>
       <c r="L129" t="n">
         <v>-0</v>
       </c>
       <c r="M129" t="n">
-        <v>80757</v>
+        <v>87217</v>
       </c>
       <c r="N129" t="n">
         <v>-0</v>
@@ -7910,31 +7910,31 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>-4799439</v>
+        <v>-4783659</v>
       </c>
       <c r="F130" t="n">
-        <v>-4799439</v>
+        <v>-4783659</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>-1380648</v>
+        <v>-1353037</v>
       </c>
       <c r="I130" t="n">
-        <v>71.23</v>
+        <v>71.72</v>
       </c>
       <c r="J130" t="n">
-        <v>202022</v>
+        <v>218217</v>
       </c>
       <c r="K130" t="n">
-        <v>202022</v>
+        <v>218217</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>202022</v>
+        <v>218217</v>
       </c>
       <c r="N130" t="n">
         <v>0</v>
@@ -7962,31 +7962,31 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4804333</v>
+        <v>4788844</v>
       </c>
       <c r="F131" t="n">
-        <v>4804333</v>
+        <v>4788844</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>8223124</v>
+        <v>8219466</v>
       </c>
       <c r="I131" t="n">
-        <v>71.16</v>
+        <v>71.64</v>
       </c>
       <c r="J131" t="n">
-        <v>-201863</v>
+        <v>-218075</v>
       </c>
       <c r="K131" t="n">
-        <v>-201863</v>
+        <v>-218075</v>
       </c>
       <c r="L131" t="n">
         <v>-0</v>
       </c>
       <c r="M131" t="n">
-        <v>-201863</v>
+        <v>-218075</v>
       </c>
       <c r="N131" t="n">
         <v>-0</v>
@@ -8014,34 +8014,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>-6211727</v>
+        <v>-6184422</v>
       </c>
       <c r="F132" t="n">
-        <v>-6211727</v>
+        <v>-6184422</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>-2792936</v>
+        <v>-2753800</v>
       </c>
       <c r="I132" t="n">
-        <v>55.04</v>
+        <v>55.47</v>
       </c>
       <c r="J132" t="n">
-        <v>261185</v>
+        <v>282038</v>
       </c>
       <c r="K132" t="n">
-        <v>261185</v>
+        <v>282038</v>
       </c>
       <c r="L132" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>261185</v>
+        <v>282038</v>
       </c>
       <c r="N132" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -8066,31 +8066,31 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6226302</v>
+        <v>6197623</v>
       </c>
       <c r="F133" t="n">
-        <v>6226302</v>
+        <v>6197623</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>9645093</v>
+        <v>9628245</v>
       </c>
       <c r="I133" t="n">
-        <v>54.91</v>
+        <v>55.35</v>
       </c>
       <c r="J133" t="n">
-        <v>-261034</v>
+        <v>-281868</v>
       </c>
       <c r="K133" t="n">
-        <v>-261034</v>
+        <v>-281868</v>
       </c>
       <c r="L133" t="n">
         <v>-0</v>
       </c>
       <c r="M133" t="n">
-        <v>-261034</v>
+        <v>-281868</v>
       </c>
       <c r="N133" t="n">
         <v>-0</v>
@@ -8118,31 +8118,31 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>-3849882</v>
+        <v>-3828265</v>
       </c>
       <c r="F134" t="n">
-        <v>-3849882</v>
+        <v>-3828265</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>-431091</v>
+        <v>-397643</v>
       </c>
       <c r="I134" t="n">
-        <v>88.8</v>
+        <v>89.61</v>
       </c>
       <c r="J134" t="n">
-        <v>161509</v>
+        <v>174326</v>
       </c>
       <c r="K134" t="n">
-        <v>161509</v>
+        <v>174326</v>
       </c>
       <c r="L134" t="n">
         <v>-0</v>
       </c>
       <c r="M134" t="n">
-        <v>161509</v>
+        <v>174326</v>
       </c>
       <c r="N134" t="n">
         <v>-0</v>
@@ -8170,34 +8170,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>-9579136</v>
+        <v>-9659224</v>
       </c>
       <c r="F135" t="n">
-        <v>-9579136</v>
+        <v>-9659224</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>-16385507</v>
+        <v>-16501600</v>
       </c>
       <c r="I135" t="n">
-        <v>-71.05</v>
+        <v>-70.84</v>
       </c>
       <c r="J135" t="n">
-        <v>496357</v>
+        <v>377410</v>
       </c>
       <c r="K135" t="n">
-        <v>496357</v>
+        <v>377410</v>
       </c>
       <c r="L135" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>496357</v>
+        <v>377410</v>
       </c>
       <c r="N135" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -8222,34 +8222,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3804480</v>
+        <v>3851128</v>
       </c>
       <c r="F136" t="n">
-        <v>3804480</v>
+        <v>3851128</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>-3001891</v>
+        <v>-2991248</v>
       </c>
       <c r="I136" t="n">
-        <v>-178.9</v>
+        <v>-177.67</v>
       </c>
       <c r="J136" t="n">
-        <v>-198954</v>
+        <v>-150890</v>
       </c>
       <c r="K136" t="n">
-        <v>-198954</v>
+        <v>-150890</v>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M136" t="n">
-        <v>-198954</v>
+        <v>-150890</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="137">
@@ -8274,34 +8274,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>9507572</v>
+        <v>9624999</v>
       </c>
       <c r="F137" t="n">
-        <v>9507572</v>
+        <v>9624999</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>2701201</v>
+        <v>2782623</v>
       </c>
       <c r="I137" t="n">
-        <v>-71.59</v>
+        <v>-71.09</v>
       </c>
       <c r="J137" t="n">
-        <v>-497659</v>
+        <v>-377395</v>
       </c>
       <c r="K137" t="n">
-        <v>-497659</v>
+        <v>-377395</v>
       </c>
       <c r="L137" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>-497659</v>
+        <v>-377395</v>
       </c>
       <c r="N137" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -8326,34 +8326,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>-9519330</v>
+        <v>-9634045</v>
       </c>
       <c r="F138" t="n">
-        <v>-9519330</v>
+        <v>-9634045</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>-16325701</v>
+        <v>-16476421</v>
       </c>
       <c r="I138" t="n">
-        <v>-71.5</v>
+        <v>-71.02</v>
       </c>
       <c r="J138" t="n">
-        <v>496910</v>
+        <v>377015</v>
       </c>
       <c r="K138" t="n">
-        <v>496910</v>
+        <v>377015</v>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M138" t="n">
-        <v>496910</v>
+        <v>377015</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="139">
@@ -8378,31 +8378,31 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>12325875</v>
+        <v>12453889</v>
       </c>
       <c r="F139" t="n">
-        <v>12325875</v>
+        <v>12453889</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>5519504</v>
+        <v>5611513</v>
       </c>
       <c r="I139" t="n">
-        <v>-55.22</v>
+        <v>-54.94</v>
       </c>
       <c r="J139" t="n">
-        <v>-642874</v>
+        <v>-488061</v>
       </c>
       <c r="K139" t="n">
-        <v>-642874</v>
+        <v>-488061</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>-642874</v>
+        <v>-488061</v>
       </c>
       <c r="N139" t="n">
         <v>0</v>
@@ -8430,31 +8430,31 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>-12364019</v>
+        <v>-12480955</v>
       </c>
       <c r="F140" t="n">
-        <v>-12364019</v>
+        <v>-12480955</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>-19170390</v>
+        <v>-19323331</v>
       </c>
       <c r="I140" t="n">
-        <v>-55.05</v>
+        <v>-54.82</v>
       </c>
       <c r="J140" t="n">
-        <v>641851</v>
+        <v>487740</v>
       </c>
       <c r="K140" t="n">
-        <v>641851</v>
+        <v>487740</v>
       </c>
       <c r="L140" t="n">
         <v>-0</v>
       </c>
       <c r="M140" t="n">
-        <v>641851</v>
+        <v>487740</v>
       </c>
       <c r="N140" t="n">
         <v>-0</v>
@@ -8482,31 +8482,31 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>7654488</v>
+        <v>7716072</v>
       </c>
       <c r="F141" t="n">
-        <v>7654488</v>
+        <v>7716072</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>848117</v>
+        <v>873696</v>
       </c>
       <c r="I141" t="n">
-        <v>-88.92</v>
+        <v>-88.68000000000001</v>
       </c>
       <c r="J141" t="n">
-        <v>-397134</v>
+        <v>-301931</v>
       </c>
       <c r="K141" t="n">
-        <v>-397134</v>
+        <v>-301931</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>-397134</v>
+        <v>-301931</v>
       </c>
       <c r="N141" t="n">
         <v>0</v>
@@ -8607,13 +8607,13 @@
         <v>-8143731</v>
       </c>
       <c r="L143" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
         <v>-8143731</v>
       </c>
       <c r="N143" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -8852,13 +8852,13 @@
         <v>5491903</v>
       </c>
       <c r="G148" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H148" t="n">
         <v>5491903</v>
       </c>
       <c r="I148" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
         <v>6207952</v>
@@ -8934,13 +8934,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.7826</v>
+        <v>2.9155</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7826</v>
+        <v>2.9155</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>1.6147</v>
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>464115515</v>
+        <v>469321504</v>
       </c>
       <c r="E2" t="n">
-        <v>464115515</v>
+        <v>469321504</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -9083,15 +9083,15 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1916356062</v>
+        <v>1974746197</v>
       </c>
       <c r="E3" t="n">
-        <v>1916356062</v>
+        <v>1974746197</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
@@ -9121,22 +9121,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35717003</v>
+        <v>33974882</v>
       </c>
       <c r="E4" t="n">
-        <v>35414190</v>
+        <v>33981839</v>
       </c>
       <c r="F4" t="n">
-        <v>2.98</v>
+        <v>2.83</v>
       </c>
       <c r="G4" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.85</v>
+        <v>0.02</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.025</v>
+        <v>0.001</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -9167,26 +9167,26 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-122122222</v>
+        <v>-117121149</v>
       </c>
       <c r="E5" t="n">
-        <v>-126174091</v>
+        <v>-117121145</v>
       </c>
       <c r="F5" t="n">
-        <v>-10.18</v>
+        <v>-9.76</v>
       </c>
       <c r="G5" t="n">
-        <v>-10.51</v>
+        <v>-9.76</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.32</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.338</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -9213,22 +9213,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-39402457</v>
+        <v>-37559746</v>
       </c>
       <c r="E6" t="n">
-        <v>-39092145</v>
+        <v>-37574614</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.28</v>
+        <v>-3.13</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.26</v>
+        <v>-3.13</v>
       </c>
       <c r="H6" t="n">
-        <v>0.79</v>
+        <v>-0.04</v>
       </c>
       <c r="I6" t="n">
-        <v>0.026</v>
+        <v>-0.001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -9259,26 +9259,26 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>133536849</v>
+        <v>127816606</v>
       </c>
       <c r="E7" t="n">
-        <v>137940218</v>
+        <v>127816606</v>
       </c>
       <c r="F7" t="n">
-        <v>11.13</v>
+        <v>10.65</v>
       </c>
       <c r="G7" t="n">
-        <v>11.5</v>
+        <v>10.65</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.367</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -9305,26 +9305,26 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24954859</v>
+        <v>24824504</v>
       </c>
       <c r="E8" t="n">
-        <v>24977852</v>
+        <v>25518180</v>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09</v>
+        <v>2.79</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002</v>
+        <v>0.058</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -9351,26 +9351,26 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-46096958</v>
+        <v>-42896763</v>
       </c>
       <c r="E9" t="n">
-        <v>-47913953</v>
+        <v>-42896766</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.84</v>
+        <v>-3.57</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.99</v>
+        <v>-3.57</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.94</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.151</v>
+        <v>-0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -9397,26 +9397,26 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-25784012</v>
+        <v>-25774751</v>
       </c>
       <c r="E10" t="n">
-        <v>-25843503</v>
+        <v>-26533540</v>
       </c>
       <c r="F10" t="n">
         <v>-2.15</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.15</v>
+        <v>-2.21</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.23</v>
+        <v>-2.94</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.005</v>
+        <v>-0.063</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -9443,26 +9443,26 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>35246098</v>
+        <v>32328723</v>
       </c>
       <c r="E11" t="n">
-        <v>36716749</v>
+        <v>32328724</v>
       </c>
       <c r="F11" t="n">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="G11" t="n">
-        <v>3.06</v>
+        <v>2.69</v>
       </c>
       <c r="H11" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -9489,22 +9489,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-8155775</v>
+        <v>-8859881</v>
       </c>
       <c r="E12" t="n">
-        <v>-8331223</v>
+        <v>-9534012</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.68</v>
+        <v>-0.74</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.79</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.15</v>
+        <v>-7.61</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.015</v>
+        <v>-0.056</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -9535,26 +9535,26 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-20497479</v>
+        <v>-20882482</v>
       </c>
       <c r="E13" t="n">
-        <v>-20902971</v>
+        <v>-20882480</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.71</v>
+        <v>-1.74</v>
       </c>
       <c r="G13" t="n">
         <v>-1.74</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.98</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.034</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -9581,22 +9581,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4659881</v>
+        <v>5485240</v>
       </c>
       <c r="E14" t="n">
-        <v>4842098</v>
+        <v>6147183</v>
       </c>
       <c r="F14" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="H14" t="n">
-        <v>3.91</v>
+        <v>12.07</v>
       </c>
       <c r="I14" t="n">
-        <v>0.015</v>
+        <v>0.055</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -9627,26 +9627,26 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>20867291</v>
+        <v>21276912</v>
       </c>
       <c r="E15" t="n">
-        <v>21277061</v>
+        <v>21276918</v>
       </c>
       <c r="F15" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="G15" t="n">
         <v>1.77</v>
       </c>
       <c r="H15" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -9673,22 +9673,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-16848137</v>
+        <v>-16078052</v>
       </c>
       <c r="E16" t="n">
-        <v>-16722189</v>
+        <v>-16086555</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4</v>
+        <v>-1.34</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.39</v>
+        <v>-1.34</v>
       </c>
       <c r="H16" t="n">
-        <v>0.75</v>
+        <v>-0.05</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01</v>
+        <v>-0.001</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -9719,26 +9719,26 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>52023150</v>
+        <v>49828201</v>
       </c>
       <c r="E17" t="n">
-        <v>53744178</v>
+        <v>49825925</v>
       </c>
       <c r="F17" t="n">
-        <v>4.34</v>
+        <v>4.15</v>
       </c>
       <c r="G17" t="n">
-        <v>4.48</v>
+        <v>4.15</v>
       </c>
       <c r="H17" t="n">
-        <v>3.31</v>
+        <v>-0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.143</v>
+        <v>-0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -9773,7 +9773,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
@@ -9920,20 +9920,20 @@
         <v>1500000000</v>
       </c>
       <c r="E2" t="n">
-        <v>10.2985</v>
+        <v>10.3259</v>
       </c>
       <c r="F2" t="n">
-        <v>10.2985</v>
+        <v>10.3259</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.117813</v>
+        <v>1.118302</v>
       </c>
       <c r="J2" t="n">
-        <v>1.117813</v>
+        <v>1.118302</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -9962,20 +9962,20 @@
         <v>900000000</v>
       </c>
       <c r="E3" t="n">
-        <v>10.2937</v>
+        <v>10.234</v>
       </c>
       <c r="F3" t="n">
-        <v>10.2937</v>
+        <v>10.234</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.177879</v>
+        <v>1.175849</v>
       </c>
       <c r="J3" t="n">
-        <v>1.177879</v>
+        <v>1.175849</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -10004,20 +10004,20 @@
         <v>1000000000</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6434</v>
+        <v>6.5254</v>
       </c>
       <c r="F4" t="n">
-        <v>6.6434</v>
+        <v>6.5254</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1.043147</v>
+        <v>1.042283</v>
       </c>
       <c r="J4" t="n">
-        <v>1.043147</v>
+        <v>1.042283</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -10056,10 +10056,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1.072207</v>
+        <v>1.072121</v>
       </c>
       <c r="J5" t="n">
-        <v>1.072207</v>
+        <v>1.072121</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -10071,7 +10071,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -10085,23 +10085,23 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>600000000</v>
+        <v>1500000000</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6291</v>
+        <v>5.0985</v>
       </c>
       <c r="F6" t="n">
-        <v>4.6291</v>
+        <v>5.0985</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1.019719</v>
+        <v>1.045712</v>
       </c>
       <c r="J6" t="n">
-        <v>1.019719</v>
+        <v>1.045712</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -10127,25 +10127,27 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1500000000</v>
+        <v>600000000</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5106</v>
+        <v>4.6768</v>
       </c>
       <c r="F7" t="n">
-        <v>4.5106</v>
+        <v>4.6768</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.986509</v>
+        <v>1.020198</v>
       </c>
       <c r="J7" t="n">
-        <v>0.986509</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>1.020198</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" t="b">
         <v>1</v>
       </c>
@@ -10210,20 +10212,20 @@
         <v>1100000000</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9931</v>
+        <v>3.926</v>
       </c>
       <c r="F9" t="n">
-        <v>3.9931</v>
+        <v>3.926</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.005995</v>
+        <v>1.012384</v>
       </c>
       <c r="J9" t="n">
-        <v>1.005995</v>
+        <v>1.012384</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -10252,20 +10254,20 @@
         <v>200000000</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7569</v>
+        <v>3.7628</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7569</v>
+        <v>3.7628</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.000007</v>
+        <v>1.000006</v>
       </c>
       <c r="J10" t="n">
-        <v>1.000007</v>
+        <v>1.000006</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -10614,20 +10616,20 @@
         <v>2100000000</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3327</v>
+        <v>-3.3872</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.3327</v>
+        <v>-3.3872</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.984198</v>
+        <v>-0.998822</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.984198</v>
+        <v>-0.998822</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="b">
@@ -10654,20 +10656,20 @@
         <v>400000000</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.7491</v>
+        <v>-3.7581</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.7491</v>
+        <v>-3.7581</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.000005</v>
+        <v>-1.000007</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.000005</v>
+        <v>-1.000007</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -10736,20 +10738,20 @@
         <v>1200000000</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9573</v>
+        <v>-4.0145</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.9573</v>
+        <v>-4.0145</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.006574</v>
+        <v>-1.010588</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.006574</v>
+        <v>-1.010588</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
